--- a/qa/3기리포트_QA_TC.xlsx
+++ b/qa/3기리포트_QA_TC.xlsx
@@ -5145,7 +5145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5848,8 +5848,76 @@
       </c>
       <c r="N10" s="15" t="n"/>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>BUG-10</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>TOP 3 순위 · 횟수 색이 목업과 다름</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Trivial</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>개발 수정</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>SC-RP-04</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>https://dev-meli-web.meli.health/report-3gi?state=nice 04 화면</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>순위 숫자 1~3 모두 강조색 · 횟수 모두 본문색 Bold · 썸네일 둥근 사각 (목업 · 디스크립션 10/12 정정)</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>1위만 강조색 · 2 · 3위 회색 · 횟수 1위만 강조색</t>
+        </is>
+      </c>
+      <c r="J11" s="16" t="inlineStr">
+        <is>
+          <t>cmp_04.png</t>
+        </is>
+      </c>
+      <c r="K11" s="10" t="inlineStr">
+        <is>
+          <t>S4-06 · 변경이력 40</t>
+        </is>
+      </c>
+      <c r="L11" s="10" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="M11" s="10" t="inlineStr">
+        <is>
+          <t>S-04</t>
+        </is>
+      </c>
+      <c r="N11" s="15" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>새 결함은 아래 빈 행에 BUG-06부터 이어서 적습니다. 심각도: Blocker 사용 불가 · Major 잘못된 정보 · Minor 정본과 다름 · Trivial 표기</t>
         </is>
@@ -5875,6 +5943,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5977,7 +6046,11 @@
           <t>1463:1286</t>
         </is>
       </c>
-      <c r="H2" s="15" t="n"/>
+      <c r="H2" s="15" t="inlineStr">
+        <is>
+          <t>디스크립션(4줄 · 6160) 유지 — 목업 카드는 Pretendard 폰트라 기획이 피그마에서 직접 수정 필요 (1463:1286 · 실패 1461:6914)</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="54" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
@@ -6015,7 +6088,11 @@
           <t>1484:1453</t>
         </is>
       </c>
-      <c r="H3" s="15" t="n"/>
+      <c r="H3" s="15" t="inlineStr">
+        <is>
+          <t>완료(10/12) — 디스크립션 S8-02 · S8-04를 목업 배치로 정정 · 프로토타입 · 문서 반영</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="54" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
@@ -6053,7 +6130,11 @@
           <t>1461:6901</t>
         </is>
       </c>
-      <c r="H4" s="15" t="n"/>
+      <c r="H4" s="15" t="inlineStr">
+        <is>
+          <t>완료(10/12) — 목업 기준 "신청이 완료되지 못했습니다" · 프로그램명 없음 · 디스크립션 · 프로토타입 · 문서 반영</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="54" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -6091,7 +6172,11 @@
           <t>1239:1351</t>
         </is>
       </c>
-      <c r="H5" s="15" t="n"/>
+      <c r="H5" s="15" t="inlineStr">
+        <is>
+          <t>완료(10/12) — 디스크립션 S1-01을 "2026 …"으로 정정 · 프로토타입 · 문서 반영</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="54" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -6129,7 +6214,11 @@
           <t>1240:1351</t>
         </is>
       </c>
-      <c r="H6" s="15" t="n"/>
+      <c r="H6" s="15" t="inlineStr">
+        <is>
+          <t>완료(10/12) — 캐릭터 없음으로 정정 · 개발 BUG-05 유지</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="54" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -6167,7 +6256,11 @@
           <t>1239:1965</t>
         </is>
       </c>
-      <c r="H7" s="15" t="n"/>
+      <c r="H7" s="15" t="inlineStr">
+        <is>
+          <t>완료(10/12) — 디스크립션을 180° · 180 − 점수 × 12로 정정</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="54" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -6205,7 +6298,11 @@
           <t>1264:1433</t>
         </is>
       </c>
-      <c r="H8" s="15" t="n"/>
+      <c r="H8" s="15" t="inlineStr">
+        <is>
+          <t>완료(10/12) — 둥근 사각 인장으로 정정 · 프로토타입 · 문서 반영</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="54" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
@@ -6243,7 +6340,11 @@
           <t>1136:5858</t>
         </is>
       </c>
-      <c r="H9" s="15" t="n"/>
+      <c r="H9" s="15" t="inlineStr">
+        <is>
+          <t>목업 유지(아이콘 자리) — 프로토타입은 이미 같음 · 개발 BUG-07 유지</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="54" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -6281,7 +6382,11 @@
           <t>1122:856</t>
         </is>
       </c>
-      <c r="H10" s="15" t="n"/>
+      <c r="H10" s="15" t="inlineStr">
+        <is>
+          <t>목업 샘플값 69% → 59% — Pretendard 폰트라 기획이 피그마에서 직접 수정 필요 (1122:887)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">

--- a/qa/3기리포트_QA_TC.xlsx
+++ b/qa/3기리포트_QA_TC.xlsx
@@ -152,13 +152,13 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1042,23 +1042,23 @@
         </is>
       </c>
       <c r="C5" s="4">
-        <f>COUNTIF(TC!$B$2:$B$52,A5)</f>
+        <f>COUNTIF(TC!$B$2:$B$51,A5)</f>
         <v/>
       </c>
       <c r="D5" s="4">
-        <f>COUNTIFS(TC!$B$2:$B$52,A5,TC!$N$2:$N$52,"통과")</f>
+        <f>COUNTIFS(TC!$B$2:$B$51,A5,TC!$N$2:$N$51,"통과")</f>
         <v/>
       </c>
       <c r="E5" s="4">
-        <f>COUNTIFS(TC!$B$2:$B$52,A5,TC!$N$2:$N$52,"실패")</f>
+        <f>COUNTIFS(TC!$B$2:$B$51,A5,TC!$N$2:$N$51,"실패")</f>
         <v/>
       </c>
       <c r="F5" s="4">
-        <f>COUNTIFS(TC!$B$2:$B$52,A5,TC!$N$2:$N$52,"보류")</f>
+        <f>COUNTIFS(TC!$B$2:$B$51,A5,TC!$N$2:$N$51,"보류")</f>
         <v/>
       </c>
       <c r="G5" s="4">
-        <f>C5-D5-E5-F5-COUNTIFS(TC!$B$2:$B$52,A5,TC!$N$2:$N$52,"해당없음")</f>
+        <f>C5-D5-E5-F5-COUNTIFS(TC!$B$2:$B$51,A5,TC!$N$2:$N$51,"해당없음")</f>
         <v/>
       </c>
       <c r="H5" s="5">
@@ -1078,23 +1078,23 @@
         </is>
       </c>
       <c r="C6" s="4">
-        <f>COUNTIF(TC!$B$2:$B$52,A6)</f>
+        <f>COUNTIF(TC!$B$2:$B$51,A6)</f>
         <v/>
       </c>
       <c r="D6" s="4">
-        <f>COUNTIFS(TC!$B$2:$B$52,A6,TC!$N$2:$N$52,"통과")</f>
+        <f>COUNTIFS(TC!$B$2:$B$51,A6,TC!$N$2:$N$51,"통과")</f>
         <v/>
       </c>
       <c r="E6" s="4">
-        <f>COUNTIFS(TC!$B$2:$B$52,A6,TC!$N$2:$N$52,"실패")</f>
+        <f>COUNTIFS(TC!$B$2:$B$51,A6,TC!$N$2:$N$51,"실패")</f>
         <v/>
       </c>
       <c r="F6" s="4">
-        <f>COUNTIFS(TC!$B$2:$B$52,A6,TC!$N$2:$N$52,"보류")</f>
+        <f>COUNTIFS(TC!$B$2:$B$51,A6,TC!$N$2:$N$51,"보류")</f>
         <v/>
       </c>
       <c r="G6" s="4">
-        <f>C6-D6-E6-F6-COUNTIFS(TC!$B$2:$B$52,A6,TC!$N$2:$N$52,"해당없음")</f>
+        <f>C6-D6-E6-F6-COUNTIFS(TC!$B$2:$B$51,A6,TC!$N$2:$N$51,"해당없음")</f>
         <v/>
       </c>
       <c r="H6" s="5">
@@ -1114,23 +1114,23 @@
         </is>
       </c>
       <c r="C7" s="4">
-        <f>COUNTIF(TC!$B$2:$B$52,A7)</f>
+        <f>COUNTIF(TC!$B$2:$B$51,A7)</f>
         <v/>
       </c>
       <c r="D7" s="4">
-        <f>COUNTIFS(TC!$B$2:$B$52,A7,TC!$N$2:$N$52,"통과")</f>
+        <f>COUNTIFS(TC!$B$2:$B$51,A7,TC!$N$2:$N$51,"통과")</f>
         <v/>
       </c>
       <c r="E7" s="4">
-        <f>COUNTIFS(TC!$B$2:$B$52,A7,TC!$N$2:$N$52,"실패")</f>
+        <f>COUNTIFS(TC!$B$2:$B$51,A7,TC!$N$2:$N$51,"실패")</f>
         <v/>
       </c>
       <c r="F7" s="4">
-        <f>COUNTIFS(TC!$B$2:$B$52,A7,TC!$N$2:$N$52,"보류")</f>
+        <f>COUNTIFS(TC!$B$2:$B$51,A7,TC!$N$2:$N$51,"보류")</f>
         <v/>
       </c>
       <c r="G7" s="4">
-        <f>C7-D7-E7-F7-COUNTIFS(TC!$B$2:$B$52,A7,TC!$N$2:$N$52,"해당없음")</f>
+        <f>C7-D7-E7-F7-COUNTIFS(TC!$B$2:$B$51,A7,TC!$N$2:$N$51,"해당없음")</f>
         <v/>
       </c>
       <c r="H7" s="5">
@@ -1224,7 +1224,7 @@
     </row>
     <row r="15">
       <c r="A15" s="10">
-        <f>COUNTIF(결함!$A$2:$A$60,"BUG-*")</f>
+        <f>COUNTIF(결함!$A$2:$A$60,"WEB-*")</f>
         <v/>
       </c>
       <c r="B15" s="10">
@@ -1312,7 +1312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T52"/>
+  <dimension ref="A1:T51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="D2" s="10" t="inlineStr">
         <is>
-          <t>체험 홈</t>
+          <t>자동 팝업</t>
         </is>
       </c>
       <c r="E2" s="10" t="inlineStr">
@@ -1472,38 +1472,42 @@
       </c>
       <c r="G2" s="10" t="inlineStr">
         <is>
-          <t>dev 빌드 설치 · 로그인</t>
+          <t>리포트를 한 번도 열지 않은 상태</t>
         </is>
       </c>
       <c r="H2" s="10" t="inlineStr">
         <is>
-          <t>체험 홈으로 들어간다</t>
+          <t>로그인 직후 홈 진입</t>
         </is>
       </c>
       <c r="I2" s="10" t="inlineStr">
         <is>
-          <t>상단에 3기 리포트 카드(전용 배너 이미지)가 보인다</t>
+          <t>리포트가 자동으로 1회 열리고 표지(SC-RP-01)부터 보인다</t>
         </is>
       </c>
       <c r="J2" s="10" t="inlineStr">
         <is>
-          <t>B-01 · IA-R-08</t>
-        </is>
-      </c>
-      <c r="K2" s="10" t="n"/>
+          <t>IA-R-01</t>
+        </is>
+      </c>
+      <c r="K2" s="14" t="inlineStr">
+        <is>
+          <t>cmp_01.png</t>
+        </is>
+      </c>
       <c r="L2" s="4" t="n"/>
       <c r="M2" s="10" t="n"/>
-      <c r="N2" s="14" t="inlineStr">
+      <c r="N2" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="O2" s="14" t="n"/>
-      <c r="P2" s="15" t="n"/>
-      <c r="Q2" s="14" t="n"/>
-      <c r="R2" s="15" t="n"/>
-      <c r="S2" s="14" t="n"/>
-      <c r="T2" s="14" t="n"/>
+      <c r="O2" s="15" t="n"/>
+      <c r="P2" s="16" t="n"/>
+      <c r="Q2" s="15" t="n"/>
+      <c r="R2" s="16" t="n"/>
+      <c r="S2" s="15" t="n"/>
+      <c r="T2" s="15" t="n"/>
     </row>
     <row r="3" ht="48" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
@@ -1513,7 +1517,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
@@ -1538,17 +1542,17 @@
       </c>
       <c r="G3" s="10" t="inlineStr">
         <is>
-          <t>리포트를 한 번도 열지 않은 상태</t>
+          <t>E-01 이후</t>
         </is>
       </c>
       <c r="H3" s="10" t="inlineStr">
         <is>
-          <t>로그인 직후 홈 진입</t>
+          <t>리포트를 닫고 앱을 껐다 다시 연다</t>
         </is>
       </c>
       <c r="I3" s="10" t="inlineStr">
         <is>
-          <t>리포트가 자동으로 1회 열리고 표지(SC-RP-01)부터 보인다</t>
+          <t>자동 팝업이 다시 뜨지 않는다 · 홈 카드는 그대로 있다</t>
         </is>
       </c>
       <c r="J3" s="10" t="inlineStr">
@@ -1556,24 +1560,20 @@
           <t>IA-R-01</t>
         </is>
       </c>
-      <c r="K3" s="16" t="inlineStr">
-        <is>
-          <t>cmp_01.png</t>
-        </is>
-      </c>
+      <c r="K3" s="10" t="n"/>
       <c r="L3" s="4" t="n"/>
       <c r="M3" s="10" t="n"/>
-      <c r="N3" s="14" t="inlineStr">
+      <c r="N3" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="O3" s="14" t="n"/>
-      <c r="P3" s="15" t="n"/>
-      <c r="Q3" s="14" t="n"/>
-      <c r="R3" s="15" t="n"/>
-      <c r="S3" s="14" t="n"/>
-      <c r="T3" s="14" t="n"/>
+      <c r="O3" s="15" t="n"/>
+      <c r="P3" s="16" t="n"/>
+      <c r="Q3" s="15" t="n"/>
+      <c r="R3" s="16" t="n"/>
+      <c r="S3" s="15" t="n"/>
+      <c r="T3" s="15" t="n"/>
     </row>
     <row r="4" ht="48" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>자동 팝업</t>
+          <t>홈 카드</t>
         </is>
       </c>
       <c r="E4" s="10" t="inlineStr">
@@ -1608,38 +1608,38 @@
       </c>
       <c r="G4" s="10" t="inlineStr">
         <is>
-          <t>E-02 이후</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
-          <t>리포트를 닫고 앱을 껐다 다시 연다</t>
+          <t>홈 카드를 누른다</t>
         </is>
       </c>
       <c r="I4" s="10" t="inlineStr">
         <is>
-          <t>자동 팝업이 다시 뜨지 않는다 · 홈 카드는 그대로 있다</t>
+          <t>리포트가 표지부터 열린다</t>
         </is>
       </c>
       <c r="J4" s="10" t="inlineStr">
         <is>
-          <t>IA-R-01</t>
+          <t>IA-R-03</t>
         </is>
       </c>
       <c r="K4" s="10" t="n"/>
       <c r="L4" s="4" t="n"/>
       <c r="M4" s="10" t="n"/>
-      <c r="N4" s="14" t="inlineStr">
+      <c r="N4" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="O4" s="14" t="n"/>
-      <c r="P4" s="15" t="n"/>
-      <c r="Q4" s="14" t="n"/>
-      <c r="R4" s="15" t="n"/>
-      <c r="S4" s="14" t="n"/>
-      <c r="T4" s="14" t="n"/>
+      <c r="O4" s="15" t="n"/>
+      <c r="P4" s="16" t="n"/>
+      <c r="Q4" s="15" t="n"/>
+      <c r="R4" s="16" t="n"/>
+      <c r="S4" s="15" t="n"/>
+      <c r="T4" s="15" t="n"/>
     </row>
     <row r="5" ht="48" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>홈 카드</t>
+          <t>진행 내역</t>
         </is>
       </c>
       <c r="E5" s="10" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10/20 제출 빌드</t>
         </is>
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>홈 카드를 누른다</t>
+          <t>내 정보 &gt; 프로그램 진행 내역 &gt; 3기 항목을 누른다</t>
         </is>
       </c>
       <c r="I5" s="10" t="inlineStr">
@@ -1689,23 +1689,23 @@
       </c>
       <c r="J5" s="10" t="inlineStr">
         <is>
-          <t>IA-R-03</t>
+          <t>F4 · IA-R-07</t>
         </is>
       </c>
       <c r="K5" s="10" t="n"/>
       <c r="L5" s="4" t="n"/>
       <c r="M5" s="10" t="n"/>
-      <c r="N5" s="14" t="inlineStr">
+      <c r="N5" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="O5" s="14" t="n"/>
-      <c r="P5" s="15" t="n"/>
-      <c r="Q5" s="14" t="n"/>
-      <c r="R5" s="15" t="n"/>
-      <c r="S5" s="14" t="n"/>
-      <c r="T5" s="14" t="n"/>
+      <c r="O5" s="15" t="n"/>
+      <c r="P5" s="16" t="n"/>
+      <c r="Q5" s="15" t="n"/>
+      <c r="R5" s="16" t="n"/>
+      <c r="S5" s="15" t="n"/>
+      <c r="T5" s="15" t="n"/>
     </row>
     <row r="6" ht="48" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>진행 내역</t>
+          <t>체험 홈</t>
         </is>
       </c>
       <c r="E6" s="10" t="inlineStr">
         <is>
-          <t>①</t>
+          <t>⑤</t>
         </is>
       </c>
       <c r="F6" s="10" t="inlineStr">
@@ -1740,38 +1740,38 @@
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>10/20 제출 빌드</t>
+          <t>다른 프로그램 진행 중</t>
         </is>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>내 정보 &gt; 프로그램 진행 내역 &gt; 3기 항목을 누른다</t>
+          <t>홈으로 들어간다</t>
         </is>
       </c>
       <c r="I6" s="10" t="inlineStr">
         <is>
-          <t>리포트가 표지부터 열린다</t>
+          <t>리포트 카드가 없다</t>
         </is>
       </c>
       <c r="J6" s="10" t="inlineStr">
         <is>
-          <t>F4 · IA-R-07</t>
+          <t>IA-R-08</t>
         </is>
       </c>
       <c r="K6" s="10" t="n"/>
       <c r="L6" s="4" t="n"/>
       <c r="M6" s="10" t="n"/>
-      <c r="N6" s="14" t="inlineStr">
+      <c r="N6" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="O6" s="14" t="n"/>
-      <c r="P6" s="15" t="n"/>
-      <c r="Q6" s="14" t="n"/>
-      <c r="R6" s="15" t="n"/>
-      <c r="S6" s="14" t="n"/>
-      <c r="T6" s="14" t="n"/>
+      <c r="O6" s="15" t="n"/>
+      <c r="P6" s="16" t="n"/>
+      <c r="Q6" s="15" t="n"/>
+      <c r="R6" s="16" t="n"/>
+      <c r="S6" s="15" t="n"/>
+      <c r="T6" s="15" t="n"/>
     </row>
     <row r="7" ht="48" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>체험 홈</t>
+          <t>공개 전</t>
         </is>
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>⑤</t>
+          <t>⑥</t>
         </is>
       </c>
       <c r="F7" s="10" t="inlineStr">
@@ -1806,38 +1806,38 @@
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
-          <t>다른 프로그램 진행 중</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>홈으로 들어간다</t>
+          <t>홈 확인 후 리포트 링크로 직접 연다</t>
         </is>
       </c>
       <c r="I7" s="10" t="inlineStr">
         <is>
-          <t>리포트 카드가 없다</t>
+          <t>카드 없음 · "아직 볼 수 없어요" 안내</t>
         </is>
       </c>
       <c r="J7" s="10" t="inlineStr">
         <is>
-          <t>IA-R-08</t>
+          <t>P09</t>
         </is>
       </c>
       <c r="K7" s="10" t="n"/>
       <c r="L7" s="4" t="n"/>
       <c r="M7" s="10" t="n"/>
-      <c r="N7" s="14" t="inlineStr">
+      <c r="N7" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="O7" s="14" t="n"/>
-      <c r="P7" s="15" t="n"/>
-      <c r="Q7" s="14" t="n"/>
-      <c r="R7" s="15" t="n"/>
-      <c r="S7" s="14" t="n"/>
-      <c r="T7" s="14" t="n"/>
+      <c r="O7" s="15" t="n"/>
+      <c r="P7" s="16" t="n"/>
+      <c r="Q7" s="15" t="n"/>
+      <c r="R7" s="16" t="n"/>
+      <c r="S7" s="15" t="n"/>
+      <c r="T7" s="15" t="n"/>
     </row>
     <row r="8" ht="48" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
@@ -1857,17 +1857,17 @@
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>공개 전</t>
+          <t>비대상 P20</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>⑥</t>
+          <t>⑦</t>
         </is>
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
-          <t>앱</t>
+          <t>앱 · 웹</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr">
@@ -1877,33 +1877,45 @@
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>홈 확인 후 리포트 링크로 직접 연다</t>
+          <t>리포트 링크로 직접 연다</t>
         </is>
       </c>
       <c r="I8" s="10" t="inlineStr">
         <is>
-          <t>카드 없음 · "아직 볼 수 없어요" 안내</t>
+          <t>제목 없이 본문 "2026년 인천 남동구 보건소 두뇌운동 치매 예방 교실 3기 참여자에게만 제공되는 리포트입니다. 자세한 문의는 인천 남동구 보건소로 문의 부탁드립니다." + [홈으로 돌아가기]</t>
         </is>
       </c>
       <c r="J8" s="10" t="inlineStr">
         <is>
-          <t>P09</t>
-        </is>
-      </c>
-      <c r="K8" s="10" t="n"/>
-      <c r="L8" s="4" t="n"/>
-      <c r="M8" s="10" t="n"/>
-      <c r="N8" s="14" t="inlineStr">
+          <t>P20 · gate-nontarget</t>
+        </is>
+      </c>
+      <c r="K8" s="14" t="inlineStr">
+        <is>
+          <t>cmp_sys05.png</t>
+        </is>
+      </c>
+      <c r="L8" s="17" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="M8" s="18" t="inlineStr">
+        <is>
+          <t>문구는 일치 · 아이콘 · 버튼 배치 다름 → WEB-7</t>
+        </is>
+      </c>
+      <c r="N8" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="O8" s="14" t="n"/>
-      <c r="P8" s="15" t="n"/>
-      <c r="Q8" s="14" t="n"/>
-      <c r="R8" s="15" t="n"/>
-      <c r="S8" s="14" t="n"/>
-      <c r="T8" s="14" t="n"/>
+      <c r="O8" s="15" t="n"/>
+      <c r="P8" s="16" t="n"/>
+      <c r="Q8" s="15" t="n"/>
+      <c r="R8" s="16" t="n"/>
+      <c r="S8" s="15" t="n"/>
+      <c r="T8" s="15" t="n"/>
     </row>
     <row r="9" ht="48" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
@@ -1923,65 +1935,53 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>비대상 P20</t>
+          <t>강제 업데이트</t>
         </is>
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>⑦</t>
+          <t>아무 계정</t>
         </is>
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
-          <t>앱 · 웹</t>
+          <t>앱</t>
         </is>
       </c>
       <c r="G9" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>앱 4.1.0 이하 설치</t>
         </is>
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>리포트 링크로 직접 연다</t>
+          <t>앱을 연다</t>
         </is>
       </c>
       <c r="I9" s="10" t="inlineStr">
         <is>
-          <t>제목 없이 본문 "2026년 인천 남동구 보건소 두뇌운동 치매 예방 교실 3기 참여자에게만 제공되는 리포트입니다. 자세한 문의는 인천 남동구 보건소로 문의 부탁드립니다." + [홈으로 돌아가기]</t>
+          <t>4.1.1 미만은 업데이트 안내 · 앱 사용 차단</t>
         </is>
       </c>
       <c r="J9" s="10" t="inlineStr">
         <is>
-          <t>P20 · gate-nontarget</t>
-        </is>
-      </c>
-      <c r="K9" s="16" t="inlineStr">
-        <is>
-          <t>cmp_sys05.png</t>
-        </is>
-      </c>
-      <c r="L9" s="17" t="inlineStr">
-        <is>
-          <t>실패</t>
-        </is>
-      </c>
-      <c r="M9" s="18" t="inlineStr">
-        <is>
-          <t>문구는 일치 · 아이콘 · 버튼 배치 다름 → BUG-07</t>
-        </is>
-      </c>
-      <c r="N9" s="14" t="inlineStr">
+          <t>K-15 · IA-R-13 · 개발 D-5</t>
+        </is>
+      </c>
+      <c r="K9" s="10" t="n"/>
+      <c r="L9" s="4" t="n"/>
+      <c r="M9" s="10" t="n"/>
+      <c r="N9" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="O9" s="14" t="n"/>
-      <c r="P9" s="15" t="n"/>
-      <c r="Q9" s="14" t="n"/>
-      <c r="R9" s="15" t="n"/>
-      <c r="S9" s="14" t="n"/>
-      <c r="T9" s="14" t="n"/>
+      <c r="O9" s="15" t="n"/>
+      <c r="P9" s="16" t="n"/>
+      <c r="Q9" s="15" t="n"/>
+      <c r="R9" s="16" t="n"/>
+      <c r="S9" s="15" t="n"/>
+      <c r="T9" s="15" t="n"/>
     </row>
     <row r="10" ht="48" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -2001,12 +2001,12 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>강제 업데이트</t>
+          <t>네트워크 오류</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>아무 계정</t>
+          <t>①</t>
         </is>
       </c>
       <c r="F10" s="10" t="inlineStr">
@@ -2016,114 +2016,126 @@
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>앱 4.1.0 이하 설치</t>
+          <t>비행기 모드</t>
         </is>
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>앱을 연다</t>
+          <t>홈 카드를 누른다</t>
         </is>
       </c>
       <c r="I10" s="10" t="inlineStr">
         <is>
-          <t>4.1.1 미만은 업데이트 안내 · 앱 사용 차단</t>
+          <t>전체 화면 오류 + [다시 시도] · "참여자에게만" 문구가 나오지 않는다</t>
         </is>
       </c>
       <c r="J10" s="10" t="inlineStr">
         <is>
-          <t>K-15 · IA-R-13 · 개발 D-5</t>
+          <t>P18</t>
         </is>
       </c>
       <c r="K10" s="10" t="n"/>
       <c r="L10" s="4" t="n"/>
       <c r="M10" s="10" t="n"/>
-      <c r="N10" s="14" t="inlineStr">
+      <c r="N10" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="O10" s="14" t="n"/>
-      <c r="P10" s="15" t="n"/>
-      <c r="Q10" s="14" t="n"/>
-      <c r="R10" s="15" t="n"/>
-      <c r="S10" s="14" t="n"/>
-      <c r="T10" s="14" t="n"/>
+      <c r="O10" s="15" t="n"/>
+      <c r="P10" s="16" t="n"/>
+      <c r="Q10" s="15" t="n"/>
+      <c r="R10" s="16" t="n"/>
+      <c r="S10" s="15" t="n"/>
+      <c r="T10" s="15" t="n"/>
     </row>
     <row r="11" ht="48" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>E-10</t>
+          <t>S-01</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>1 진입</t>
+          <t>2 8개 섹션</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>네트워크 오류</t>
+          <t>01 표지</t>
         </is>
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>①</t>
+          <t>① ② ③ ④</t>
         </is>
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
-          <t>앱</t>
+          <t>앱 · 웹</t>
         </is>
       </c>
       <c r="G11" s="10" t="inlineStr">
         <is>
-          <t>비행기 모드</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>홈 카드를 누른다</t>
+          <t>표지를 본다</t>
         </is>
       </c>
       <c r="I11" s="10" t="inlineStr">
         <is>
-          <t>전체 화면 오류 + [다시 시도] · "참여자에게만" 문구가 나오지 않는다</t>
+          <t>피그마 목업처럼 배지 "2026 인천 남동구 보건소 치매 예방 3기" · "{마스킹 이름}님," · 기간 · 참여일 · 왼쪽 정렬 · 메달 그래픽</t>
         </is>
       </c>
       <c r="J11" s="10" t="inlineStr">
         <is>
-          <t>P18</t>
-        </is>
-      </c>
-      <c r="K11" s="10" t="n"/>
-      <c r="L11" s="4" t="n"/>
-      <c r="M11" s="10" t="n"/>
-      <c r="N11" s="14" t="inlineStr">
+          <t>S1-01~04 · 목업 1097:791</t>
+        </is>
+      </c>
+      <c r="K11" s="14" t="inlineStr">
+        <is>
+          <t>cmp_01.png</t>
+        </is>
+      </c>
+      <c r="L11" s="17" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="M11" s="18" t="inlineStr">
+        <is>
+          <t>문구 일치 · 가운데 정렬 · 메달 없음 → WEB-3</t>
+        </is>
+      </c>
+      <c r="N11" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="O11" s="14" t="n"/>
-      <c r="P11" s="15" t="n"/>
-      <c r="Q11" s="14" t="n"/>
-      <c r="R11" s="15" t="n"/>
-      <c r="S11" s="14" t="n"/>
-      <c r="T11" s="14" t="n"/>
+      <c r="O11" s="15" t="n"/>
+      <c r="P11" s="16" t="n"/>
+      <c r="Q11" s="15" t="n"/>
+      <c r="R11" s="16" t="n"/>
+      <c r="S11" s="15" t="n"/>
+      <c r="T11" s="15" t="n"/>
     </row>
     <row r="12" ht="48" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>S-01</t>
+          <t>S-02</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
@@ -2133,42 +2145,42 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>01 표지</t>
+          <t>02 숫자로 먼저</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
-          <t>② ③ ④</t>
+          <t>②</t>
         </is>
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
-          <t>앱 · 웹</t>
+          <t>앱</t>
         </is>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>§데이터 요청 5번 원값 수령</t>
         </is>
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>표지를 본다</t>
+          <t>화면 숫자와 원값을 대조한다</t>
         </is>
       </c>
       <c r="I12" s="10" t="inlineStr">
         <is>
-          <t>피그마 목업처럼 배지 "2026 인천 남동구 보건소 치매 예방 3기" · "{마스킹 이름}님," · 기간 · 참여일 · 왼쪽 정렬 · 메달 그래픽</t>
+          <t>뇌 점수 시작→종료 · 함께한 날 · 참여율 · 게임 횟수 · 마음 기록이 원값과 같다</t>
         </is>
       </c>
       <c r="J12" s="10" t="inlineStr">
         <is>
-          <t>S1-01~04 · 목업 1097:791</t>
-        </is>
-      </c>
-      <c r="K12" s="16" t="inlineStr">
-        <is>
-          <t>cmp_01.png</t>
+          <t>S2 · F-01~F-04 · F-08</t>
+        </is>
+      </c>
+      <c r="K12" s="14" t="inlineStr">
+        <is>
+          <t>cmp_02.png</t>
         </is>
       </c>
       <c r="L12" s="17" t="inlineStr">
@@ -2178,30 +2190,30 @@
       </c>
       <c r="M12" s="18" t="inlineStr">
         <is>
-          <t>문구 일치 · 가운데 정렬 · 메달 없음 → BUG-03</t>
-        </is>
-      </c>
-      <c r="N12" s="14" t="inlineStr">
+          <t>숫자 정상 · 꺾은선이 거의 평평 → WEB-4</t>
+        </is>
+      </c>
+      <c r="N12" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="O12" s="14" t="n"/>
-      <c r="P12" s="15" t="n"/>
-      <c r="Q12" s="14" t="n"/>
-      <c r="R12" s="15" t="n"/>
-      <c r="S12" s="14" t="n"/>
-      <c r="T12" s="14" t="n"/>
+      <c r="O12" s="15" t="n"/>
+      <c r="P12" s="16" t="n"/>
+      <c r="Q12" s="15" t="n"/>
+      <c r="R12" s="16" t="n"/>
+      <c r="S12" s="15" t="n"/>
+      <c r="T12" s="15" t="n"/>
     </row>
     <row r="13" ht="48" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>S-02</t>
+          <t>S-03</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
@@ -2211,7 +2223,7 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>02 숫자로 먼저</t>
+          <t>03 집중의 리듬</t>
         </is>
       </c>
       <c r="E13" s="10" t="inlineStr">
@@ -2221,32 +2233,32 @@
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
-          <t>앱</t>
+          <t>앱 · 웹</t>
         </is>
       </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
-          <t>§데이터 요청 5번 원값 수령</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>화면 숫자와 원값을 대조한다</t>
+          <t>요일 · 시간 · 막대를 본다</t>
         </is>
       </c>
       <c r="I13" s="10" t="inlineStr">
         <is>
-          <t>뇌 점수 시작→종료 · 함께한 날 · 참여율 · 게임 횟수 · 마음 기록이 원값과 같다</t>
+          <t>월~금만 · "프로그램 운영일은 평일(월–금)입니다"</t>
         </is>
       </c>
       <c r="J13" s="10" t="inlineStr">
         <is>
-          <t>S2 · F-01~F-04 · F-08</t>
-        </is>
-      </c>
-      <c r="K13" s="16" t="inlineStr">
-        <is>
-          <t>cmp_02.png</t>
+          <t>S3 · F-07</t>
+        </is>
+      </c>
+      <c r="K13" s="14" t="inlineStr">
+        <is>
+          <t>cmp_03.png</t>
         </is>
       </c>
       <c r="L13" s="17" t="inlineStr">
@@ -2256,25 +2268,25 @@
       </c>
       <c r="M13" s="18" t="inlineStr">
         <is>
-          <t>숫자 정상 · 꺾은선이 거의 평평 → BUG-04</t>
-        </is>
-      </c>
-      <c r="N13" s="14" t="inlineStr">
+          <t>88% 강조색 · 멘트 카드 다름 → WEB-5</t>
+        </is>
+      </c>
+      <c r="N13" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="O13" s="14" t="n"/>
-      <c r="P13" s="15" t="n"/>
-      <c r="Q13" s="14" t="n"/>
-      <c r="R13" s="15" t="n"/>
-      <c r="S13" s="14" t="n"/>
-      <c r="T13" s="14" t="n"/>
+      <c r="O13" s="15" t="n"/>
+      <c r="P13" s="16" t="n"/>
+      <c r="Q13" s="15" t="n"/>
+      <c r="R13" s="16" t="n"/>
+      <c r="S13" s="15" t="n"/>
+      <c r="T13" s="15" t="n"/>
     </row>
     <row r="14" ht="48" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>S-03</t>
+          <t>S-04</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -2289,7 +2301,7 @@
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>03 집중의 리듬</t>
+          <t>04 게임</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
@@ -2309,55 +2321,55 @@
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>요일 · 시간 · 막대를 본다</t>
+          <t>최다 게임 · 횟수 · 종수 · TOP3</t>
         </is>
       </c>
       <c r="I14" s="10" t="inlineStr">
         <is>
-          <t>월~금만 · "프로그램 운영일은 평일(월–금)입니다"</t>
+          <t>"해본 게임 N종 / 전체 16종 중" · TOP3 정렬</t>
         </is>
       </c>
       <c r="J14" s="10" t="inlineStr">
         <is>
-          <t>S3 · F-07</t>
-        </is>
-      </c>
-      <c r="K14" s="16" t="inlineStr">
-        <is>
-          <t>cmp_03.png</t>
+          <t>S4 · F-03b · F-05</t>
+        </is>
+      </c>
+      <c r="K14" s="14" t="inlineStr">
+        <is>
+          <t>cmp_04.png</t>
         </is>
       </c>
       <c r="L14" s="17" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>통과</t>
         </is>
       </c>
       <c r="M14" s="18" t="inlineStr">
         <is>
-          <t>88% 강조색 · 멘트 카드 다름 → BUG-05</t>
-        </is>
-      </c>
-      <c r="N14" s="14" t="inlineStr">
+          <t>게임명 줄바꿈만 다름 → WEB-9 (P3)</t>
+        </is>
+      </c>
+      <c r="N14" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="O14" s="14" t="n"/>
-      <c r="P14" s="15" t="n"/>
-      <c r="Q14" s="14" t="n"/>
-      <c r="R14" s="15" t="n"/>
-      <c r="S14" s="14" t="n"/>
-      <c r="T14" s="14" t="n"/>
+      <c r="O14" s="15" t="n"/>
+      <c r="P14" s="16" t="n"/>
+      <c r="Q14" s="15" t="n"/>
+      <c r="R14" s="16" t="n"/>
+      <c r="S14" s="15" t="n"/>
+      <c r="T14" s="15" t="n"/>
     </row>
     <row r="15" ht="48" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>S-04</t>
+          <t>S-05</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
@@ -2367,12 +2379,12 @@
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>04 게임</t>
+          <t>04B 랭킹</t>
         </is>
       </c>
       <c r="E15" s="10" t="inlineStr">
         <is>
-          <t>②</t>
+          <t>② ①</t>
         </is>
       </c>
       <c r="F15" s="10" t="inlineStr">
@@ -2387,22 +2399,22 @@
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>최다 게임 · 횟수 · 종수 · TOP3</t>
+          <t>순위 · 상위 % 타일 · 배지 · 하단 문구</t>
         </is>
       </c>
       <c r="I15" s="10" t="inlineStr">
         <is>
-          <t>"해본 게임 N종 / 전체 16종 중" · TOP3 정렬</t>
+          <t>타일 % = 배지 % · 1~3위면 내 행 없음 · "아래로 {823-순위}명이 더 함께했어요" · 최하위면 문구 없음</t>
         </is>
       </c>
       <c r="J15" s="10" t="inlineStr">
         <is>
-          <t>S4 · F-03b · F-05</t>
-        </is>
-      </c>
-      <c r="K15" s="16" t="inlineStr">
-        <is>
-          <t>cmp_04.png</t>
+          <t>S4B-04~08 · F-06 · F-06b · P08</t>
+        </is>
+      </c>
+      <c r="K15" s="14" t="inlineStr">
+        <is>
+          <t>cmp_04B.png</t>
         </is>
       </c>
       <c r="L15" s="17" t="inlineStr">
@@ -2412,30 +2424,30 @@
       </c>
       <c r="M15" s="18" t="inlineStr">
         <is>
-          <t>게임명 줄바꿈만 다름 → BUG-09 (P3)</t>
-        </is>
-      </c>
-      <c r="N15" s="14" t="inlineStr">
+          <t>12위 · 상위 2% · 811명 · 목업과 같음</t>
+        </is>
+      </c>
+      <c r="N15" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="O15" s="14" t="n"/>
-      <c r="P15" s="15" t="n"/>
-      <c r="Q15" s="14" t="n"/>
-      <c r="R15" s="15" t="n"/>
-      <c r="S15" s="14" t="n"/>
-      <c r="T15" s="14" t="n"/>
+      <c r="O15" s="15" t="n"/>
+      <c r="P15" s="16" t="n"/>
+      <c r="Q15" s="15" t="n"/>
+      <c r="R15" s="16" t="n"/>
+      <c r="S15" s="15" t="n"/>
+      <c r="T15" s="15" t="n"/>
     </row>
     <row r="16" ht="48" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>S-05</t>
+          <t>S-06</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
@@ -2445,12 +2457,12 @@
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>04B 랭킹</t>
+          <t>05 마음</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>② ①</t>
+          <t>② + 측정 1회 · 0회 계정</t>
         </is>
       </c>
       <c r="F16" s="10" t="inlineStr">
@@ -2460,27 +2472,27 @@
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>측정 1회 · 0회 계정은 개발에 요청</t>
         </is>
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>순위 · 상위 % 타일 · 배지 · 하단 문구</t>
+          <t>게이지 · 상태 · 안내박스</t>
         </is>
       </c>
       <c r="I16" s="10" t="inlineStr">
         <is>
-          <t>타일 % = 배지 % · 1~3위면 내 행 없음 · "아래로 {823-순위}명이 더 함께했어요" · 최하위면 문구 없음</t>
+          <t>종료 점수 구간으로 판정 · 1회면 고스트 없음 · 0회면 "검사 기록이 없습니다."</t>
         </is>
       </c>
       <c r="J16" s="10" t="inlineStr">
         <is>
-          <t>S4B-04~08 · F-06 · F-06b · P08</t>
-        </is>
-      </c>
-      <c r="K16" s="16" t="inlineStr">
-        <is>
-          <t>cmp_04B.png</t>
+          <t>S5 · P03 · P04</t>
+        </is>
+      </c>
+      <c r="K16" s="14" t="inlineStr">
+        <is>
+          <t>cmp_05.png</t>
         </is>
       </c>
       <c r="L16" s="17" t="inlineStr">
@@ -2490,25 +2502,25 @@
       </c>
       <c r="M16" s="18" t="inlineStr">
         <is>
-          <t>12위 · 상위 2% · 811명 · 목업과 같음</t>
-        </is>
-      </c>
-      <c r="N16" s="14" t="inlineStr">
+          <t>7→3점 양호 · 라벨 위치만 다름 → WEB-9 (P3)</t>
+        </is>
+      </c>
+      <c r="N16" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="O16" s="14" t="n"/>
-      <c r="P16" s="15" t="n"/>
-      <c r="Q16" s="14" t="n"/>
-      <c r="R16" s="15" t="n"/>
-      <c r="S16" s="14" t="n"/>
-      <c r="T16" s="14" t="n"/>
+      <c r="O16" s="15" t="n"/>
+      <c r="P16" s="16" t="n"/>
+      <c r="Q16" s="15" t="n"/>
+      <c r="R16" s="16" t="n"/>
+      <c r="S16" s="15" t="n"/>
+      <c r="T16" s="15" t="n"/>
     </row>
     <row r="17" ht="48" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>S-06</t>
+          <t>S-07</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -2523,12 +2535,12 @@
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>05 마음</t>
+          <t>06 걸음</t>
         </is>
       </c>
       <c r="E17" s="10" t="inlineStr">
         <is>
-          <t>② + 측정 1회 · 0회 계정</t>
+          <t>② + 미연동 계정</t>
         </is>
       </c>
       <c r="F17" s="10" t="inlineStr">
@@ -2538,27 +2550,27 @@
       </c>
       <c r="G17" s="10" t="inlineStr">
         <is>
-          <t>측정 1회 · 0회 계정은 개발에 요청</t>
+          <t>미연동 계정은 개발에 요청</t>
         </is>
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>게이지 · 상태 · 안내박스</t>
+          <t>걸음 · 환산 · 칼로리</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr">
         <is>
-          <t>종료 점수 구간으로 판정 · 1회면 고스트 없음 · 0회면 "검사 기록이 없습니다."</t>
+          <t>미연동이면 섹션 자체 없음 · 7km 미만이면 환산 카드 없음 · N=1이면 회차 없이 "걸었어요"</t>
         </is>
       </c>
       <c r="J17" s="10" t="inlineStr">
         <is>
-          <t>S5 · P03 · P04</t>
-        </is>
-      </c>
-      <c r="K17" s="16" t="inlineStr">
-        <is>
-          <t>cmp_05.png</t>
+          <t>S6 · P16 · P17</t>
+        </is>
+      </c>
+      <c r="K17" s="14" t="inlineStr">
+        <is>
+          <t>cmp_06.png</t>
         </is>
       </c>
       <c r="L17" s="17" t="inlineStr">
@@ -2568,25 +2580,25 @@
       </c>
       <c r="M17" s="18" t="inlineStr">
         <is>
-          <t>7→3점 양호 · 라벨 위치만 다름 → BUG-09 (P3)</t>
-        </is>
-      </c>
-      <c r="N17" s="14" t="inlineStr">
+          <t>목업과 같음</t>
+        </is>
+      </c>
+      <c r="N17" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="O17" s="14" t="n"/>
-      <c r="P17" s="15" t="n"/>
-      <c r="Q17" s="14" t="n"/>
-      <c r="R17" s="15" t="n"/>
-      <c r="S17" s="14" t="n"/>
-      <c r="T17" s="14" t="n"/>
+      <c r="O17" s="15" t="n"/>
+      <c r="P17" s="16" t="n"/>
+      <c r="Q17" s="15" t="n"/>
+      <c r="R17" s="16" t="n"/>
+      <c r="S17" s="15" t="n"/>
+      <c r="T17" s="15" t="n"/>
     </row>
     <row r="18" ht="48" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>S-07</t>
+          <t>S-08</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -2601,75 +2613,75 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>06 걸음</t>
+          <t>스크롤 힌트</t>
         </is>
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
-          <t>② + 미연동 계정</t>
+          <t>②</t>
         </is>
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
-          <t>앱 · 웹</t>
+          <t>앱</t>
         </is>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>미연동 계정은 개발에 요청</t>
+          <t>작은 폰(iPhone SE급)</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>걸음 · 환산 · 칼로리</t>
+          <t>각 섹션에 들어간 직후와 스크롤한 뒤</t>
         </is>
       </c>
       <c r="I18" s="10" t="inlineStr">
         <is>
-          <t>미연동이면 섹션 자체 없음 · 7km 미만이면 환산 카드 없음 · N=1이면 회차 없이 "걸었어요"</t>
+          <t>진입 직후만 하단 고정 · 스크롤하면 풀림 · 본문을 계속 가리지 않음</t>
         </is>
       </c>
       <c r="J18" s="10" t="inlineStr">
         <is>
-          <t>S6 · P16 · P17</t>
-        </is>
-      </c>
-      <c r="K18" s="16" t="inlineStr">
-        <is>
-          <t>cmp_06.png</t>
+          <t>S1-05 · FE-05</t>
+        </is>
+      </c>
+      <c r="K18" s="14" t="inlineStr">
+        <is>
+          <t>cmp_05.png</t>
         </is>
       </c>
       <c r="L18" s="17" t="inlineStr">
         <is>
-          <t>통과</t>
+          <t>보류</t>
         </is>
       </c>
       <c r="M18" s="18" t="inlineStr">
         <is>
-          <t>목업과 같음</t>
-        </is>
-      </c>
-      <c r="N18" s="14" t="inlineStr">
+          <t>375×812 웹에서 진입 직후 힌트가 05 안내박스를 가림 → WEB-8 · 앱에서 확인</t>
+        </is>
+      </c>
+      <c r="N18" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="O18" s="14" t="n"/>
-      <c r="P18" s="15" t="n"/>
-      <c r="Q18" s="14" t="n"/>
-      <c r="R18" s="15" t="n"/>
-      <c r="S18" s="14" t="n"/>
-      <c r="T18" s="14" t="n"/>
+      <c r="O18" s="15" t="n"/>
+      <c r="P18" s="16" t="n"/>
+      <c r="Q18" s="15" t="n"/>
+      <c r="R18" s="16" t="n"/>
+      <c r="S18" s="15" t="n"/>
+      <c r="T18" s="15" t="n"/>
     </row>
     <row r="19" ht="48" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>S-08</t>
+          <t>S-09</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
@@ -2679,12 +2691,12 @@
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>스크롤 힌트</t>
+          <t>닫기 버튼</t>
         </is>
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>②</t>
+          <t>①</t>
         </is>
       </c>
       <c r="F19" s="10" t="inlineStr">
@@ -2694,60 +2706,48 @@
       </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
-          <t>작은 폰(iPhone SE급)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t>각 섹션에 들어간 직후와 스크롤한 뒤</t>
+          <t>아무 섹션에서 스크롤 중</t>
         </is>
       </c>
       <c r="I19" s="10" t="inlineStr">
         <is>
-          <t>진입 직후만 하단 고정 · 스크롤하면 풀림 · 본문을 계속 가리지 않음</t>
+          <t>✕가 항상 우상단에 고정</t>
         </is>
       </c>
       <c r="J19" s="10" t="inlineStr">
         <is>
-          <t>S1-05 · FE-05</t>
-        </is>
-      </c>
-      <c r="K19" s="16" t="inlineStr">
-        <is>
-          <t>cmp_05.png</t>
-        </is>
-      </c>
-      <c r="L19" s="17" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="M19" s="18" t="inlineStr">
-        <is>
-          <t>375×812 웹에서 진입 직후 힌트가 05 안내박스를 가림 → BUG-08 · 앱에서 확인</t>
-        </is>
-      </c>
-      <c r="N19" s="14" t="inlineStr">
+          <t>S1-06</t>
+        </is>
+      </c>
+      <c r="K19" s="10" t="n"/>
+      <c r="L19" s="4" t="n"/>
+      <c r="M19" s="10" t="n"/>
+      <c r="N19" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="O19" s="14" t="n"/>
-      <c r="P19" s="15" t="n"/>
-      <c r="Q19" s="14" t="n"/>
-      <c r="R19" s="15" t="n"/>
-      <c r="S19" s="14" t="n"/>
-      <c r="T19" s="14" t="n"/>
+      <c r="O19" s="15" t="n"/>
+      <c r="P19" s="16" t="n"/>
+      <c r="Q19" s="15" t="n"/>
+      <c r="R19" s="16" t="n"/>
+      <c r="S19" s="15" t="n"/>
+      <c r="T19" s="15" t="n"/>
     </row>
     <row r="20" ht="48" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>S-09</t>
+          <t>S-10</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
@@ -2757,12 +2757,12 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>닫기 버튼</t>
+          <t>큰 글씨</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>①</t>
+          <t>②</t>
         </is>
       </c>
       <c r="F20" s="10" t="inlineStr">
@@ -2772,63 +2772,63 @@
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OS 글자 크기 최대</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>아무 섹션에서 스크롤 중</t>
+          <t>전 섹션을 본다</t>
         </is>
       </c>
       <c r="I20" s="10" t="inlineStr">
         <is>
-          <t>✕가 항상 우상단에 고정</t>
+          <t>줄 넘침 · 겹침 · 잘림 없음</t>
         </is>
       </c>
       <c r="J20" s="10" t="inlineStr">
         <is>
-          <t>S1-06</t>
+          <t>IA-R-14 · D-28</t>
         </is>
       </c>
       <c r="K20" s="10" t="n"/>
       <c r="L20" s="4" t="n"/>
       <c r="M20" s="10" t="n"/>
-      <c r="N20" s="14" t="inlineStr">
+      <c r="N20" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="O20" s="14" t="n"/>
-      <c r="P20" s="15" t="n"/>
-      <c r="Q20" s="14" t="n"/>
-      <c r="R20" s="15" t="n"/>
-      <c r="S20" s="14" t="n"/>
-      <c r="T20" s="14" t="n"/>
+      <c r="O20" s="15" t="n"/>
+      <c r="P20" s="16" t="n"/>
+      <c r="Q20" s="15" t="n"/>
+      <c r="R20" s="16" t="n"/>
+      <c r="S20" s="15" t="n"/>
+      <c r="T20" s="15" t="n"/>
     </row>
     <row r="21" ht="48" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>S-10</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>2 8개 섹션</t>
+          <t>3 증서 저장</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>큰 글씨</t>
+          <t>07 A</t>
         </is>
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
-          <t>②</t>
+          <t>①</t>
         </is>
       </c>
       <c r="F21" s="10" t="inlineStr">
@@ -2838,43 +2838,51 @@
       </c>
       <c r="G21" s="10" t="inlineStr">
         <is>
-          <t>OS 글자 크기 최대</t>
+          <t>사진 권한 허용</t>
         </is>
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>전 섹션을 본다</t>
+          <t>수료증 저장하기</t>
         </is>
       </c>
       <c r="I21" s="10" t="inlineStr">
         <is>
-          <t>줄 넘침 · 겹침 · 잘림 없음</t>
+          <t>사진첩에 1:1 이미지 1장 · 숫자 0이나 빈칸 없음</t>
         </is>
       </c>
       <c r="J21" s="10" t="inlineStr">
         <is>
-          <t>IA-R-14 · D-28</t>
-        </is>
-      </c>
-      <c r="K21" s="10" t="n"/>
+          <t>S7-10 · §12</t>
+        </is>
+      </c>
+      <c r="K21" s="14" t="inlineStr">
+        <is>
+          <t>cmp_07A.png</t>
+        </is>
+      </c>
       <c r="L21" s="4" t="n"/>
-      <c r="M21" s="10" t="n"/>
-      <c r="N21" s="14" t="inlineStr">
+      <c r="M21" s="10" t="inlineStr">
+        <is>
+          <t>웹은 앱 브리지가 없어 저장 버튼 비활성(정상) · 테두리 장식 없음 → WEB-6</t>
+        </is>
+      </c>
+      <c r="N21" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="O21" s="14" t="n"/>
-      <c r="P21" s="15" t="n"/>
-      <c r="Q21" s="14" t="n"/>
-      <c r="R21" s="15" t="n"/>
-      <c r="S21" s="14" t="n"/>
-      <c r="T21" s="14" t="n"/>
+      <c r="O21" s="15" t="n"/>
+      <c r="P21" s="16" t="n"/>
+      <c r="Q21" s="15" t="n"/>
+      <c r="R21" s="16" t="n"/>
+      <c r="S21" s="15" t="n"/>
+      <c r="T21" s="15" t="n"/>
     </row>
     <row r="22" ht="48" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
@@ -2904,56 +2912,48 @@
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>사진 권한 허용</t>
+          <t>C-01 이후</t>
         </is>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>수료증 저장하기</t>
+          <t>파일명 · 형식 확인</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr">
         <is>
-          <t>사진첩에 1:1 이미지 1장 · 숫자 0이나 빈칸 없음</t>
+          <t>맬리브레인_3기_수료증_{원문이름} · Android JPEG / iOS PNG</t>
         </is>
       </c>
       <c r="J22" s="10" t="inlineStr">
         <is>
-          <t>S7-10 · §12</t>
-        </is>
-      </c>
-      <c r="K22" s="16" t="inlineStr">
-        <is>
-          <t>cmp_07A.png</t>
-        </is>
-      </c>
+          <t>S7-10 · Q-10</t>
+        </is>
+      </c>
+      <c r="K22" s="10" t="n"/>
       <c r="L22" s="4" t="n"/>
-      <c r="M22" s="10" t="inlineStr">
-        <is>
-          <t>웹은 앱 브리지가 없어 저장 버튼 비활성(정상) · 테두리 장식 없음 → BUG-06</t>
-        </is>
-      </c>
-      <c r="N22" s="14" t="inlineStr">
+      <c r="M22" s="10" t="n"/>
+      <c r="N22" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="O22" s="14" t="n"/>
-      <c r="P22" s="15" t="n"/>
-      <c r="Q22" s="14" t="n"/>
-      <c r="R22" s="15" t="n"/>
-      <c r="S22" s="14" t="n"/>
-      <c r="T22" s="14" t="n"/>
+      <c r="O22" s="15" t="n"/>
+      <c r="P22" s="16" t="n"/>
+      <c r="Q22" s="15" t="n"/>
+      <c r="R22" s="16" t="n"/>
+      <c r="S22" s="15" t="n"/>
+      <c r="T22" s="15" t="n"/>
     </row>
     <row r="23" ht="48" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
@@ -2963,63 +2963,75 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>07 A</t>
+          <t>07 B</t>
         </is>
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>①</t>
+          <t>③</t>
         </is>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
-          <t>앱</t>
+          <t>앱 · 웹</t>
         </is>
       </c>
       <c r="G23" s="10" t="inlineStr">
         <is>
-          <t>C-01 이후</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>파일명 · 형식 확인</t>
+          <t>참여기록 저장하기</t>
         </is>
       </c>
       <c r="I23" s="10" t="inlineStr">
         <is>
-          <t>맬리브레인_3기_수료증_{원문이름} · Android JPEG / iOS PNG</t>
+          <t>라벨 "참여기록 저장하기" · 파일명 …_참여기록_…</t>
         </is>
       </c>
       <c r="J23" s="10" t="inlineStr">
         <is>
-          <t>S7-10 · Q-10</t>
-        </is>
-      </c>
-      <c r="K23" s="10" t="n"/>
-      <c r="L23" s="4" t="n"/>
-      <c r="M23" s="10" t="n"/>
-      <c r="N23" s="14" t="inlineStr">
+          <t>S7-10 · Q-02</t>
+        </is>
+      </c>
+      <c r="K23" s="14" t="inlineStr">
+        <is>
+          <t>cmp_07B.png</t>
+        </is>
+      </c>
+      <c r="L23" s="17" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="M23" s="18" t="inlineStr">
+        <is>
+          <t>라벨 확인(웹)</t>
+        </is>
+      </c>
+      <c r="N23" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="O23" s="14" t="n"/>
-      <c r="P23" s="15" t="n"/>
-      <c r="Q23" s="14" t="n"/>
-      <c r="R23" s="15" t="n"/>
-      <c r="S23" s="14" t="n"/>
-      <c r="T23" s="14" t="n"/>
+      <c r="O23" s="15" t="n"/>
+      <c r="P23" s="16" t="n"/>
+      <c r="Q23" s="15" t="n"/>
+      <c r="R23" s="16" t="n"/>
+      <c r="S23" s="15" t="n"/>
+      <c r="T23" s="15" t="n"/>
     </row>
     <row r="24" ht="48" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
@@ -3029,12 +3041,12 @@
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>07 B</t>
+          <t>07 C</t>
         </is>
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>③</t>
+          <t>④</t>
         </is>
       </c>
       <c r="F24" s="10" t="inlineStr">
@@ -3049,22 +3061,22 @@
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>참여기록 저장하기</t>
+          <t>증서 화면</t>
         </is>
       </c>
       <c r="I24" s="10" t="inlineStr">
         <is>
-          <t>라벨 "참여기록 저장하기" · 파일명 …_참여기록_…</t>
+          <t>저장 버튼 없음 · 참여 실적 줄 없음 · 4기 · 홈 버튼만</t>
         </is>
       </c>
       <c r="J24" s="10" t="inlineStr">
         <is>
-          <t>S7-10 · Q-02</t>
-        </is>
-      </c>
-      <c r="K24" s="16" t="inlineStr">
-        <is>
-          <t>cmp_07B.png</t>
+          <t>S7-08 · S7-10</t>
+        </is>
+      </c>
+      <c r="K24" s="14" t="inlineStr">
+        <is>
+          <t>cmp_07C.png</t>
         </is>
       </c>
       <c r="L24" s="17" t="inlineStr">
@@ -3072,32 +3084,28 @@
           <t>통과</t>
         </is>
       </c>
-      <c r="M24" s="18" t="inlineStr">
-        <is>
-          <t>라벨 확인(웹)</t>
-        </is>
-      </c>
-      <c r="N24" s="14" t="inlineStr">
+      <c r="M24" s="18" t="n"/>
+      <c r="N24" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="O24" s="14" t="n"/>
-      <c r="P24" s="15" t="n"/>
-      <c r="Q24" s="14" t="n"/>
-      <c r="R24" s="15" t="n"/>
-      <c r="S24" s="14" t="n"/>
-      <c r="T24" s="14" t="n"/>
+      <c r="O24" s="15" t="n"/>
+      <c r="P24" s="16" t="n"/>
+      <c r="Q24" s="15" t="n"/>
+      <c r="R24" s="16" t="n"/>
+      <c r="S24" s="15" t="n"/>
+      <c r="T24" s="15" t="n"/>
     </row>
     <row r="25" ht="48" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>C-05</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
@@ -3107,71 +3115,63 @@
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>07 C</t>
+          <t>07 A</t>
         </is>
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
-          <t>④</t>
+          <t>①</t>
         </is>
       </c>
       <c r="F25" s="10" t="inlineStr">
         <is>
-          <t>앱 · 웹</t>
+          <t>앱</t>
         </is>
       </c>
       <c r="G25" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>사진 권한 거부</t>
         </is>
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>증서 화면</t>
+          <t>수료증 저장하기</t>
         </is>
       </c>
       <c r="I25" s="10" t="inlineStr">
         <is>
-          <t>저장 버튼 없음 · 참여 실적 줄 없음 · 4기 · 홈 버튼만</t>
+          <t>권한 안내 · 앱이 멈추지 않음</t>
         </is>
       </c>
       <c r="J25" s="10" t="inlineStr">
         <is>
-          <t>S7-08 · S7-10</t>
-        </is>
-      </c>
-      <c r="K25" s="16" t="inlineStr">
-        <is>
-          <t>cmp_07C.png</t>
-        </is>
-      </c>
-      <c r="L25" s="17" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="M25" s="18" t="n"/>
-      <c r="N25" s="14" t="inlineStr">
+          <t>P15</t>
+        </is>
+      </c>
+      <c r="K25" s="10" t="n"/>
+      <c r="L25" s="4" t="n"/>
+      <c r="M25" s="10" t="n"/>
+      <c r="N25" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="O25" s="14" t="n"/>
-      <c r="P25" s="15" t="n"/>
-      <c r="Q25" s="14" t="n"/>
-      <c r="R25" s="15" t="n"/>
-      <c r="S25" s="14" t="n"/>
-      <c r="T25" s="14" t="n"/>
+      <c r="O25" s="15" t="n"/>
+      <c r="P25" s="16" t="n"/>
+      <c r="Q25" s="15" t="n"/>
+      <c r="R25" s="16" t="n"/>
+      <c r="S25" s="15" t="n"/>
+      <c r="T25" s="15" t="n"/>
     </row>
     <row r="26" ht="48" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>C-05</t>
+          <t>C-06</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
@@ -3196,43 +3196,43 @@
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>사진 권한 거부</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>수료증 저장하기</t>
+          <t>저장 후</t>
         </is>
       </c>
       <c r="I26" s="10" t="inlineStr">
         <is>
-          <t>권한 안내 · 앱이 멈추지 않음</t>
+          <t>리포트가 닫히지 않고 그대로</t>
         </is>
       </c>
       <c r="J26" s="10" t="inlineStr">
         <is>
-          <t>P15</t>
+          <t>IA-R-10</t>
         </is>
       </c>
       <c r="K26" s="10" t="n"/>
       <c r="L26" s="4" t="n"/>
       <c r="M26" s="10" t="n"/>
-      <c r="N26" s="14" t="inlineStr">
+      <c r="N26" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="O26" s="14" t="n"/>
-      <c r="P26" s="15" t="n"/>
-      <c r="Q26" s="14" t="n"/>
-      <c r="R26" s="15" t="n"/>
-      <c r="S26" s="14" t="n"/>
-      <c r="T26" s="14" t="n"/>
+      <c r="O26" s="15" t="n"/>
+      <c r="P26" s="16" t="n"/>
+      <c r="Q26" s="15" t="n"/>
+      <c r="R26" s="16" t="n"/>
+      <c r="S26" s="15" t="n"/>
+      <c r="T26" s="15" t="n"/>
     </row>
     <row r="27" ht="48" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>C-06</t>
+          <t>C-07</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -3257,7 +3257,7 @@
       </c>
       <c r="F27" s="10" t="inlineStr">
         <is>
-          <t>앱</t>
+          <t>앱 · 웹</t>
         </is>
       </c>
       <c r="G27" s="10" t="inlineStr">
@@ -3267,53 +3267,61 @@
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>저장 후</t>
+          <t>증서 이름 확인</t>
         </is>
       </c>
       <c r="I27" s="10" t="inlineStr">
         <is>
-          <t>리포트가 닫히지 않고 그대로</t>
+          <t>표지는 마스킹(김*리) · 증서는 원문 이름</t>
         </is>
       </c>
       <c r="J27" s="10" t="inlineStr">
         <is>
-          <t>IA-R-10</t>
-        </is>
-      </c>
-      <c r="K27" s="10" t="n"/>
-      <c r="L27" s="4" t="n"/>
-      <c r="M27" s="10" t="n"/>
-      <c r="N27" s="14" t="inlineStr">
+          <t>S7-06 · P12</t>
+        </is>
+      </c>
+      <c r="K27" s="14" t="inlineStr">
+        <is>
+          <t>cmp_07A.png</t>
+        </is>
+      </c>
+      <c r="L27" s="17" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="M27" s="18" t="n"/>
+      <c r="N27" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="O27" s="14" t="n"/>
-      <c r="P27" s="15" t="n"/>
-      <c r="Q27" s="14" t="n"/>
-      <c r="R27" s="15" t="n"/>
-      <c r="S27" s="14" t="n"/>
-      <c r="T27" s="14" t="n"/>
+      <c r="O27" s="15" t="n"/>
+      <c r="P27" s="16" t="n"/>
+      <c r="Q27" s="15" t="n"/>
+      <c r="R27" s="16" t="n"/>
+      <c r="S27" s="15" t="n"/>
+      <c r="T27" s="15" t="n"/>
     </row>
     <row r="28" ht="48" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>C-07</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>3 증서 저장</t>
+          <t>4 4기 신청</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>07 A</t>
+          <t>07-h 시트</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr">
@@ -3333,22 +3341,22 @@
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
-          <t>증서 이름 확인</t>
+          <t>4기도 참여하기</t>
         </is>
       </c>
       <c r="I28" s="10" t="inlineStr">
         <is>
-          <t>표지는 마스킹(김*리) · 증서는 원문 이름</t>
+          <t>바텀시트 · 문구는 결정 Q-1대로 · [닫기] [네, 신청합니다]</t>
         </is>
       </c>
       <c r="J28" s="10" t="inlineStr">
         <is>
-          <t>S7-06 · P12</t>
-        </is>
-      </c>
-      <c r="K28" s="16" t="inlineStr">
-        <is>
-          <t>cmp_07A.png</t>
+          <t>07-h · K-13</t>
+        </is>
+      </c>
+      <c r="K28" s="14" t="inlineStr">
+        <is>
+          <t>cmp_07h.png</t>
         </is>
       </c>
       <c r="L28" s="17" t="inlineStr">
@@ -3356,28 +3364,32 @@
           <t>통과</t>
         </is>
       </c>
-      <c r="M28" s="18" t="n"/>
-      <c r="N28" s="14" t="inlineStr">
+      <c r="M28" s="18" t="inlineStr">
+        <is>
+          <t>목업과 같음 · 명칭에 4기 없음은 결정 Q-1</t>
+        </is>
+      </c>
+      <c r="N28" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="O28" s="14" t="n"/>
-      <c r="P28" s="15" t="n"/>
-      <c r="Q28" s="14" t="n"/>
-      <c r="R28" s="15" t="n"/>
-      <c r="S28" s="14" t="n"/>
-      <c r="T28" s="14" t="n"/>
+      <c r="O28" s="15" t="n"/>
+      <c r="P28" s="16" t="n"/>
+      <c r="Q28" s="15" t="n"/>
+      <c r="R28" s="16" t="n"/>
+      <c r="S28" s="15" t="n"/>
+      <c r="T28" s="15" t="n"/>
     </row>
     <row r="29" ht="48" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
@@ -3407,24 +3419,20 @@
       </c>
       <c r="H29" s="10" t="inlineStr">
         <is>
-          <t>4기도 참여하기</t>
+          <t>[닫기] / 딤 탭</t>
         </is>
       </c>
       <c r="I29" s="10" t="inlineStr">
         <is>
-          <t>바텀시트 · 문구는 결정 Q-1대로 · [닫기] [네, 신청합니다]</t>
+          <t>시트만 닫힘 · 신청 저장 안 됨</t>
         </is>
       </c>
       <c r="J29" s="10" t="inlineStr">
         <is>
-          <t>07-h · K-13</t>
-        </is>
-      </c>
-      <c r="K29" s="16" t="inlineStr">
-        <is>
-          <t>cmp_07h.png</t>
-        </is>
-      </c>
+          <t>07-h</t>
+        </is>
+      </c>
+      <c r="K29" s="10" t="n"/>
       <c r="L29" s="17" t="inlineStr">
         <is>
           <t>통과</t>
@@ -3432,30 +3440,30 @@
       </c>
       <c r="M29" s="18" t="inlineStr">
         <is>
-          <t>목업과 같음 · 명칭에 4기 없음은 결정 Q-1</t>
-        </is>
-      </c>
-      <c r="N29" s="14" t="inlineStr">
+          <t>[닫기] 확인(웹)</t>
+        </is>
+      </c>
+      <c r="N29" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="O29" s="14" t="n"/>
-      <c r="P29" s="15" t="n"/>
-      <c r="Q29" s="14" t="n"/>
-      <c r="R29" s="15" t="n"/>
-      <c r="S29" s="14" t="n"/>
-      <c r="T29" s="14" t="n"/>
+      <c r="O29" s="15" t="n"/>
+      <c r="P29" s="16" t="n"/>
+      <c r="Q29" s="15" t="n"/>
+      <c r="R29" s="16" t="n"/>
+      <c r="S29" s="15" t="n"/>
+      <c r="T29" s="15" t="n"/>
     </row>
     <row r="30" ht="48" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
@@ -3465,7 +3473,7 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>07-h 시트</t>
+          <t>08 완료</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr">
@@ -3485,51 +3493,55 @@
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>[닫기] / 딤 탭</t>
+          <t>[네, 신청합니다]</t>
         </is>
       </c>
       <c r="I30" s="10" t="inlineStr">
         <is>
-          <t>시트만 닫힘 · 신청 저장 안 됨</t>
+          <t>완료 화면 · 본문 4줄 "4기가 시작될 때 보건소에서 연락드리겠습니다. 자세한 문의사항은 032-453-6160으로 문의 바랍니다. 감사합니다."</t>
         </is>
       </c>
       <c r="J30" s="10" t="inlineStr">
         <is>
-          <t>07-h</t>
-        </is>
-      </c>
-      <c r="K30" s="10" t="n"/>
+          <t>SC-RP-08 · S8-05 · K-14</t>
+        </is>
+      </c>
+      <c r="K30" s="14" t="inlineStr">
+        <is>
+          <t>cmp_08.png</t>
+        </is>
+      </c>
       <c r="L30" s="17" t="inlineStr">
         <is>
-          <t>통과</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="M30" s="18" t="inlineStr">
         <is>
-          <t>[닫기] 확인(웹)</t>
-        </is>
-      </c>
-      <c r="N30" s="14" t="inlineStr">
+          <t>배치는 목업과 같음 · 첫 줄 누락 · 번호 6163 → WEB-1 · 02</t>
+        </is>
+      </c>
+      <c r="N30" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="O30" s="14" t="n"/>
-      <c r="P30" s="15" t="n"/>
-      <c r="Q30" s="14" t="n"/>
-      <c r="R30" s="15" t="n"/>
-      <c r="S30" s="14" t="n"/>
-      <c r="T30" s="14" t="n"/>
+      <c r="O30" s="15" t="n"/>
+      <c r="P30" s="16" t="n"/>
+      <c r="Q30" s="15" t="n"/>
+      <c r="R30" s="16" t="n"/>
+      <c r="S30" s="15" t="n"/>
+      <c r="T30" s="15" t="n"/>
     </row>
     <row r="31" ht="48" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
@@ -3549,7 +3561,7 @@
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
-          <t>앱 · 웹</t>
+          <t>앱</t>
         </is>
       </c>
       <c r="G31" s="10" t="inlineStr">
@@ -3559,55 +3571,43 @@
       </c>
       <c r="H31" s="10" t="inlineStr">
         <is>
-          <t>[네, 신청합니다]</t>
+          <t>[네, 신청합니다] 연타</t>
         </is>
       </c>
       <c r="I31" s="10" t="inlineStr">
         <is>
-          <t>완료 화면 · 본문 4줄 "4기가 시작될 때 보건소에서 연락드리겠습니다. 자세한 문의사항은 032-453-6160으로 문의 바랍니다. 감사합니다."</t>
+          <t>신청 1건만 저장</t>
         </is>
       </c>
       <c r="J31" s="10" t="inlineStr">
         <is>
-          <t>SC-RP-08 · S8-05 · K-14</t>
-        </is>
-      </c>
-      <c r="K31" s="16" t="inlineStr">
-        <is>
-          <t>cmp_08.png</t>
-        </is>
-      </c>
-      <c r="L31" s="17" t="inlineStr">
-        <is>
-          <t>실패</t>
-        </is>
-      </c>
-      <c r="M31" s="18" t="inlineStr">
-        <is>
-          <t>배치는 목업과 같음 · 첫 줄 누락 · 번호 6163 → BUG-01 · 02</t>
-        </is>
-      </c>
-      <c r="N31" s="14" t="inlineStr">
+          <t>IA-R-12</t>
+        </is>
+      </c>
+      <c r="K31" s="10" t="n"/>
+      <c r="L31" s="4" t="n"/>
+      <c r="M31" s="10" t="n"/>
+      <c r="N31" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="O31" s="14" t="n"/>
-      <c r="P31" s="15" t="n"/>
-      <c r="Q31" s="14" t="n"/>
-      <c r="R31" s="15" t="n"/>
-      <c r="S31" s="14" t="n"/>
-      <c r="T31" s="14" t="n"/>
+      <c r="O31" s="15" t="n"/>
+      <c r="P31" s="16" t="n"/>
+      <c r="Q31" s="15" t="n"/>
+      <c r="R31" s="16" t="n"/>
+      <c r="S31" s="15" t="n"/>
+      <c r="T31" s="15" t="n"/>
     </row>
     <row r="32" ht="48" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>A-05</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
@@ -3617,7 +3617,7 @@
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>08 완료</t>
+          <t>07-l</t>
         </is>
       </c>
       <c r="E32" s="10" t="inlineStr">
@@ -3627,48 +3627,60 @@
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>앱</t>
+          <t>앱 · 웹</t>
         </is>
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>A-03 이후</t>
         </is>
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
-          <t>[네, 신청합니다] 연타</t>
+          <t>홈 → 리포트 다시 열기</t>
         </is>
       </c>
       <c r="I32" s="10" t="inlineStr">
         <is>
-          <t>신청 1건만 저장</t>
+          <t>4기 버튼 비활성 + "4기 신청이 완료되었습니다"</t>
         </is>
       </c>
       <c r="J32" s="10" t="inlineStr">
         <is>
-          <t>IA-R-12</t>
-        </is>
-      </c>
-      <c r="K32" s="10" t="n"/>
-      <c r="L32" s="4" t="n"/>
-      <c r="M32" s="10" t="n"/>
-      <c r="N32" s="14" t="inlineStr">
+          <t>07-l · IA-R-12</t>
+        </is>
+      </c>
+      <c r="K32" s="14" t="inlineStr">
+        <is>
+          <t>cmp_07l.png</t>
+        </is>
+      </c>
+      <c r="L32" s="17" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="M32" s="18" t="inlineStr">
+        <is>
+          <t>state=07l · 목업과 같음</t>
+        </is>
+      </c>
+      <c r="N32" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="O32" s="14" t="n"/>
-      <c r="P32" s="15" t="n"/>
-      <c r="Q32" s="14" t="n"/>
-      <c r="R32" s="15" t="n"/>
-      <c r="S32" s="14" t="n"/>
-      <c r="T32" s="14" t="n"/>
+      <c r="O32" s="15" t="n"/>
+      <c r="P32" s="16" t="n"/>
+      <c r="Q32" s="15" t="n"/>
+      <c r="R32" s="16" t="n"/>
+      <c r="S32" s="15" t="n"/>
+      <c r="T32" s="15" t="n"/>
     </row>
     <row r="33" ht="48" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>A-05</t>
+          <t>A-06</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
@@ -3693,7 +3705,7 @@
       </c>
       <c r="F33" s="10" t="inlineStr">
         <is>
-          <t>앱 · 웹</t>
+          <t>앱</t>
         </is>
       </c>
       <c r="G33" s="10" t="inlineStr">
@@ -3703,50 +3715,38 @@
       </c>
       <c r="H33" s="10" t="inlineStr">
         <is>
-          <t>홈 → 리포트 다시 열기</t>
+          <t>다른 폰에서 같은 계정 로그인</t>
         </is>
       </c>
       <c r="I33" s="10" t="inlineStr">
         <is>
-          <t>4기 버튼 비활성 + "4기 신청이 완료되었습니다"</t>
+          <t>07-l 상태 그대로 (서버 값 기준)</t>
         </is>
       </c>
       <c r="J33" s="10" t="inlineStr">
         <is>
-          <t>07-l · IA-R-12</t>
-        </is>
-      </c>
-      <c r="K33" s="16" t="inlineStr">
-        <is>
-          <t>cmp_07l.png</t>
-        </is>
-      </c>
-      <c r="L33" s="17" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="M33" s="18" t="inlineStr">
-        <is>
-          <t>state=07l · 목업과 같음</t>
-        </is>
-      </c>
-      <c r="N33" s="14" t="inlineStr">
+          <t>apply.season4_applied</t>
+        </is>
+      </c>
+      <c r="K33" s="10" t="n"/>
+      <c r="L33" s="4" t="n"/>
+      <c r="M33" s="10" t="n"/>
+      <c r="N33" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="O33" s="14" t="n"/>
-      <c r="P33" s="15" t="n"/>
-      <c r="Q33" s="14" t="n"/>
-      <c r="R33" s="15" t="n"/>
-      <c r="S33" s="14" t="n"/>
-      <c r="T33" s="14" t="n"/>
+      <c r="O33" s="15" t="n"/>
+      <c r="P33" s="16" t="n"/>
+      <c r="Q33" s="15" t="n"/>
+      <c r="R33" s="16" t="n"/>
+      <c r="S33" s="15" t="n"/>
+      <c r="T33" s="15" t="n"/>
     </row>
     <row r="34" ht="48" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>A-06</t>
+          <t>A-07</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>07-l</t>
+          <t>08-a 실패</t>
         </is>
       </c>
       <c r="E34" s="10" t="inlineStr">
@@ -3776,48 +3776,56 @@
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>A-03 이후</t>
+          <t>비행기 모드</t>
         </is>
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
-          <t>다른 폰에서 같은 계정 로그인</t>
+          <t>[네, 신청합니다]</t>
         </is>
       </c>
       <c r="I34" s="10" t="inlineStr">
         <is>
-          <t>07-l 상태 그대로 (서버 값 기준)</t>
+          <t>실패 화면 · 제목은 FIG-03 결정대로 · 032-453-6160 · [다시 시도] 누르면 확인 없이 자동 재신청</t>
         </is>
       </c>
       <c r="J34" s="10" t="inlineStr">
         <is>
-          <t>apply.season4_applied</t>
+          <t>08-a · S8-06</t>
         </is>
       </c>
       <c r="K34" s="10" t="n"/>
-      <c r="L34" s="4" t="n"/>
-      <c r="M34" s="10" t="n"/>
-      <c r="N34" s="14" t="inlineStr">
+      <c r="L34" s="17" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="O34" s="14" t="n"/>
-      <c r="P34" s="15" t="n"/>
-      <c r="Q34" s="14" t="n"/>
-      <c r="R34" s="15" t="n"/>
-      <c r="S34" s="14" t="n"/>
-      <c r="T34" s="14" t="n"/>
+      <c r="M34" s="18" t="inlineStr">
+        <is>
+          <t>웹 샘플 없음 → 개발에 state=08a 요청</t>
+        </is>
+      </c>
+      <c r="N34" s="15" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+      <c r="O34" s="15" t="n"/>
+      <c r="P34" s="16" t="n"/>
+      <c r="Q34" s="15" t="n"/>
+      <c r="R34" s="16" t="n"/>
+      <c r="S34" s="15" t="n"/>
+      <c r="T34" s="15" t="n"/>
     </row>
     <row r="35" ht="48" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>A-07</t>
+          <t>A-08</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
@@ -3827,12 +3835,12 @@
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>08-a 실패</t>
+          <t>07-l</t>
         </is>
       </c>
       <c r="E35" s="10" t="inlineStr">
         <is>
-          <t>①</t>
+          <t>②</t>
         </is>
       </c>
       <c r="F35" s="10" t="inlineStr">
@@ -3842,56 +3850,48 @@
       </c>
       <c r="G35" s="10" t="inlineStr">
         <is>
-          <t>비행기 모드</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
-          <t>[네, 신청합니다]</t>
+          <t>리포트 열기</t>
         </is>
       </c>
       <c r="I35" s="10" t="inlineStr">
         <is>
-          <t>실패 화면 · 제목은 FIG-03 결정대로 · 032-453-6160 · [다시 시도] 누르면 확인 없이 자동 재신청</t>
+          <t>처음부터 07-l</t>
         </is>
       </c>
       <c r="J35" s="10" t="inlineStr">
         <is>
-          <t>08-a · S8-06</t>
+          <t>07-l</t>
         </is>
       </c>
       <c r="K35" s="10" t="n"/>
-      <c r="L35" s="17" t="inlineStr">
+      <c r="L35" s="4" t="n"/>
+      <c r="M35" s="10" t="n"/>
+      <c r="N35" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="M35" s="18" t="inlineStr">
-        <is>
-          <t>웹 샘플 없음 → 개발에 state=08a 요청</t>
-        </is>
-      </c>
-      <c r="N35" s="14" t="inlineStr">
-        <is>
-          <t>미실행</t>
-        </is>
-      </c>
-      <c r="O35" s="14" t="n"/>
-      <c r="P35" s="15" t="n"/>
-      <c r="Q35" s="14" t="n"/>
-      <c r="R35" s="15" t="n"/>
-      <c r="S35" s="14" t="n"/>
-      <c r="T35" s="14" t="n"/>
+      <c r="O35" s="15" t="n"/>
+      <c r="P35" s="16" t="n"/>
+      <c r="Q35" s="15" t="n"/>
+      <c r="R35" s="16" t="n"/>
+      <c r="S35" s="15" t="n"/>
+      <c r="T35" s="15" t="n"/>
     </row>
     <row r="36" ht="48" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>A-08</t>
+          <t>A-09</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
@@ -3901,12 +3901,12 @@
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>07-l</t>
+          <t>07-m</t>
         </is>
       </c>
       <c r="E36" s="10" t="inlineStr">
         <is>
-          <t>②</t>
+          <t>⑤</t>
         </is>
       </c>
       <c r="F36" s="10" t="inlineStr">
@@ -3921,43 +3921,43 @@
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
-          <t>리포트 열기</t>
+          <t>증서 화면</t>
         </is>
       </c>
       <c r="I36" s="10" t="inlineStr">
         <is>
-          <t>처음부터 07-l</t>
+          <t>4기 버튼 없음</t>
         </is>
       </c>
       <c r="J36" s="10" t="inlineStr">
         <is>
-          <t>07-l</t>
+          <t>07-m</t>
         </is>
       </c>
       <c r="K36" s="10" t="n"/>
       <c r="L36" s="4" t="n"/>
       <c r="M36" s="10" t="n"/>
-      <c r="N36" s="14" t="inlineStr">
+      <c r="N36" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="O36" s="14" t="n"/>
-      <c r="P36" s="15" t="n"/>
-      <c r="Q36" s="14" t="n"/>
-      <c r="R36" s="15" t="n"/>
-      <c r="S36" s="14" t="n"/>
-      <c r="T36" s="14" t="n"/>
+      <c r="O36" s="15" t="n"/>
+      <c r="P36" s="16" t="n"/>
+      <c r="Q36" s="15" t="n"/>
+      <c r="R36" s="16" t="n"/>
+      <c r="S36" s="15" t="n"/>
+      <c r="T36" s="15" t="n"/>
     </row>
     <row r="37" ht="48" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>A-09</t>
+          <t>A-10</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>07-m</t>
+          <t>노출 시점</t>
         </is>
       </c>
       <c r="E37" s="10" t="inlineStr">
         <is>
-          <t>⑤</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="F37" s="10" t="inlineStr">
@@ -3982,63 +3982,63 @@
       </c>
       <c r="G37" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10/27 출시 빌드</t>
         </is>
       </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
-          <t>증서 화면</t>
+          <t>출시 전 · 후 버튼 노출</t>
         </is>
       </c>
       <c r="I37" s="10" t="inlineStr">
         <is>
-          <t>4기 버튼 없음</t>
+          <t>10/27부터 노출</t>
         </is>
       </c>
       <c r="J37" s="10" t="inlineStr">
         <is>
-          <t>07-m</t>
+          <t>S7-11</t>
         </is>
       </c>
       <c r="K37" s="10" t="n"/>
       <c r="L37" s="4" t="n"/>
       <c r="M37" s="10" t="n"/>
-      <c r="N37" s="14" t="inlineStr">
+      <c r="N37" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="O37" s="14" t="n"/>
-      <c r="P37" s="15" t="n"/>
-      <c r="Q37" s="14" t="n"/>
-      <c r="R37" s="15" t="n"/>
-      <c r="S37" s="14" t="n"/>
-      <c r="T37" s="14" t="n"/>
+      <c r="O37" s="15" t="n"/>
+      <c r="P37" s="16" t="n"/>
+      <c r="Q37" s="15" t="n"/>
+      <c r="R37" s="16" t="n"/>
+      <c r="S37" s="15" t="n"/>
+      <c r="T37" s="15" t="n"/>
     </row>
     <row r="38" ht="48" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>A-10</t>
+          <t>X-01</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>4 4기 신청</t>
+          <t>5 닫기 · 뒤로가기</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>노출 시점</t>
+          <t>공통</t>
         </is>
       </c>
       <c r="E38" s="10" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>①</t>
         </is>
       </c>
       <c r="F38" s="10" t="inlineStr">
@@ -4048,43 +4048,43 @@
       </c>
       <c r="G38" s="10" t="inlineStr">
         <is>
-          <t>10/27 출시 빌드</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
-          <t>출시 전 · 후 버튼 노출</t>
+          <t>아무 섹션에서 ✕</t>
         </is>
       </c>
       <c r="I38" s="10" t="inlineStr">
         <is>
-          <t>10/27부터 노출</t>
+          <t>홈으로 복귀</t>
         </is>
       </c>
       <c r="J38" s="10" t="inlineStr">
         <is>
-          <t>S7-11</t>
+          <t>IA-R-05</t>
         </is>
       </c>
       <c r="K38" s="10" t="n"/>
       <c r="L38" s="4" t="n"/>
       <c r="M38" s="10" t="n"/>
-      <c r="N38" s="14" t="inlineStr">
+      <c r="N38" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="O38" s="14" t="n"/>
-      <c r="P38" s="15" t="n"/>
-      <c r="Q38" s="14" t="n"/>
-      <c r="R38" s="15" t="n"/>
-      <c r="S38" s="14" t="n"/>
-      <c r="T38" s="14" t="n"/>
+      <c r="O38" s="15" t="n"/>
+      <c r="P38" s="16" t="n"/>
+      <c r="Q38" s="15" t="n"/>
+      <c r="R38" s="16" t="n"/>
+      <c r="S38" s="15" t="n"/>
+      <c r="T38" s="15" t="n"/>
     </row>
     <row r="39" ht="48" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>X-01</t>
+          <t>X-02</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="F39" s="10" t="inlineStr">
         <is>
-          <t>앱</t>
+          <t>Android</t>
         </is>
       </c>
       <c r="G39" s="10" t="inlineStr">
@@ -4119,12 +4119,12 @@
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
-          <t>아무 섹션에서 ✕</t>
+          <t>리포트 / 시트 열림 / 완료 화면에서 뒤로가기</t>
         </is>
       </c>
       <c r="I39" s="10" t="inlineStr">
         <is>
-          <t>홈으로 복귀</t>
+          <t>시트가 열려 있으면 시트만 닫힘 · 그 외 홈</t>
         </is>
       </c>
       <c r="J39" s="10" t="inlineStr">
@@ -4135,27 +4135,27 @@
       <c r="K39" s="10" t="n"/>
       <c r="L39" s="4" t="n"/>
       <c r="M39" s="10" t="n"/>
-      <c r="N39" s="14" t="inlineStr">
+      <c r="N39" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="O39" s="14" t="n"/>
-      <c r="P39" s="15" t="n"/>
-      <c r="Q39" s="14" t="n"/>
-      <c r="R39" s="15" t="n"/>
-      <c r="S39" s="14" t="n"/>
-      <c r="T39" s="14" t="n"/>
+      <c r="O39" s="15" t="n"/>
+      <c r="P39" s="16" t="n"/>
+      <c r="Q39" s="15" t="n"/>
+      <c r="R39" s="16" t="n"/>
+      <c r="S39" s="15" t="n"/>
+      <c r="T39" s="15" t="n"/>
     </row>
     <row r="40" ht="48" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>X-02</t>
+          <t>X-03</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
@@ -4175,7 +4175,7 @@
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>iOS</t>
         </is>
       </c>
       <c r="G40" s="10" t="inlineStr">
@@ -4185,38 +4185,38 @@
       </c>
       <c r="H40" s="10" t="inlineStr">
         <is>
-          <t>리포트 / 시트 열림 / 완료 화면에서 뒤로가기</t>
+          <t>밀어서 닫기</t>
         </is>
       </c>
       <c r="I40" s="10" t="inlineStr">
         <is>
-          <t>시트가 열려 있으면 시트만 닫힘 · 그 외 홈</t>
+          <t>홈 복귀 · 화면 깨짐 없음</t>
         </is>
       </c>
       <c r="J40" s="10" t="inlineStr">
         <is>
-          <t>IA-R-05</t>
+          <t>개발 B-7</t>
         </is>
       </c>
       <c r="K40" s="10" t="n"/>
       <c r="L40" s="4" t="n"/>
       <c r="M40" s="10" t="n"/>
-      <c r="N40" s="14" t="inlineStr">
+      <c r="N40" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="O40" s="14" t="n"/>
-      <c r="P40" s="15" t="n"/>
-      <c r="Q40" s="14" t="n"/>
-      <c r="R40" s="15" t="n"/>
-      <c r="S40" s="14" t="n"/>
-      <c r="T40" s="14" t="n"/>
+      <c r="O40" s="15" t="n"/>
+      <c r="P40" s="16" t="n"/>
+      <c r="Q40" s="15" t="n"/>
+      <c r="R40" s="16" t="n"/>
+      <c r="S40" s="15" t="n"/>
+      <c r="T40" s="15" t="n"/>
     </row>
     <row r="41" ht="48" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>X-03</t>
+          <t>X-04</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>08 완료</t>
         </is>
       </c>
       <c r="E41" s="10" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
-          <t>iOS</t>
+          <t>앱</t>
         </is>
       </c>
       <c r="G41" s="10" t="inlineStr">
@@ -4251,38 +4251,42 @@
       </c>
       <c r="H41" s="10" t="inlineStr">
         <is>
-          <t>밀어서 닫기</t>
+          <t>[홈으로 돌아가기]</t>
         </is>
       </c>
       <c r="I41" s="10" t="inlineStr">
         <is>
-          <t>홈 복귀 · 화면 깨짐 없음</t>
+          <t>홈 복귀</t>
         </is>
       </c>
       <c r="J41" s="10" t="inlineStr">
         <is>
-          <t>개발 B-7</t>
+          <t>S8-07</t>
         </is>
       </c>
       <c r="K41" s="10" t="n"/>
       <c r="L41" s="4" t="n"/>
-      <c r="M41" s="10" t="n"/>
-      <c r="N41" s="14" t="inlineStr">
+      <c r="M41" s="10" t="inlineStr">
+        <is>
+          <t>웹에서는 동작 안 하는 게 정상</t>
+        </is>
+      </c>
+      <c r="N41" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="O41" s="14" t="n"/>
-      <c r="P41" s="15" t="n"/>
-      <c r="Q41" s="14" t="n"/>
-      <c r="R41" s="15" t="n"/>
-      <c r="S41" s="14" t="n"/>
-      <c r="T41" s="14" t="n"/>
+      <c r="O41" s="15" t="n"/>
+      <c r="P41" s="16" t="n"/>
+      <c r="Q41" s="15" t="n"/>
+      <c r="R41" s="16" t="n"/>
+      <c r="S41" s="15" t="n"/>
+      <c r="T41" s="15" t="n"/>
     </row>
     <row r="42" ht="48" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>X-04</t>
+          <t>T-01</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
@@ -4292,17 +4296,17 @@
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>5 닫기 · 뒤로가기</t>
+          <t>6 4기 전환</t>
         </is>
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>08 완료</t>
+          <t>체험 홈</t>
         </is>
       </c>
       <c r="E42" s="10" t="inlineStr">
         <is>
-          <t>①</t>
+          <t>4기 승인 계정</t>
         </is>
       </c>
       <c r="F42" s="10" t="inlineStr">
@@ -4312,47 +4316,43 @@
       </c>
       <c r="G42" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>개발에 4기 시작일 당겨 달라고 요청</t>
         </is>
       </c>
       <c r="H42" s="10" t="inlineStr">
         <is>
-          <t>[홈으로 돌아가기]</t>
+          <t>4기 홈 전환 후 확인</t>
         </is>
       </c>
       <c r="I42" s="10" t="inlineStr">
         <is>
-          <t>홈 복귀</t>
+          <t>리포트 카드 사라짐 · 진행 내역으로는 열림</t>
         </is>
       </c>
       <c r="J42" s="10" t="inlineStr">
         <is>
-          <t>S8-07</t>
+          <t>IA-R-08 · F4</t>
         </is>
       </c>
       <c r="K42" s="10" t="n"/>
       <c r="L42" s="4" t="n"/>
-      <c r="M42" s="10" t="inlineStr">
-        <is>
-          <t>웹에서는 동작 안 하는 게 정상</t>
-        </is>
-      </c>
-      <c r="N42" s="14" t="inlineStr">
+      <c r="M42" s="10" t="n"/>
+      <c r="N42" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="O42" s="14" t="n"/>
-      <c r="P42" s="15" t="n"/>
-      <c r="Q42" s="14" t="n"/>
-      <c r="R42" s="15" t="n"/>
-      <c r="S42" s="14" t="n"/>
-      <c r="T42" s="14" t="n"/>
+      <c r="O42" s="15" t="n"/>
+      <c r="P42" s="16" t="n"/>
+      <c r="Q42" s="15" t="n"/>
+      <c r="R42" s="16" t="n"/>
+      <c r="S42" s="15" t="n"/>
+      <c r="T42" s="15" t="n"/>
     </row>
     <row r="43" ht="48" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>T-01</t>
+          <t>M-01</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
@@ -4362,17 +4362,17 @@
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>6 4기 전환</t>
+          <t>6 측정</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>체험 홈</t>
+          <t>이벤트</t>
         </is>
       </c>
       <c r="E43" s="10" t="inlineStr">
         <is>
-          <t>4기 승인 계정</t>
+          <t>①</t>
         </is>
       </c>
       <c r="F43" s="10" t="inlineStr">
@@ -4382,43 +4382,51 @@
       </c>
       <c r="G43" s="10" t="inlineStr">
         <is>
-          <t>개발에 4기 시작일 당겨 달라고 요청</t>
+          <t>개발에 이벤트 로그 확인 요청</t>
         </is>
       </c>
       <c r="H43" s="10" t="inlineStr">
         <is>
-          <t>4기 홈 전환 후 확인</t>
+          <t>카드 / 자동 팝업 / 진행 내역으로 각각 진입</t>
         </is>
       </c>
       <c r="I43" s="10" t="inlineStr">
         <is>
-          <t>리포트 카드 사라짐 · 진행 내역으로는 열림</t>
+          <t>entry 값이 경로별로 다르게 남음 · programId 채워짐</t>
         </is>
       </c>
       <c r="J43" s="10" t="inlineStr">
         <is>
-          <t>IA-R-08 · F4</t>
+          <t>IA-Q-06 · 개발 D-4</t>
         </is>
       </c>
       <c r="K43" s="10" t="n"/>
-      <c r="L43" s="4" t="n"/>
-      <c r="M43" s="10" t="n"/>
-      <c r="N43" s="14" t="inlineStr">
+      <c r="L43" s="17" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="M43" s="18" t="inlineStr">
+        <is>
+          <t>웹 샘플은 entry=manual · programId 빈 값</t>
+        </is>
+      </c>
+      <c r="N43" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="O43" s="14" t="n"/>
-      <c r="P43" s="15" t="n"/>
-      <c r="Q43" s="14" t="n"/>
-      <c r="R43" s="15" t="n"/>
-      <c r="S43" s="14" t="n"/>
-      <c r="T43" s="14" t="n"/>
+      <c r="O43" s="15" t="n"/>
+      <c r="P43" s="16" t="n"/>
+      <c r="Q43" s="15" t="n"/>
+      <c r="R43" s="16" t="n"/>
+      <c r="S43" s="15" t="n"/>
+      <c r="T43" s="15" t="n"/>
     </row>
     <row r="44" ht="48" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>M-01</t>
+          <t>M-02</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
@@ -4448,66 +4456,66 @@
       </c>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t>개발에 이벤트 로그 확인 요청</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H44" s="10" t="inlineStr">
         <is>
-          <t>카드 / 자동 팝업 / 진행 내역으로 각각 진입</t>
+          <t>한 섹션에 30초 머문 뒤 이동</t>
         </is>
       </c>
       <c r="I44" s="10" t="inlineStr">
         <is>
-          <t>entry 값이 경로별로 다르게 남음 · programId 채워짐</t>
+          <t>해당 섹션 dwell ≈ 30초</t>
         </is>
       </c>
       <c r="J44" s="10" t="inlineStr">
         <is>
-          <t>IA-Q-06 · 개발 D-4</t>
+          <t>IA-Q-06</t>
         </is>
       </c>
       <c r="K44" s="10" t="n"/>
       <c r="L44" s="17" t="inlineStr">
         <is>
-          <t>보류</t>
+          <t>통과</t>
         </is>
       </c>
       <c r="M44" s="18" t="inlineStr">
         <is>
-          <t>웹 샘플은 entry=manual · programId 빈 값</t>
-        </is>
-      </c>
-      <c r="N44" s="14" t="inlineStr">
+          <t>웹에서 section_view/leave + dwellMs 발생 확인</t>
+        </is>
+      </c>
+      <c r="N44" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="O44" s="14" t="n"/>
-      <c r="P44" s="15" t="n"/>
-      <c r="Q44" s="14" t="n"/>
-      <c r="R44" s="15" t="n"/>
-      <c r="S44" s="14" t="n"/>
-      <c r="T44" s="14" t="n"/>
+      <c r="O44" s="15" t="n"/>
+      <c r="P44" s="16" t="n"/>
+      <c r="Q44" s="15" t="n"/>
+      <c r="R44" s="16" t="n"/>
+      <c r="S44" s="15" t="n"/>
+      <c r="T44" s="15" t="n"/>
     </row>
     <row r="45" ht="48" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>M-02</t>
+          <t>PH-01</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>6 측정</t>
+          <t>6 전화번호</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t>이벤트</t>
+          <t>전 화면</t>
         </is>
       </c>
       <c r="E45" s="10" t="inlineStr">
@@ -4517,139 +4525,143 @@
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
-          <t>앱</t>
+          <t>앱 · 웹 · 문자</t>
         </is>
       </c>
       <c r="G45" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>개발 수정 반영 후</t>
         </is>
       </c>
       <c r="H45" s="10" t="inlineStr">
         <is>
-          <t>한 섹션에 30초 머문 뒤 이동</t>
+          <t>리포트 완료 · 실패 화면 · 신청폼 결과 화면 · 문자 본문의 번호</t>
         </is>
       </c>
       <c r="I45" s="10" t="inlineStr">
         <is>
-          <t>해당 섹션 dwell ≈ 30초</t>
+          <t>모두 032-453-6160 (6163 · 담당자 번호 없음)</t>
         </is>
       </c>
       <c r="J45" s="10" t="inlineStr">
         <is>
-          <t>IA-Q-06</t>
-        </is>
-      </c>
-      <c r="K45" s="10" t="n"/>
+          <t>K-14 · 보건소 요청 10/12</t>
+        </is>
+      </c>
+      <c r="K45" s="14" t="inlineStr">
+        <is>
+          <t>cmp_08.png</t>
+        </is>
+      </c>
       <c r="L45" s="17" t="inlineStr">
         <is>
-          <t>통과</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="M45" s="18" t="inlineStr">
         <is>
-          <t>웹에서 section_view/leave + dwellMs 발생 확인</t>
-        </is>
-      </c>
-      <c r="N45" s="14" t="inlineStr">
+          <t>완료 화면 032-453-6163 → WEB-1</t>
+        </is>
+      </c>
+      <c r="N45" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="O45" s="14" t="n"/>
-      <c r="P45" s="15" t="n"/>
-      <c r="Q45" s="14" t="n"/>
-      <c r="R45" s="15" t="n"/>
-      <c r="S45" s="14" t="n"/>
-      <c r="T45" s="14" t="n"/>
+      <c r="O45" s="15" t="n"/>
+      <c r="P45" s="16" t="n"/>
+      <c r="Q45" s="15" t="n"/>
+      <c r="R45" s="16" t="n"/>
+      <c r="S45" s="15" t="n"/>
+      <c r="T45" s="15" t="n"/>
     </row>
     <row r="46" ht="48" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>PH-01</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>6 전화번호</t>
+          <t>6 신청폼 4기</t>
         </is>
       </c>
       <c r="D46" s="10" t="inlineStr">
         <is>
-          <t>전 화면</t>
+          <t>첫 화면</t>
         </is>
       </c>
       <c r="E46" s="10" t="inlineStr">
         <is>
-          <t>①</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F46" s="10" t="inlineStr">
         <is>
-          <t>앱 · 웹 · 문자</t>
+          <t>휴대폰 브라우저</t>
         </is>
       </c>
       <c r="G46" s="10" t="inlineStr">
         <is>
-          <t>개발 수정 반영 후</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H46" s="10" t="inlineStr">
         <is>
-          <t>리포트 완료 · 실패 화면 · 신청폼 결과 화면 · 문자 본문의 번호</t>
+          <t>/invitations/namdong4</t>
         </is>
       </c>
       <c r="I46" s="10" t="inlineStr">
         <is>
-          <t>모두 032-453-6160 (6163 · 담당자 번호 없음)</t>
+          <t>명칭 · 기관명은 결정 Q-1 · Q-2대로 · "2027년 2월~11월"</t>
         </is>
       </c>
       <c r="J46" s="10" t="inlineStr">
         <is>
-          <t>K-14 · 보건소 요청 10/12</t>
-        </is>
-      </c>
-      <c r="K46" s="16" t="inlineStr">
-        <is>
-          <t>cmp_08.png</t>
+          <t>개발 B-8</t>
+        </is>
+      </c>
+      <c r="K46" s="14" t="inlineStr">
+        <is>
+          <t>dev_form4_landing.png</t>
         </is>
       </c>
       <c r="L46" s="17" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>보류</t>
         </is>
       </c>
       <c r="M46" s="18" t="inlineStr">
         <is>
-          <t>완료 화면 032-453-6163 → BUG-01</t>
-        </is>
-      </c>
-      <c r="N46" s="14" t="inlineStr">
+          <t>"인천 남동구 보건소 x 맬리 · 치매예방교실 4기" → Q-1 · Q-2</t>
+        </is>
+      </c>
+      <c r="N46" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="O46" s="14" t="n"/>
-      <c r="P46" s="15" t="n"/>
-      <c r="Q46" s="14" t="n"/>
-      <c r="R46" s="15" t="n"/>
-      <c r="S46" s="14" t="n"/>
-      <c r="T46" s="14" t="n"/>
+      <c r="O46" s="15" t="n"/>
+      <c r="P46" s="16" t="n"/>
+      <c r="Q46" s="15" t="n"/>
+      <c r="R46" s="16" t="n"/>
+      <c r="S46" s="15" t="n"/>
+      <c r="T46" s="15" t="n"/>
     </row>
     <row r="47" ht="48" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
@@ -4659,12 +4671,12 @@
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>첫 화면</t>
+          <t>입력 · 결과</t>
         </is>
       </c>
       <c r="E47" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>본인 번호</t>
         </is>
       </c>
       <c r="F47" s="10" t="inlineStr">
@@ -4674,60 +4686,60 @@
       </c>
       <c r="G47" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>실제 문자 발송 — 본인 번호로 1회만</t>
         </is>
       </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
-          <t>/invitations/namdong4</t>
+          <t>입력 폼 제출</t>
         </is>
       </c>
       <c r="I47" s="10" t="inlineStr">
         <is>
-          <t>명칭 · 기관명은 결정 Q-1 · Q-2대로 · "2027년 2월~11월"</t>
+          <t>결과 화면 문구 · 문자 내용 · 케어센터 신청자 관리에 1건</t>
         </is>
       </c>
       <c r="J47" s="10" t="inlineStr">
         <is>
-          <t>개발 B-8</t>
-        </is>
-      </c>
-      <c r="K47" s="16" t="inlineStr">
-        <is>
-          <t>dev_form4_landing.png</t>
+          <t>개발 B-8 · Q-3</t>
+        </is>
+      </c>
+      <c r="K47" s="14" t="inlineStr">
+        <is>
+          <t>dev_form4_form.png</t>
         </is>
       </c>
       <c r="L47" s="17" t="inlineStr">
         <is>
-          <t>보류</t>
+          <t>미실행</t>
         </is>
       </c>
       <c r="M47" s="18" t="inlineStr">
         <is>
-          <t>"인천 남동구 보건소 x 맬리 · 치매예방교실 4기" → Q-1 · Q-2</t>
-        </is>
-      </c>
-      <c r="N47" s="14" t="inlineStr">
+          <t>제출 금지 조건으로 미실행 · 입력 폼 "신청하면 바로 참여가 확정" → Q-3</t>
+        </is>
+      </c>
+      <c r="N47" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="O47" s="14" t="n"/>
-      <c r="P47" s="15" t="n"/>
-      <c r="Q47" s="14" t="n"/>
-      <c r="R47" s="15" t="n"/>
-      <c r="S47" s="14" t="n"/>
-      <c r="T47" s="14" t="n"/>
+      <c r="O47" s="15" t="n"/>
+      <c r="P47" s="16" t="n"/>
+      <c r="Q47" s="15" t="n"/>
+      <c r="R47" s="16" t="n"/>
+      <c r="S47" s="15" t="n"/>
+      <c r="T47" s="15" t="n"/>
     </row>
     <row r="48" ht="48" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
@@ -4737,7 +4749,7 @@
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
-          <t>입력 · 결과</t>
+          <t>중복</t>
         </is>
       </c>
       <c r="E48" s="10" t="inlineStr">
@@ -4752,60 +4764,48 @@
       </c>
       <c r="G48" s="10" t="inlineStr">
         <is>
-          <t>실제 문자 발송 — 본인 번호로 1회만</t>
+          <t>F-02 이후</t>
         </is>
       </c>
       <c r="H48" s="10" t="inlineStr">
         <is>
-          <t>입력 폼 제출</t>
+          <t>같은 번호로 다시 제출</t>
         </is>
       </c>
       <c r="I48" s="10" t="inlineStr">
         <is>
-          <t>결과 화면 문구 · 문자 내용 · 케어센터 신청자 관리에 1건</t>
+          <t>중복 안내 (정의 없음 → Q-4)</t>
         </is>
       </c>
       <c r="J48" s="10" t="inlineStr">
         <is>
-          <t>개발 B-8 · Q-3</t>
-        </is>
-      </c>
-      <c r="K48" s="16" t="inlineStr">
-        <is>
-          <t>dev_form4_form.png</t>
-        </is>
-      </c>
-      <c r="L48" s="17" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K48" s="10" t="n"/>
+      <c r="L48" s="4" t="n"/>
+      <c r="M48" s="10" t="n"/>
+      <c r="N48" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="M48" s="18" t="inlineStr">
-        <is>
-          <t>제출 금지 조건으로 미실행 · 입력 폼 "신청하면 바로 참여가 확정" → Q-3</t>
-        </is>
-      </c>
-      <c r="N48" s="14" t="inlineStr">
-        <is>
-          <t>미실행</t>
-        </is>
-      </c>
-      <c r="O48" s="14" t="n"/>
-      <c r="P48" s="15" t="n"/>
-      <c r="Q48" s="14" t="n"/>
-      <c r="R48" s="15" t="n"/>
-      <c r="S48" s="14" t="n"/>
-      <c r="T48" s="14" t="n"/>
+      <c r="O48" s="15" t="n"/>
+      <c r="P48" s="16" t="n"/>
+      <c r="Q48" s="15" t="n"/>
+      <c r="R48" s="16" t="n"/>
+      <c r="S48" s="15" t="n"/>
+      <c r="T48" s="15" t="n"/>
     </row>
     <row r="49" ht="48" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
@@ -4815,12 +4815,12 @@
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>중복</t>
+          <t>대리 등록</t>
         </is>
       </c>
       <c r="E49" s="10" t="inlineStr">
         <is>
-          <t>본인 번호</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F49" s="10" t="inlineStr">
@@ -4830,17 +4830,17 @@
       </c>
       <c r="G49" s="10" t="inlineStr">
         <is>
-          <t>F-02 이후</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
-          <t>같은 번호로 다시 제출</t>
+          <t>"보건소 직원이신가요?"</t>
         </is>
       </c>
       <c r="I49" s="10" t="inlineStr">
         <is>
-          <t>중복 안내 (정의 없음 → Q-4)</t>
+          <t>대리 등록 경로가 열림 (제출하지 않음)</t>
         </is>
       </c>
       <c r="J49" s="10" t="inlineStr">
@@ -4851,37 +4851,37 @@
       <c r="K49" s="10" t="n"/>
       <c r="L49" s="4" t="n"/>
       <c r="M49" s="10" t="n"/>
-      <c r="N49" s="14" t="inlineStr">
+      <c r="N49" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="O49" s="14" t="n"/>
-      <c r="P49" s="15" t="n"/>
-      <c r="Q49" s="14" t="n"/>
-      <c r="R49" s="15" t="n"/>
-      <c r="S49" s="14" t="n"/>
-      <c r="T49" s="14" t="n"/>
+      <c r="O49" s="15" t="n"/>
+      <c r="P49" s="16" t="n"/>
+      <c r="Q49" s="15" t="n"/>
+      <c r="R49" s="16" t="n"/>
+      <c r="S49" s="15" t="n"/>
+      <c r="T49" s="15" t="n"/>
     </row>
     <row r="50" ht="48" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>F-05</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>6 신청폼 4기</t>
+          <t>6 신청폼 3기</t>
         </is>
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>대리 등록</t>
+          <t>3기 링크</t>
         </is>
       </c>
       <c r="E50" s="10" t="inlineStr">
@@ -4901,38 +4901,50 @@
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
-          <t>"보건소 직원이신가요?"</t>
+          <t>/invitations/namdong3</t>
         </is>
       </c>
       <c r="I50" s="10" t="inlineStr">
         <is>
-          <t>대리 등록 경로가 열림 (제출하지 않음)</t>
+          <t>결정 Q-6대로</t>
         </is>
       </c>
       <c r="J50" s="10" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K50" s="10" t="n"/>
-      <c r="L50" s="4" t="n"/>
-      <c r="M50" s="10" t="n"/>
-      <c r="N50" s="14" t="inlineStr">
+          <t>개발 §A ⑤</t>
+        </is>
+      </c>
+      <c r="K50" s="14" t="inlineStr">
+        <is>
+          <t>dev_form3_landing.png</t>
+        </is>
+      </c>
+      <c r="L50" s="17" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="M50" s="18" t="inlineStr">
+        <is>
+          <t>지금은 3기 첫 화면 정상 노출</t>
+        </is>
+      </c>
+      <c r="N50" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="O50" s="14" t="n"/>
-      <c r="P50" s="15" t="n"/>
-      <c r="Q50" s="14" t="n"/>
-      <c r="R50" s="15" t="n"/>
-      <c r="S50" s="14" t="n"/>
-      <c r="T50" s="14" t="n"/>
+      <c r="O50" s="15" t="n"/>
+      <c r="P50" s="16" t="n"/>
+      <c r="Q50" s="15" t="n"/>
+      <c r="R50" s="16" t="n"/>
+      <c r="S50" s="15" t="n"/>
+      <c r="T50" s="15" t="n"/>
     </row>
     <row r="51" ht="48" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>F-05</t>
+          <t>K-01</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
@@ -4942,12 +4954,12 @@
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>6 신청폼 3기</t>
+          <t>6 케어센터</t>
         </is>
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t>3기 링크</t>
+          <t>4기</t>
         </is>
       </c>
       <c r="E51" s="10" t="inlineStr">
@@ -4957,125 +4969,47 @@
       </c>
       <c r="F51" s="10" t="inlineStr">
         <is>
-          <t>휴대폰 브라우저</t>
+          <t>PC</t>
         </is>
       </c>
       <c r="G51" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>로그인</t>
         </is>
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
-          <t>/invitations/namdong3</t>
+          <t>목록 · 신청자 관리</t>
         </is>
       </c>
       <c r="I51" s="10" t="inlineStr">
         <is>
-          <t>결정 Q-6대로</t>
+          <t>4기 "진행 예정" · 신청자 관리 탭 열림</t>
         </is>
       </c>
       <c r="J51" s="10" t="inlineStr">
         <is>
-          <t>개발 §A ⑤</t>
-        </is>
-      </c>
-      <c r="K51" s="16" t="inlineStr">
-        <is>
-          <t>dev_form3_landing.png</t>
-        </is>
-      </c>
-      <c r="L51" s="17" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="M51" s="18" t="inlineStr">
-        <is>
-          <t>지금은 3기 첫 화면 정상 노출</t>
-        </is>
-      </c>
-      <c r="N51" s="14" t="inlineStr">
+          <t>개발 B-9</t>
+        </is>
+      </c>
+      <c r="K51" s="10" t="n"/>
+      <c r="L51" s="4" t="n"/>
+      <c r="M51" s="10" t="n"/>
+      <c r="N51" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
         </is>
       </c>
-      <c r="O51" s="14" t="n"/>
-      <c r="P51" s="15" t="n"/>
-      <c r="Q51" s="14" t="n"/>
-      <c r="R51" s="15" t="n"/>
-      <c r="S51" s="14" t="n"/>
-      <c r="T51" s="14" t="n"/>
-    </row>
-    <row r="52" ht="48" customHeight="1">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>K-01</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C52" s="10" t="inlineStr">
-        <is>
-          <t>6 케어센터</t>
-        </is>
-      </c>
-      <c r="D52" s="10" t="inlineStr">
-        <is>
-          <t>4기</t>
-        </is>
-      </c>
-      <c r="E52" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F52" s="10" t="inlineStr">
-        <is>
-          <t>PC</t>
-        </is>
-      </c>
-      <c r="G52" s="10" t="inlineStr">
-        <is>
-          <t>로그인</t>
-        </is>
-      </c>
-      <c r="H52" s="10" t="inlineStr">
-        <is>
-          <t>목록 · 신청자 관리</t>
-        </is>
-      </c>
-      <c r="I52" s="10" t="inlineStr">
-        <is>
-          <t>4기 "진행 예정" · 신청자 관리 탭 열림</t>
-        </is>
-      </c>
-      <c r="J52" s="10" t="inlineStr">
-        <is>
-          <t>개발 B-9</t>
-        </is>
-      </c>
-      <c r="K52" s="10" t="n"/>
-      <c r="L52" s="4" t="n"/>
-      <c r="M52" s="10" t="n"/>
-      <c r="N52" s="14" t="inlineStr">
-        <is>
-          <t>미실행</t>
-        </is>
-      </c>
-      <c r="O52" s="14" t="n"/>
-      <c r="P52" s="15" t="n"/>
-      <c r="Q52" s="14" t="n"/>
-      <c r="R52" s="15" t="n"/>
-      <c r="S52" s="14" t="n"/>
-      <c r="T52" s="14" t="n"/>
+      <c r="O51" s="15" t="n"/>
+      <c r="P51" s="16" t="n"/>
+      <c r="Q51" s="15" t="n"/>
+      <c r="R51" s="16" t="n"/>
+      <c r="S51" s="15" t="n"/>
+      <c r="T51" s="15" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:T1"/>
-  <conditionalFormatting sqref="L2:L52">
+  <conditionalFormatting sqref="L2:L51">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"실패"</formula>
     </cfRule>
@@ -5083,7 +5017,7 @@
       <formula>"통과"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N52">
+  <conditionalFormatting sqref="N2:N51">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="0">
       <formula>"실패"</formula>
     </cfRule>
@@ -5091,7 +5025,7 @@
       <formula>"통과"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O52">
+  <conditionalFormatting sqref="O2:O51">
     <cfRule type="cellIs" priority="5" operator="equal" dxfId="0">
       <formula>"실패"</formula>
     </cfRule>
@@ -5099,41 +5033,41 @@
       <formula>"통과"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B52">
+  <conditionalFormatting sqref="B2:B51">
     <cfRule type="cellIs" priority="7" operator="equal" dxfId="2">
       <formula>"P1"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="N2:O52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N2:O51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"미실행,통과,실패,보류,해당없음"</formula1>
     </dataValidation>
-    <dataValidation sqref="L2:L52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L2:L51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"통과,실패,보류,미실행"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5239,7 +5173,7 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>BUG-01</t>
+          <t>WEB-1</t>
         </is>
       </c>
       <c r="B2" s="10" t="inlineStr">
@@ -5257,7 +5191,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E2" s="14" t="inlineStr">
+      <c r="E2" s="15" t="inlineStr">
         <is>
           <t>개발 수정</t>
         </is>
@@ -5282,7 +5216,7 @@
           <t>032-453-6163</t>
         </is>
       </c>
-      <c r="J2" s="16" t="inlineStr">
+      <c r="J2" s="14" t="inlineStr">
         <is>
           <t>cmp_08.png</t>
         </is>
@@ -5302,12 +5236,12 @@
           <t>PH-01 · A-03 · A-07</t>
         </is>
       </c>
-      <c r="N2" s="15" t="n"/>
+      <c r="N2" s="16" t="n"/>
     </row>
     <row r="3" ht="60" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>BUG-02</t>
+          <t>WEB-2</t>
         </is>
       </c>
       <c r="B3" s="10" t="inlineStr">
@@ -5325,7 +5259,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E3" s="14" t="inlineStr">
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t>기획 선행</t>
         </is>
@@ -5350,7 +5284,7 @@
           <t>2줄: 자세한 문의사항은 … 문의 바랍니다. 감사합니다. — 피그마 목업 카드(1463:1286)가 아직 2줄이라 개발이 목업을 따름</t>
         </is>
       </c>
-      <c r="J3" s="16" t="inlineStr">
+      <c r="J3" s="14" t="inlineStr">
         <is>
           <t>cmp_08.png</t>
         </is>
@@ -5370,12 +5304,12 @@
           <t>A-03</t>
         </is>
       </c>
-      <c r="N3" s="15" t="n"/>
+      <c r="N3" s="16" t="n"/>
     </row>
     <row r="4" ht="60" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>BUG-03</t>
+          <t>WEB-3</t>
         </is>
       </c>
       <c r="B4" s="10" t="inlineStr">
@@ -5393,7 +5327,7 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="15" t="inlineStr">
         <is>
           <t>확인 필요</t>
         </is>
@@ -5418,7 +5352,7 @@
           <t>가운데 정렬 / 메달 없이 캐릭터만</t>
         </is>
       </c>
-      <c r="J4" s="16" t="inlineStr">
+      <c r="J4" s="14" t="inlineStr">
         <is>
           <t>cmp_01.png</t>
         </is>
@@ -5438,12 +5372,12 @@
           <t>S-01</t>
         </is>
       </c>
-      <c r="N4" s="15" t="n"/>
+      <c r="N4" s="16" t="n"/>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>BUG-04</t>
+          <t>WEB-4</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
@@ -5461,7 +5395,7 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E5" s="14" t="inlineStr">
+      <c r="E5" s="15" t="inlineStr">
         <is>
           <t>개발 수정</t>
         </is>
@@ -5486,7 +5420,7 @@
           <t>시작과 끝이 거의 수평 · 10월 라벨 강조 없음</t>
         </is>
       </c>
-      <c r="J5" s="16" t="inlineStr">
+      <c r="J5" s="14" t="inlineStr">
         <is>
           <t>cmp_02.png</t>
         </is>
@@ -5506,12 +5440,12 @@
           <t>S-02</t>
         </is>
       </c>
-      <c r="N5" s="15" t="n"/>
+      <c r="N5" s="16" t="n"/>
     </row>
     <row r="6" ht="60" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>BUG-05</t>
+          <t>WEB-5</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
@@ -5529,7 +5463,7 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>확인 필요</t>
         </is>
@@ -5554,7 +5488,7 @@
           <t>88% 검정 / 왼쪽에 회색 원(캐릭터 자리) + 헤드라인 2줄로 줄바꿈</t>
         </is>
       </c>
-      <c r="J6" s="16" t="inlineStr">
+      <c r="J6" s="14" t="inlineStr">
         <is>
           <t>cmp_03.png</t>
         </is>
@@ -5574,12 +5508,12 @@
           <t>S-03</t>
         </is>
       </c>
-      <c r="N6" s="15" t="n"/>
+      <c r="N6" s="16" t="n"/>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>BUG-06</t>
+          <t>WEB-6</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
@@ -5597,7 +5531,7 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="15" t="inlineStr">
         <is>
           <t>개발 수정</t>
         </is>
@@ -5622,7 +5556,7 @@
           <t>금박 테두리만 · 내부 라인 · 마름모 없음</t>
         </is>
       </c>
-      <c r="J7" s="16" t="inlineStr">
+      <c r="J7" s="14" t="inlineStr">
         <is>
           <t>cmp_07A.png</t>
         </is>
@@ -5642,12 +5576,12 @@
           <t>C-01 · C-04</t>
         </is>
       </c>
-      <c r="N7" s="15" t="n"/>
+      <c r="N7" s="16" t="n"/>
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>BUG-07</t>
+          <t>WEB-7</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
@@ -5665,7 +5599,7 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr">
+      <c r="E8" s="15" t="inlineStr">
         <is>
           <t>확인 필요</t>
         </is>
@@ -5690,7 +5624,7 @@
           <t>아이콘 없음 · 버튼이 본문 바로 아래 좁은 회색 버튼</t>
         </is>
       </c>
-      <c r="J8" s="16" t="inlineStr">
+      <c r="J8" s="14" t="inlineStr">
         <is>
           <t>cmp_sys05.png</t>
         </is>
@@ -5707,15 +5641,15 @@
       </c>
       <c r="M8" s="10" t="inlineStr">
         <is>
-          <t>E-08</t>
-        </is>
-      </c>
-      <c r="N8" s="15" t="n"/>
+          <t>E-07</t>
+        </is>
+      </c>
+      <c r="N8" s="16" t="n"/>
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>BUG-08</t>
+          <t>WEB-8</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
@@ -5733,7 +5667,7 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E9" s="15" t="inlineStr">
         <is>
           <t>앱 확인</t>
         </is>
@@ -5758,7 +5692,7 @@
           <t>05 안내박스 마지막 줄 · 04B 하단 문구 위에 힌트가 겹침 (375×812)</t>
         </is>
       </c>
-      <c r="J9" s="16" t="inlineStr">
+      <c r="J9" s="14" t="inlineStr">
         <is>
           <t>cmp_05.png</t>
         </is>
@@ -5778,12 +5712,12 @@
           <t>S-08</t>
         </is>
       </c>
-      <c r="N9" s="15" t="n"/>
+      <c r="N9" s="16" t="n"/>
     </row>
     <row r="10" ht="60" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>BUG-09</t>
+          <t>WEB-9</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
@@ -5801,7 +5735,7 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="E10" s="15" t="inlineStr">
         <is>
           <t>확인 필요</t>
         </is>
@@ -5826,7 +5760,7 @@
           <t>게임명 2줄 / 라벨이 아크 끝 아래</t>
         </is>
       </c>
-      <c r="J10" s="16" t="inlineStr">
+      <c r="J10" s="14" t="inlineStr">
         <is>
           <t>cmp_04.png</t>
         </is>
@@ -5846,12 +5780,12 @@
           <t>S-04 · S-06</t>
         </is>
       </c>
-      <c r="N10" s="15" t="n"/>
+      <c r="N10" s="16" t="n"/>
     </row>
     <row r="11" ht="60" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>BUG-10</t>
+          <t>WEB-10</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
@@ -5869,7 +5803,7 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="E11" s="15" t="inlineStr">
         <is>
           <t>개발 수정</t>
         </is>
@@ -5894,7 +5828,7 @@
           <t>1위만 강조색 · 2 · 3위 회색 · 횟수 1위만 강조색</t>
         </is>
       </c>
-      <c r="J11" s="16" t="inlineStr">
+      <c r="J11" s="14" t="inlineStr">
         <is>
           <t>cmp_04.png</t>
         </is>
@@ -5914,12 +5848,12 @@
           <t>S-04</t>
         </is>
       </c>
-      <c r="N11" s="15" t="n"/>
+      <c r="N11" s="16" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>새 결함은 아래 빈 행에 BUG-06부터 이어서 적습니다. 심각도: Blocker 사용 불가 · Major 잘못된 정보 · Minor 정본과 다름 · Trivial 표기</t>
+          <t>이 시트는 기획이 개발 웹 샘플에서 먼저 본 차이(WEB-1~10)입니다. 앱에서 찾은 문제는 노션 QA 체크표의 해당 TC '문제' 칸에 적습니다. 심각도: Blocker 사용 불가 · Major 잘못된 정보 · Minor 정본과 다름 · Trivial 표기</t>
         </is>
       </c>
     </row>
@@ -6046,7 +5980,7 @@
           <t>1463:1286</t>
         </is>
       </c>
-      <c r="H2" s="15" t="inlineStr">
+      <c r="H2" s="16" t="inlineStr">
         <is>
           <t>디스크립션(4줄 · 6160) 유지 — 목업 카드는 Pretendard 폰트라 기획이 피그마에서 직접 수정 필요 (1463:1286 · 실패 1461:6914)</t>
         </is>
@@ -6088,7 +6022,7 @@
           <t>1484:1453</t>
         </is>
       </c>
-      <c r="H3" s="15" t="inlineStr">
+      <c r="H3" s="16" t="inlineStr">
         <is>
           <t>완료(10/12) — 디스크립션 S8-02 · S8-04를 목업 배치로 정정 · 프로토타입 · 문서 반영</t>
         </is>
@@ -6130,7 +6064,7 @@
           <t>1461:6901</t>
         </is>
       </c>
-      <c r="H4" s="15" t="inlineStr">
+      <c r="H4" s="16" t="inlineStr">
         <is>
           <t>완료(10/12) — 목업 기준 "신청이 완료되지 못했습니다" · 프로그램명 없음 · 디스크립션 · 프로토타입 · 문서 반영</t>
         </is>
@@ -6172,7 +6106,7 @@
           <t>1239:1351</t>
         </is>
       </c>
-      <c r="H5" s="15" t="inlineStr">
+      <c r="H5" s="16" t="inlineStr">
         <is>
           <t>완료(10/12) — 디스크립션 S1-01을 "2026 …"으로 정정 · 프로토타입 · 문서 반영</t>
         </is>
@@ -6214,9 +6148,9 @@
           <t>1240:1351</t>
         </is>
       </c>
-      <c r="H6" s="15" t="inlineStr">
-        <is>
-          <t>완료(10/12) — 캐릭터 없음으로 정정 · 개발 BUG-05 유지</t>
+      <c r="H6" s="16" t="inlineStr">
+        <is>
+          <t>완료(10/12) — 캐릭터 없음으로 정정 · 개발 WEB-5 유지</t>
         </is>
       </c>
     </row>
@@ -6256,7 +6190,7 @@
           <t>1239:1965</t>
         </is>
       </c>
-      <c r="H7" s="15" t="inlineStr">
+      <c r="H7" s="16" t="inlineStr">
         <is>
           <t>완료(10/12) — 디스크립션을 180° · 180 − 점수 × 12로 정정</t>
         </is>
@@ -6298,7 +6232,7 @@
           <t>1264:1433</t>
         </is>
       </c>
-      <c r="H8" s="15" t="inlineStr">
+      <c r="H8" s="16" t="inlineStr">
         <is>
           <t>완료(10/12) — 둥근 사각 인장으로 정정 · 프로토타입 · 문서 반영</t>
         </is>
@@ -6340,9 +6274,9 @@
           <t>1136:5858</t>
         </is>
       </c>
-      <c r="H9" s="15" t="inlineStr">
-        <is>
-          <t>목업 유지(아이콘 자리) — 프로토타입은 이미 같음 · 개발 BUG-07 유지</t>
+      <c r="H9" s="16" t="inlineStr">
+        <is>
+          <t>목업 유지(아이콘 자리) — 프로토타입은 이미 같음 · 개발 WEB-7 유지</t>
         </is>
       </c>
     </row>
@@ -6382,7 +6316,7 @@
           <t>1122:856</t>
         </is>
       </c>
-      <c r="H10" s="15" t="inlineStr">
+      <c r="H10" s="16" t="inlineStr">
         <is>
           <t>목업 샘플값 69% → 59% — Pretendard 폰트라 기획이 피그마에서 직접 수정 필요 (1122:887)</t>
         </is>
@@ -6488,8 +6422,8 @@
           <t>10/15</t>
         </is>
       </c>
-      <c r="F2" s="15" t="n"/>
-      <c r="G2" s="14" t="n"/>
+      <c r="F2" s="16" t="n"/>
+      <c r="G2" s="15" t="n"/>
       <c r="H2" s="10" t="inlineStr">
         <is>
           <t>K-13 · 개발 §A ①</t>
@@ -6522,8 +6456,8 @@
           <t>10/15</t>
         </is>
       </c>
-      <c r="F3" s="15" t="n"/>
-      <c r="G3" s="14" t="n"/>
+      <c r="F3" s="16" t="n"/>
+      <c r="G3" s="15" t="n"/>
       <c r="H3" s="10" t="inlineStr">
         <is>
           <t>K-09 · 개발 §A ①</t>
@@ -6556,8 +6490,8 @@
           <t>10/15</t>
         </is>
       </c>
-      <c r="F4" s="15" t="n"/>
-      <c r="G4" s="14" t="n"/>
+      <c r="F4" s="16" t="n"/>
+      <c r="G4" s="15" t="n"/>
       <c r="H4" s="10" t="inlineStr">
         <is>
           <t>개발 D-2 · form 06 #1</t>
@@ -6590,8 +6524,8 @@
           <t>10/15</t>
         </is>
       </c>
-      <c r="F5" s="15" t="n"/>
-      <c r="G5" s="14" t="n"/>
+      <c r="F5" s="16" t="n"/>
+      <c r="G5" s="15" t="n"/>
       <c r="H5" s="10" t="inlineStr">
         <is>
           <t>개발 §A ④</t>
@@ -6624,8 +6558,8 @@
           <t>10/15</t>
         </is>
       </c>
-      <c r="F6" s="15" t="n"/>
-      <c r="G6" s="14" t="n"/>
+      <c r="F6" s="16" t="n"/>
+      <c r="G6" s="15" t="n"/>
       <c r="H6" s="10" t="inlineStr">
         <is>
           <t>—</t>
@@ -6658,8 +6592,8 @@
           <t>10/15</t>
         </is>
       </c>
-      <c r="F7" s="15" t="n"/>
-      <c r="G7" s="14" t="n"/>
+      <c r="F7" s="16" t="n"/>
+      <c r="G7" s="15" t="n"/>
       <c r="H7" s="10" t="inlineStr">
         <is>
           <t>개발 §A ⑤</t>
@@ -6692,8 +6626,8 @@
           <t>10/15</t>
         </is>
       </c>
-      <c r="F8" s="15" t="n"/>
-      <c r="G8" s="14" t="n"/>
+      <c r="F8" s="16" t="n"/>
+      <c r="G8" s="15" t="n"/>
       <c r="H8" s="10" t="inlineStr">
         <is>
           <t>개발 §A ②</t>
@@ -6726,8 +6660,8 @@
           <t>10/15 (마지막 기한)</t>
         </is>
       </c>
-      <c r="F9" s="15" t="n"/>
-      <c r="G9" s="14" t="n"/>
+      <c r="F9" s="16" t="n"/>
+      <c r="G9" s="15" t="n"/>
       <c r="H9" s="10" t="inlineStr">
         <is>
           <t>IA-Q-04 · IA-Q-05 · 개발 §A ⑥</t>
@@ -6819,8 +6753,8 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="F2" s="14" t="n"/>
-      <c r="G2" s="15" t="n"/>
+      <c r="F2" s="15" t="n"/>
+      <c r="G2" s="16" t="n"/>
     </row>
     <row r="3" ht="32" customHeight="1">
       <c r="A3" s="4" t="n">
@@ -6846,8 +6780,8 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="F3" s="14" t="n"/>
-      <c r="G3" s="15" t="n"/>
+      <c r="F3" s="15" t="n"/>
+      <c r="G3" s="16" t="n"/>
     </row>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="4" t="n">
@@ -6873,8 +6807,8 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="F4" s="14" t="n"/>
-      <c r="G4" s="15" t="n"/>
+      <c r="F4" s="15" t="n"/>
+      <c r="G4" s="16" t="n"/>
     </row>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="4" t="n">
@@ -6900,8 +6834,8 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="F5" s="14" t="n"/>
-      <c r="G5" s="15" t="n"/>
+      <c r="F5" s="15" t="n"/>
+      <c r="G5" s="16" t="n"/>
     </row>
     <row r="6" ht="32" customHeight="1">
       <c r="A6" s="4" t="n">
@@ -6927,8 +6861,8 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="15" t="n"/>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="16" t="n"/>
     </row>
     <row r="7" ht="32" customHeight="1">
       <c r="A7" s="4" t="n">
@@ -6954,8 +6888,8 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="F7" s="15" t="n"/>
+      <c r="G7" s="16" t="n"/>
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="4" t="n">
@@ -6981,8 +6915,8 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="15" t="n"/>
+      <c r="F8" s="15" t="n"/>
+      <c r="G8" s="16" t="n"/>
     </row>
     <row r="9" ht="32" customHeight="1">
       <c r="A9" s="4" t="n">
@@ -7008,8 +6942,8 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="F9" s="15" t="n"/>
+      <c r="G9" s="16" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:G1"/>
@@ -7090,7 +7024,7 @@
       </c>
       <c r="E3" s="10" t="inlineStr">
         <is>
-          <t>첫 진입 · 자동 팝업 · 저장 · 4기 신청 전체</t>
+          <t>자동 팝업 → 증서 저장 → 4기 신청</t>
         </is>
       </c>
     </row>
@@ -7112,12 +7046,12 @@
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>A · 4기 신청 완료</t>
+          <t>A 수료</t>
         </is>
       </c>
       <c r="E4" s="10" t="inlineStr">
         <is>
-          <t>꽉 찬 데이터(게임 71회 · 마음 12일 · 1위) · 07-l</t>
+          <t>게임 · 마음 · 걸음 꽉 찬 데이터 · 랭킹 1위</t>
         </is>
       </c>
     </row>
@@ -7144,7 +7078,7 @@
       </c>
       <c r="E5" s="10" t="inlineStr">
         <is>
-          <t>참여기록 라벨 · 파일명</t>
+          <t>"참여기록 저장하기" 라벨</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7132,7 @@
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>다른 프로그램 진행 중 → 카드 없음 · 07-m 4기 버튼 숨김</t>
+          <t>다른 프로그램 진행 중이라 카드 없음 · 4기 버튼 숨김(07-m)</t>
         </is>
       </c>
     </row>
@@ -7225,7 +7159,7 @@
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>카드 없음 · 링크로 열면 "아직 볼 수 없어요"</t>
+          <t>카드 없음 · 공개 전 안내 확인용</t>
         </is>
       </c>
     </row>
@@ -7252,7 +7186,7 @@
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>카드 없음 · 링크로 열면 P20 비대상 안내</t>
+          <t>카드 없음 · 비대상 안내(P20) 확인용</t>
         </is>
       </c>
     </row>
@@ -7394,7 +7328,7 @@
           <t>수료 A</t>
         </is>
       </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>https://dev-meli-web.meli.health/report-3gi?state=nice</t>
         </is>
@@ -7406,7 +7340,7 @@
           <t>참여기록 B</t>
         </is>
       </c>
-      <c r="B25" s="16" t="inlineStr">
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t>https://dev-meli-web.meli.health/report-3gi?state=07B</t>
         </is>
@@ -7418,7 +7352,7 @@
           <t>참여확인 C</t>
         </is>
       </c>
-      <c r="B26" s="16" t="inlineStr">
+      <c r="B26" s="14" t="inlineStr">
         <is>
           <t>https://dev-meli-web.meli.health/report-3gi?state=07C</t>
         </is>
@@ -7430,7 +7364,7 @@
           <t>4기 신청 완료</t>
         </is>
       </c>
-      <c r="B27" s="16" t="inlineStr">
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>https://dev-meli-web.meli.health/report-3gi?state=07l</t>
         </is>
@@ -7442,7 +7376,7 @@
           <t>비대상 P20</t>
         </is>
       </c>
-      <c r="B28" s="16" t="inlineStr">
+      <c r="B28" s="14" t="inlineStr">
         <is>
           <t>https://dev-meli-web.meli.health/report-3gi?state=sys05</t>
         </is>
@@ -7454,7 +7388,7 @@
           <t>신청폼 4기 (제출하면 실제 문자 — 본인 번호만)</t>
         </is>
       </c>
-      <c r="B29" s="16" t="inlineStr">
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t>https://dev-meli-web.meli.health/invitations/namdong4</t>
         </is>
@@ -7518,12 +7452,12 @@
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>SC-RP-01 표지 · BUG-03</t>
+          <t>SC-RP-01 표지 · WEB-3</t>
         </is>
       </c>
       <c r="H3" s="8" t="inlineStr">
         <is>
-          <t>SC-RP-02 · BUG-04</t>
+          <t>SC-RP-02 · WEB-4</t>
         </is>
       </c>
     </row>
@@ -7542,12 +7476,12 @@
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>SC-RP-03 · BUG-05</t>
+          <t>SC-RP-03 · WEB-5</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>SC-RP-04 · BUG-09</t>
+          <t>SC-RP-04 · WEB-9</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7505,7 @@
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>SC-RP-05 · BUG-08 · 09</t>
+          <t>SC-RP-05 · WEB-8 · 09</t>
         </is>
       </c>
     </row>
@@ -7595,7 +7529,7 @@
       </c>
       <c r="H93" s="8" t="inlineStr">
         <is>
-          <t>SC-RP-07 A · BUG-06</t>
+          <t>SC-RP-07 A · WEB-6</t>
         </is>
       </c>
     </row>
@@ -7662,12 +7596,12 @@
     <row r="183">
       <c r="A183" s="8" t="inlineStr">
         <is>
-          <t>SC-RP-08 · BUG-01 · 02</t>
+          <t>SC-RP-08 · WEB-1 · 02</t>
         </is>
       </c>
       <c r="H183" s="8" t="inlineStr">
         <is>
-          <t>SYS-05 · BUG-07</t>
+          <t>SYS-05 · WEB-7</t>
         </is>
       </c>
     </row>

--- a/qa/3기리포트_QA_TC.xlsx
+++ b/qa/3기리포트_QA_TC.xlsx
@@ -1042,23 +1042,23 @@
         </is>
       </c>
       <c r="C5" s="4">
-        <f>COUNTIF(TC!$B$2:$B$51,A5)</f>
+        <f>COUNTIF(TC!$B$2:$B$47,A5)</f>
         <v/>
       </c>
       <c r="D5" s="4">
-        <f>COUNTIFS(TC!$B$2:$B$51,A5,TC!$N$2:$N$51,"통과")</f>
+        <f>COUNTIFS(TC!$B$2:$B$47,A5,TC!$N$2:$N$47,"통과")</f>
         <v/>
       </c>
       <c r="E5" s="4">
-        <f>COUNTIFS(TC!$B$2:$B$51,A5,TC!$N$2:$N$51,"실패")</f>
+        <f>COUNTIFS(TC!$B$2:$B$47,A5,TC!$N$2:$N$47,"실패")</f>
         <v/>
       </c>
       <c r="F5" s="4">
-        <f>COUNTIFS(TC!$B$2:$B$51,A5,TC!$N$2:$N$51,"보류")</f>
+        <f>COUNTIFS(TC!$B$2:$B$47,A5,TC!$N$2:$N$47,"보류")</f>
         <v/>
       </c>
       <c r="G5" s="4">
-        <f>C5-D5-E5-F5-COUNTIFS(TC!$B$2:$B$51,A5,TC!$N$2:$N$51,"해당없음")</f>
+        <f>C5-D5-E5-F5-COUNTIFS(TC!$B$2:$B$47,A5,TC!$N$2:$N$47,"해당없음")</f>
         <v/>
       </c>
       <c r="H5" s="5">
@@ -1078,23 +1078,23 @@
         </is>
       </c>
       <c r="C6" s="4">
-        <f>COUNTIF(TC!$B$2:$B$51,A6)</f>
+        <f>COUNTIF(TC!$B$2:$B$47,A6)</f>
         <v/>
       </c>
       <c r="D6" s="4">
-        <f>COUNTIFS(TC!$B$2:$B$51,A6,TC!$N$2:$N$51,"통과")</f>
+        <f>COUNTIFS(TC!$B$2:$B$47,A6,TC!$N$2:$N$47,"통과")</f>
         <v/>
       </c>
       <c r="E6" s="4">
-        <f>COUNTIFS(TC!$B$2:$B$51,A6,TC!$N$2:$N$51,"실패")</f>
+        <f>COUNTIFS(TC!$B$2:$B$47,A6,TC!$N$2:$N$47,"실패")</f>
         <v/>
       </c>
       <c r="F6" s="4">
-        <f>COUNTIFS(TC!$B$2:$B$51,A6,TC!$N$2:$N$51,"보류")</f>
+        <f>COUNTIFS(TC!$B$2:$B$47,A6,TC!$N$2:$N$47,"보류")</f>
         <v/>
       </c>
       <c r="G6" s="4">
-        <f>C6-D6-E6-F6-COUNTIFS(TC!$B$2:$B$51,A6,TC!$N$2:$N$51,"해당없음")</f>
+        <f>C6-D6-E6-F6-COUNTIFS(TC!$B$2:$B$47,A6,TC!$N$2:$N$47,"해당없음")</f>
         <v/>
       </c>
       <c r="H6" s="5">
@@ -1114,23 +1114,23 @@
         </is>
       </c>
       <c r="C7" s="4">
-        <f>COUNTIF(TC!$B$2:$B$51,A7)</f>
+        <f>COUNTIF(TC!$B$2:$B$47,A7)</f>
         <v/>
       </c>
       <c r="D7" s="4">
-        <f>COUNTIFS(TC!$B$2:$B$51,A7,TC!$N$2:$N$51,"통과")</f>
+        <f>COUNTIFS(TC!$B$2:$B$47,A7,TC!$N$2:$N$47,"통과")</f>
         <v/>
       </c>
       <c r="E7" s="4">
-        <f>COUNTIFS(TC!$B$2:$B$51,A7,TC!$N$2:$N$51,"실패")</f>
+        <f>COUNTIFS(TC!$B$2:$B$47,A7,TC!$N$2:$N$47,"실패")</f>
         <v/>
       </c>
       <c r="F7" s="4">
-        <f>COUNTIFS(TC!$B$2:$B$51,A7,TC!$N$2:$N$51,"보류")</f>
+        <f>COUNTIFS(TC!$B$2:$B$47,A7,TC!$N$2:$N$47,"보류")</f>
         <v/>
       </c>
       <c r="G7" s="4">
-        <f>C7-D7-E7-F7-COUNTIFS(TC!$B$2:$B$51,A7,TC!$N$2:$N$51,"해당없음")</f>
+        <f>C7-D7-E7-F7-COUNTIFS(TC!$B$2:$B$47,A7,TC!$N$2:$N$47,"해당없음")</f>
         <v/>
       </c>
       <c r="H7" s="5">
@@ -1312,7 +1312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T51"/>
+  <dimension ref="A1:T47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2808,22 +2808,22 @@
     <row r="21" ht="48" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>S-11</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>3 증서 저장</t>
+          <t>2 8개 섹션</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>07 A</t>
+          <t>SYS-01 · SYS-02</t>
         </is>
       </c>
       <c r="E21" s="10" t="inlineStr">
@@ -2838,35 +2838,27 @@
       </c>
       <c r="G21" s="10" t="inlineStr">
         <is>
-          <t>사진 권한 허용</t>
+          <t>느린 네트워크 (속도 제한 · 신호 약한 곳)</t>
         </is>
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>수료증 저장하기</t>
+          <t>홈 카드를 누른다</t>
         </is>
       </c>
       <c r="I21" s="10" t="inlineStr">
         <is>
-          <t>사진첩에 1:1 이미지 1장 · 숫자 0이나 빈칸 없음</t>
+          <t>"리포트를 불러오고 있어요" → 3초 넘으면 "조금만 기다려주세요" 추가</t>
         </is>
       </c>
       <c r="J21" s="10" t="inlineStr">
         <is>
-          <t>S7-10 · §12</t>
-        </is>
-      </c>
-      <c r="K21" s="14" t="inlineStr">
-        <is>
-          <t>cmp_07A.png</t>
-        </is>
-      </c>
+          <t>P19 · SYS-01 · SYS-02</t>
+        </is>
+      </c>
+      <c r="K21" s="10" t="n"/>
       <c r="L21" s="4" t="n"/>
-      <c r="M21" s="10" t="inlineStr">
-        <is>
-          <t>웹은 앱 브리지가 없어 저장 버튼 비활성(정상) · 테두리 장식 없음 → WEB-6</t>
-        </is>
-      </c>
+      <c r="M21" s="10" t="n"/>
       <c r="N21" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
@@ -2882,7 +2874,7 @@
     <row r="22" ht="48" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
@@ -2912,27 +2904,35 @@
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>C-01 이후</t>
+          <t>사진 권한 허용</t>
         </is>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>파일명 · 형식 확인</t>
+          <t>수료증 저장하기</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr">
         <is>
-          <t>맬리브레인_3기_수료증_{원문이름} · Android JPEG / iOS PNG</t>
+          <t>사진첩에 1:1 이미지 1장 · 숫자 0이나 빈칸 없음</t>
         </is>
       </c>
       <c r="J22" s="10" t="inlineStr">
         <is>
-          <t>S7-10 · Q-10</t>
-        </is>
-      </c>
-      <c r="K22" s="10" t="n"/>
+          <t>S7-10 · §12</t>
+        </is>
+      </c>
+      <c r="K22" s="14" t="inlineStr">
+        <is>
+          <t>cmp_07A.png</t>
+        </is>
+      </c>
       <c r="L22" s="4" t="n"/>
-      <c r="M22" s="10" t="n"/>
+      <c r="M22" s="10" t="inlineStr">
+        <is>
+          <t>웹은 앱 브리지가 없어 저장 버튼 비활성(정상) · 테두리 장식 없음 → WEB-6</t>
+        </is>
+      </c>
       <c r="N22" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
@@ -2948,12 +2948,12 @@
     <row r="23" ht="48" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
@@ -2963,54 +2963,42 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>07 B</t>
+          <t>07 A</t>
         </is>
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>③</t>
+          <t>①</t>
         </is>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
-          <t>앱 · 웹</t>
+          <t>앱</t>
         </is>
       </c>
       <c r="G23" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>C-01 이후</t>
         </is>
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>참여기록 저장하기</t>
+          <t>파일명 · 형식 확인</t>
         </is>
       </c>
       <c r="I23" s="10" t="inlineStr">
         <is>
-          <t>라벨 "참여기록 저장하기" · 파일명 …_참여기록_…</t>
+          <t>맬리브레인_3기_수료증_{원문이름} · Android JPEG / iOS PNG</t>
         </is>
       </c>
       <c r="J23" s="10" t="inlineStr">
         <is>
-          <t>S7-10 · Q-02</t>
-        </is>
-      </c>
-      <c r="K23" s="14" t="inlineStr">
-        <is>
-          <t>cmp_07B.png</t>
-        </is>
-      </c>
-      <c r="L23" s="17" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="M23" s="18" t="inlineStr">
-        <is>
-          <t>라벨 확인(웹)</t>
-        </is>
-      </c>
+          <t>S7-10 · Q-10</t>
+        </is>
+      </c>
+      <c r="K23" s="10" t="n"/>
+      <c r="L23" s="4" t="n"/>
+      <c r="M23" s="10" t="n"/>
       <c r="N23" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
@@ -3026,12 +3014,12 @@
     <row r="24" ht="48" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
@@ -3041,12 +3029,12 @@
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>07 C</t>
+          <t>07 B</t>
         </is>
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>④</t>
+          <t>③</t>
         </is>
       </c>
       <c r="F24" s="10" t="inlineStr">
@@ -3061,22 +3049,22 @@
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>증서 화면</t>
+          <t>참여기록 저장하기</t>
         </is>
       </c>
       <c r="I24" s="10" t="inlineStr">
         <is>
-          <t>저장 버튼 없음 · 참여 실적 줄 없음 · 4기 · 홈 버튼만</t>
+          <t>라벨 "참여기록 저장하기" · 파일명 …_참여기록_…</t>
         </is>
       </c>
       <c r="J24" s="10" t="inlineStr">
         <is>
-          <t>S7-08 · S7-10</t>
+          <t>S7-10 · Q-02</t>
         </is>
       </c>
       <c r="K24" s="14" t="inlineStr">
         <is>
-          <t>cmp_07C.png</t>
+          <t>cmp_07B.png</t>
         </is>
       </c>
       <c r="L24" s="17" t="inlineStr">
@@ -3084,7 +3072,11 @@
           <t>통과</t>
         </is>
       </c>
-      <c r="M24" s="18" t="n"/>
+      <c r="M24" s="18" t="inlineStr">
+        <is>
+          <t>라벨 확인(웹)</t>
+        </is>
+      </c>
       <c r="N24" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
@@ -3100,12 +3092,12 @@
     <row r="25" ht="48" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>C-05</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
@@ -3115,42 +3107,50 @@
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>07 A</t>
+          <t>07 C</t>
         </is>
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
-          <t>①</t>
+          <t>④</t>
         </is>
       </c>
       <c r="F25" s="10" t="inlineStr">
         <is>
-          <t>앱</t>
+          <t>앱 · 웹</t>
         </is>
       </c>
       <c r="G25" s="10" t="inlineStr">
         <is>
-          <t>사진 권한 거부</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>수료증 저장하기</t>
+          <t>증서 화면</t>
         </is>
       </c>
       <c r="I25" s="10" t="inlineStr">
         <is>
-          <t>권한 안내 · 앱이 멈추지 않음</t>
+          <t>저장 버튼 없음 · 참여 실적 줄 없음 · 4기 · 홈 버튼만</t>
         </is>
       </c>
       <c r="J25" s="10" t="inlineStr">
         <is>
-          <t>P15</t>
-        </is>
-      </c>
-      <c r="K25" s="10" t="n"/>
-      <c r="L25" s="4" t="n"/>
-      <c r="M25" s="10" t="n"/>
+          <t>S7-08 · S7-10</t>
+        </is>
+      </c>
+      <c r="K25" s="14" t="inlineStr">
+        <is>
+          <t>cmp_07C.png</t>
+        </is>
+      </c>
+      <c r="L25" s="17" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="M25" s="18" t="n"/>
       <c r="N25" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
@@ -3166,12 +3166,12 @@
     <row r="26" ht="48" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>C-06</t>
+          <t>C-05</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
@@ -3196,22 +3196,22 @@
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>사진 권한 거부</t>
         </is>
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>저장 후</t>
+          <t>수료증 저장하기</t>
         </is>
       </c>
       <c r="I26" s="10" t="inlineStr">
         <is>
-          <t>리포트가 닫히지 않고 그대로</t>
+          <t>권한 안내 · 앱이 멈추지 않음</t>
         </is>
       </c>
       <c r="J26" s="10" t="inlineStr">
         <is>
-          <t>IA-R-10</t>
+          <t>P15</t>
         </is>
       </c>
       <c r="K26" s="10" t="n"/>
@@ -3232,7 +3232,7 @@
     <row r="27" ht="48" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>C-07</t>
+          <t>C-06</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -3257,7 +3257,7 @@
       </c>
       <c r="F27" s="10" t="inlineStr">
         <is>
-          <t>앱 · 웹</t>
+          <t>앱</t>
         </is>
       </c>
       <c r="G27" s="10" t="inlineStr">
@@ -3267,30 +3267,22 @@
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>증서 이름 확인</t>
+          <t>저장 후</t>
         </is>
       </c>
       <c r="I27" s="10" t="inlineStr">
         <is>
-          <t>표지는 마스킹(김*리) · 증서는 원문 이름</t>
+          <t>리포트가 닫히지 않고 그대로</t>
         </is>
       </c>
       <c r="J27" s="10" t="inlineStr">
         <is>
-          <t>S7-06 · P12</t>
-        </is>
-      </c>
-      <c r="K27" s="14" t="inlineStr">
-        <is>
-          <t>cmp_07A.png</t>
-        </is>
-      </c>
-      <c r="L27" s="17" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="M27" s="18" t="n"/>
+          <t>IA-R-10</t>
+        </is>
+      </c>
+      <c r="K27" s="10" t="n"/>
+      <c r="L27" s="4" t="n"/>
+      <c r="M27" s="10" t="n"/>
       <c r="N27" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
@@ -3306,22 +3298,22 @@
     <row r="28" ht="48" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>C-07</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>4 4기 신청</t>
+          <t>3 증서 저장</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>07-h 시트</t>
+          <t>07 A</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr">
@@ -3341,22 +3333,22 @@
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
-          <t>4기도 참여하기</t>
+          <t>증서 이름 확인</t>
         </is>
       </c>
       <c r="I28" s="10" t="inlineStr">
         <is>
-          <t>바텀시트 · 문구는 결정 Q-1대로 · [닫기] [네, 신청합니다]</t>
+          <t>표지는 마스킹(김*리) · 증서는 원문 이름</t>
         </is>
       </c>
       <c r="J28" s="10" t="inlineStr">
         <is>
-          <t>07-h · K-13</t>
+          <t>S7-06 · P12</t>
         </is>
       </c>
       <c r="K28" s="14" t="inlineStr">
         <is>
-          <t>cmp_07h.png</t>
+          <t>cmp_07A.png</t>
         </is>
       </c>
       <c r="L28" s="17" t="inlineStr">
@@ -3364,11 +3356,7 @@
           <t>통과</t>
         </is>
       </c>
-      <c r="M28" s="18" t="inlineStr">
-        <is>
-          <t>목업과 같음 · 명칭에 4기 없음은 결정 Q-1</t>
-        </is>
-      </c>
+      <c r="M28" s="18" t="n"/>
       <c r="N28" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
@@ -3384,7 +3372,7 @@
     <row r="29" ht="48" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>C-08</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
@@ -3394,12 +3382,12 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>4 4기 신청</t>
+          <t>3 증서 저장</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>07-h 시트</t>
+          <t>07 A</t>
         </is>
       </c>
       <c r="E29" s="10" t="inlineStr">
@@ -3419,30 +3407,22 @@
       </c>
       <c r="H29" s="10" t="inlineStr">
         <is>
-          <t>[닫기] / 딤 탭</t>
+          <t>증서 실적 줄을 본다</t>
         </is>
       </c>
       <c r="I29" s="10" t="inlineStr">
         <is>
-          <t>시트만 닫힘 · 신청 저장 안 됨</t>
+          <t>피그마 1241:1395와 같음 — 라벨 '함께한 날' · '참여율' Regular 12 #5C6675 · '/242일' Regular 13 #9AA3AD · 숫자만 ExtraBold 14 #191F28</t>
         </is>
       </c>
       <c r="J29" s="10" t="inlineStr">
         <is>
-          <t>07-h</t>
+          <t>S7-06 · P12</t>
         </is>
       </c>
       <c r="K29" s="10" t="n"/>
-      <c r="L29" s="17" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="M29" s="18" t="inlineStr">
-        <is>
-          <t>[닫기] 확인(웹)</t>
-        </is>
-      </c>
+      <c r="L29" s="4" t="n"/>
+      <c r="M29" s="10" t="n"/>
       <c r="N29" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
@@ -3458,69 +3438,57 @@
     <row r="30" ht="48" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>C-09</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>4 4기 신청</t>
+          <t>3 증서 저장</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>08 완료</t>
+          <t>07-d</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>①</t>
+          <t>이름 없는 계정</t>
         </is>
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>앱 · 웹</t>
+          <t>앱</t>
         </is>
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>닉네임 · 이름 없는 계정 (개발에 요청)</t>
         </is>
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>[네, 신청합니다]</t>
+          <t>표지와 증서를 본다</t>
         </is>
       </c>
       <c r="I30" s="10" t="inlineStr">
         <is>
-          <t>완료 화면 · 본문 4줄 "4기가 시작될 때 보건소에서 연락드리겠습니다. 자세한 문의사항은 032-453-6160으로 문의 바랍니다. 감사합니다."</t>
+          <t>표지 "회원님," · 증서 이름 자리 "회원님" (빈칸 · null 없음)</t>
         </is>
       </c>
       <c r="J30" s="10" t="inlineStr">
         <is>
-          <t>SC-RP-08 · S8-05 · K-14</t>
-        </is>
-      </c>
-      <c r="K30" s="14" t="inlineStr">
-        <is>
-          <t>cmp_08.png</t>
-        </is>
-      </c>
-      <c r="L30" s="17" t="inlineStr">
-        <is>
-          <t>실패</t>
-        </is>
-      </c>
-      <c r="M30" s="18" t="inlineStr">
-        <is>
-          <t>배치는 목업과 같음 · 첫 줄 누락 · 번호 6163 → WEB-1 · 02</t>
-        </is>
-      </c>
+          <t>P12 · 07-d</t>
+        </is>
+      </c>
+      <c r="K30" s="10" t="n"/>
+      <c r="L30" s="4" t="n"/>
+      <c r="M30" s="10" t="n"/>
       <c r="N30" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
@@ -3536,12 +3504,12 @@
     <row r="31" ht="48" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
@@ -3551,7 +3519,7 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>08 완료</t>
+          <t>07-h 시트</t>
         </is>
       </c>
       <c r="E31" s="10" t="inlineStr">
@@ -3561,7 +3529,7 @@
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
-          <t>앱</t>
+          <t>앱 · 웹</t>
         </is>
       </c>
       <c r="G31" s="10" t="inlineStr">
@@ -3571,22 +3539,34 @@
       </c>
       <c r="H31" s="10" t="inlineStr">
         <is>
-          <t>[네, 신청합니다] 연타</t>
+          <t>4기도 참여하기</t>
         </is>
       </c>
       <c r="I31" s="10" t="inlineStr">
         <is>
-          <t>신청 1건만 저장</t>
+          <t>바텀시트 · 문구는 결정 Q-1대로 · [닫기] [네, 신청합니다]</t>
         </is>
       </c>
       <c r="J31" s="10" t="inlineStr">
         <is>
-          <t>IA-R-12</t>
-        </is>
-      </c>
-      <c r="K31" s="10" t="n"/>
-      <c r="L31" s="4" t="n"/>
-      <c r="M31" s="10" t="n"/>
+          <t>07-h · K-13</t>
+        </is>
+      </c>
+      <c r="K31" s="14" t="inlineStr">
+        <is>
+          <t>cmp_07h.png</t>
+        </is>
+      </c>
+      <c r="L31" s="17" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="M31" s="18" t="inlineStr">
+        <is>
+          <t>목업과 같음 · 명칭에 4기 없음은 결정 Q-1</t>
+        </is>
+      </c>
       <c r="N31" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
@@ -3602,12 +3582,12 @@
     <row r="32" ht="48" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>A-05</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
@@ -3617,7 +3597,7 @@
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>07-l</t>
+          <t>07-h 시트</t>
         </is>
       </c>
       <c r="E32" s="10" t="inlineStr">
@@ -3632,29 +3612,25 @@
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>A-03 이후</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
-          <t>홈 → 리포트 다시 열기</t>
+          <t>[닫기] / 딤 탭</t>
         </is>
       </c>
       <c r="I32" s="10" t="inlineStr">
         <is>
-          <t>4기 버튼 비활성 + "4기 신청이 완료되었습니다"</t>
+          <t>시트만 닫힘 · 신청 저장 안 됨</t>
         </is>
       </c>
       <c r="J32" s="10" t="inlineStr">
         <is>
-          <t>07-l · IA-R-12</t>
-        </is>
-      </c>
-      <c r="K32" s="14" t="inlineStr">
-        <is>
-          <t>cmp_07l.png</t>
-        </is>
-      </c>
+          <t>07-h</t>
+        </is>
+      </c>
+      <c r="K32" s="10" t="n"/>
       <c r="L32" s="17" t="inlineStr">
         <is>
           <t>통과</t>
@@ -3662,7 +3638,7 @@
       </c>
       <c r="M32" s="18" t="inlineStr">
         <is>
-          <t>state=07l · 목업과 같음</t>
+          <t>[닫기] 확인(웹)</t>
         </is>
       </c>
       <c r="N32" s="15" t="inlineStr">
@@ -3680,7 +3656,7 @@
     <row r="33" ht="48" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>A-06</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
@@ -3695,7 +3671,7 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>07-l</t>
+          <t>08 완료</t>
         </is>
       </c>
       <c r="E33" s="10" t="inlineStr">
@@ -3705,32 +3681,44 @@
       </c>
       <c r="F33" s="10" t="inlineStr">
         <is>
-          <t>앱</t>
+          <t>앱 · 웹</t>
         </is>
       </c>
       <c r="G33" s="10" t="inlineStr">
         <is>
-          <t>A-03 이후</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H33" s="10" t="inlineStr">
         <is>
-          <t>다른 폰에서 같은 계정 로그인</t>
+          <t>[네, 신청합니다]</t>
         </is>
       </c>
       <c r="I33" s="10" t="inlineStr">
         <is>
-          <t>07-l 상태 그대로 (서버 값 기준)</t>
+          <t>완료 화면 · 본문 4줄 "4기가 시작될 때 보건소에서 연락드리겠습니다. 자세한 문의사항은 032-453-6160으로 문의 바랍니다. 감사합니다."</t>
         </is>
       </c>
       <c r="J33" s="10" t="inlineStr">
         <is>
-          <t>apply.season4_applied</t>
-        </is>
-      </c>
-      <c r="K33" s="10" t="n"/>
-      <c r="L33" s="4" t="n"/>
-      <c r="M33" s="10" t="n"/>
+          <t>SC-RP-08 · S8-05 · K-14</t>
+        </is>
+      </c>
+      <c r="K33" s="14" t="inlineStr">
+        <is>
+          <t>cmp_08.png</t>
+        </is>
+      </c>
+      <c r="L33" s="17" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="M33" s="18" t="inlineStr">
+        <is>
+          <t>배치는 목업과 같음 · 첫 줄 누락 · 번호 6163 → WEB-1 · 02</t>
+        </is>
+      </c>
       <c r="N33" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
@@ -3746,7 +3734,7 @@
     <row r="34" ht="48" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>A-07</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
@@ -3761,7 +3749,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>08-a 실패</t>
+          <t>07-l</t>
         </is>
       </c>
       <c r="E34" s="10" t="inlineStr">
@@ -3771,38 +3759,42 @@
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
-          <t>앱</t>
+          <t>앱 · 웹</t>
         </is>
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>비행기 모드</t>
+          <t>A-03 이후</t>
         </is>
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
-          <t>[네, 신청합니다]</t>
+          <t>홈 → 리포트 다시 열기</t>
         </is>
       </c>
       <c r="I34" s="10" t="inlineStr">
         <is>
-          <t>실패 화면 · 제목은 FIG-03 결정대로 · 032-453-6160 · [다시 시도] 누르면 확인 없이 자동 재신청</t>
+          <t>4기 버튼 비활성 + "4기 신청이 완료되었습니다"</t>
         </is>
       </c>
       <c r="J34" s="10" t="inlineStr">
         <is>
-          <t>08-a · S8-06</t>
-        </is>
-      </c>
-      <c r="K34" s="10" t="n"/>
+          <t>07-l · IA-R-12</t>
+        </is>
+      </c>
+      <c r="K34" s="14" t="inlineStr">
+        <is>
+          <t>cmp_07l.png</t>
+        </is>
+      </c>
       <c r="L34" s="17" t="inlineStr">
         <is>
-          <t>미실행</t>
+          <t>통과</t>
         </is>
       </c>
       <c r="M34" s="18" t="inlineStr">
         <is>
-          <t>웹 샘플 없음 → 개발에 state=08a 요청</t>
+          <t>state=07l · 목업과 같음</t>
         </is>
       </c>
       <c r="N34" s="15" t="inlineStr">
@@ -3820,12 +3812,12 @@
     <row r="35" ht="48" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>A-08</t>
+          <t>A-05</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
@@ -3835,12 +3827,12 @@
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>07-l</t>
+          <t>08-a 실패</t>
         </is>
       </c>
       <c r="E35" s="10" t="inlineStr">
         <is>
-          <t>②</t>
+          <t>①</t>
         </is>
       </c>
       <c r="F35" s="10" t="inlineStr">
@@ -3850,27 +3842,35 @@
       </c>
       <c r="G35" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>비행기 모드</t>
         </is>
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
-          <t>리포트 열기</t>
+          <t>[네, 신청합니다]</t>
         </is>
       </c>
       <c r="I35" s="10" t="inlineStr">
         <is>
-          <t>처음부터 07-l</t>
+          <t>실패 화면 · 제목은 FIG-03 결정대로 · 032-453-6160 · [다시 시도] 누르면 확인 없이 자동 재신청</t>
         </is>
       </c>
       <c r="J35" s="10" t="inlineStr">
         <is>
-          <t>07-l</t>
+          <t>08-a · S8-06</t>
         </is>
       </c>
       <c r="K35" s="10" t="n"/>
-      <c r="L35" s="4" t="n"/>
-      <c r="M35" s="10" t="n"/>
+      <c r="L35" s="17" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+      <c r="M35" s="18" t="inlineStr">
+        <is>
+          <t>웹 샘플 없음 → 개발에 state=08a 요청</t>
+        </is>
+      </c>
       <c r="N35" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
@@ -3886,12 +3886,12 @@
     <row r="36" ht="48" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>A-09</t>
+          <t>A-06</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
@@ -3901,12 +3901,12 @@
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>07-m</t>
+          <t>07-l</t>
         </is>
       </c>
       <c r="E36" s="10" t="inlineStr">
         <is>
-          <t>⑤</t>
+          <t>②</t>
         </is>
       </c>
       <c r="F36" s="10" t="inlineStr">
@@ -3921,17 +3921,17 @@
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
-          <t>증서 화면</t>
+          <t>리포트 열기</t>
         </is>
       </c>
       <c r="I36" s="10" t="inlineStr">
         <is>
-          <t>4기 버튼 없음</t>
+          <t>처음부터 07-l</t>
         </is>
       </c>
       <c r="J36" s="10" t="inlineStr">
         <is>
-          <t>07-m</t>
+          <t>07-l</t>
         </is>
       </c>
       <c r="K36" s="10" t="n"/>
@@ -3952,12 +3952,12 @@
     <row r="37" ht="48" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>A-10</t>
+          <t>A-07</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>노출 시점</t>
+          <t>07-m</t>
         </is>
       </c>
       <c r="E37" s="10" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>⑤</t>
         </is>
       </c>
       <c r="F37" s="10" t="inlineStr">
@@ -3982,22 +3982,22 @@
       </c>
       <c r="G37" s="10" t="inlineStr">
         <is>
-          <t>10/27 출시 빌드</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
-          <t>출시 전 · 후 버튼 노출</t>
+          <t>증서 화면</t>
         </is>
       </c>
       <c r="I37" s="10" t="inlineStr">
         <is>
-          <t>10/27부터 노출</t>
+          <t>4기 버튼 없음</t>
         </is>
       </c>
       <c r="J37" s="10" t="inlineStr">
         <is>
-          <t>S7-11</t>
+          <t>07-m</t>
         </is>
       </c>
       <c r="K37" s="10" t="n"/>
@@ -4018,27 +4018,27 @@
     <row r="38" ht="48" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>X-01</t>
+          <t>A-08</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>5 닫기 · 뒤로가기</t>
+          <t>4 4기 신청</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>노출 시점</t>
         </is>
       </c>
       <c r="E38" s="10" t="inlineStr">
         <is>
-          <t>①</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="F38" s="10" t="inlineStr">
@@ -4048,22 +4048,22 @@
       </c>
       <c r="G38" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10/27 출시 빌드</t>
         </is>
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
-          <t>아무 섹션에서 ✕</t>
+          <t>출시 전 · 후 버튼 노출</t>
         </is>
       </c>
       <c r="I38" s="10" t="inlineStr">
         <is>
-          <t>홈으로 복귀</t>
+          <t>10/27부터 노출</t>
         </is>
       </c>
       <c r="J38" s="10" t="inlineStr">
         <is>
-          <t>IA-R-05</t>
+          <t>S7-11</t>
         </is>
       </c>
       <c r="K38" s="10" t="n"/>
@@ -4084,7 +4084,7 @@
     <row r="39" ht="48" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>X-02</t>
+          <t>X-01</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="F39" s="10" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>앱</t>
         </is>
       </c>
       <c r="G39" s="10" t="inlineStr">
@@ -4119,12 +4119,12 @@
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
-          <t>리포트 / 시트 열림 / 완료 화면에서 뒤로가기</t>
+          <t>아무 섹션에서 ✕</t>
         </is>
       </c>
       <c r="I39" s="10" t="inlineStr">
         <is>
-          <t>시트가 열려 있으면 시트만 닫힘 · 그 외 홈</t>
+          <t>홈으로 복귀</t>
         </is>
       </c>
       <c r="J39" s="10" t="inlineStr">
@@ -4150,12 +4150,12 @@
     <row r="40" ht="48" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>X-03</t>
+          <t>X-02</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
@@ -4175,7 +4175,7 @@
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>iOS</t>
+          <t>Android</t>
         </is>
       </c>
       <c r="G40" s="10" t="inlineStr">
@@ -4185,17 +4185,17 @@
       </c>
       <c r="H40" s="10" t="inlineStr">
         <is>
-          <t>밀어서 닫기</t>
+          <t>리포트 / 시트 열림 / 완료 화면에서 뒤로가기</t>
         </is>
       </c>
       <c r="I40" s="10" t="inlineStr">
         <is>
-          <t>홈 복귀 · 화면 깨짐 없음</t>
+          <t>시트가 열려 있으면 시트만 닫힘 · 그 외 홈</t>
         </is>
       </c>
       <c r="J40" s="10" t="inlineStr">
         <is>
-          <t>개발 B-7</t>
+          <t>IA-R-05</t>
         </is>
       </c>
       <c r="K40" s="10" t="n"/>
@@ -4216,7 +4216,7 @@
     <row r="41" ht="48" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>X-04</t>
+          <t>X-03</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>08 완료</t>
+          <t>공통</t>
         </is>
       </c>
       <c r="E41" s="10" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
-          <t>앱</t>
+          <t>iOS</t>
         </is>
       </c>
       <c r="G41" s="10" t="inlineStr">
@@ -4251,26 +4251,22 @@
       </c>
       <c r="H41" s="10" t="inlineStr">
         <is>
-          <t>[홈으로 돌아가기]</t>
+          <t>밀어서 닫기</t>
         </is>
       </c>
       <c r="I41" s="10" t="inlineStr">
         <is>
-          <t>홈 복귀</t>
+          <t>홈 복귀 · 화면 깨짐 없음</t>
         </is>
       </c>
       <c r="J41" s="10" t="inlineStr">
         <is>
-          <t>S8-07</t>
+          <t>개발 B-7</t>
         </is>
       </c>
       <c r="K41" s="10" t="n"/>
       <c r="L41" s="4" t="n"/>
-      <c r="M41" s="10" t="inlineStr">
-        <is>
-          <t>웹에서는 동작 안 하는 게 정상</t>
-        </is>
-      </c>
+      <c r="M41" s="10" t="n"/>
       <c r="N41" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
@@ -4286,7 +4282,7 @@
     <row r="42" ht="48" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>T-01</t>
+          <t>X-04</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
@@ -4296,17 +4292,17 @@
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>6 4기 전환</t>
+          <t>5 닫기 · 뒤로가기</t>
         </is>
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>체험 홈</t>
+          <t>08 완료</t>
         </is>
       </c>
       <c r="E42" s="10" t="inlineStr">
         <is>
-          <t>4기 승인 계정</t>
+          <t>①</t>
         </is>
       </c>
       <c r="F42" s="10" t="inlineStr">
@@ -4316,27 +4312,31 @@
       </c>
       <c r="G42" s="10" t="inlineStr">
         <is>
-          <t>개발에 4기 시작일 당겨 달라고 요청</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H42" s="10" t="inlineStr">
         <is>
-          <t>4기 홈 전환 후 확인</t>
+          <t>[홈으로 돌아가기]</t>
         </is>
       </c>
       <c r="I42" s="10" t="inlineStr">
         <is>
-          <t>리포트 카드 사라짐 · 진행 내역으로는 열림</t>
+          <t>홈 복귀</t>
         </is>
       </c>
       <c r="J42" s="10" t="inlineStr">
         <is>
-          <t>IA-R-08 · F4</t>
+          <t>S8-07</t>
         </is>
       </c>
       <c r="K42" s="10" t="n"/>
       <c r="L42" s="4" t="n"/>
-      <c r="M42" s="10" t="n"/>
+      <c r="M42" s="10" t="inlineStr">
+        <is>
+          <t>웹에서는 동작 안 하는 게 정상</t>
+        </is>
+      </c>
       <c r="N42" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
@@ -4352,7 +4352,7 @@
     <row r="43" ht="48" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>M-01</t>
+          <t>T-01</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
@@ -4362,17 +4362,17 @@
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>6 측정</t>
+          <t>6 4기 전환</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>이벤트</t>
+          <t>체험 홈</t>
         </is>
       </c>
       <c r="E43" s="10" t="inlineStr">
         <is>
-          <t>①</t>
+          <t>4기 승인 계정</t>
         </is>
       </c>
       <c r="F43" s="10" t="inlineStr">
@@ -4382,35 +4382,27 @@
       </c>
       <c r="G43" s="10" t="inlineStr">
         <is>
-          <t>개발에 이벤트 로그 확인 요청</t>
+          <t>개발에 4기 시작일 당겨 달라고 요청</t>
         </is>
       </c>
       <c r="H43" s="10" t="inlineStr">
         <is>
-          <t>카드 / 자동 팝업 / 진행 내역으로 각각 진입</t>
+          <t>4기 홈 전환 후 확인</t>
         </is>
       </c>
       <c r="I43" s="10" t="inlineStr">
         <is>
-          <t>entry 값이 경로별로 다르게 남음 · programId 채워짐</t>
+          <t>리포트 카드 사라짐 · 진행 내역으로는 열림</t>
         </is>
       </c>
       <c r="J43" s="10" t="inlineStr">
         <is>
-          <t>IA-Q-06 · 개발 D-4</t>
+          <t>IA-R-08 · F4</t>
         </is>
       </c>
       <c r="K43" s="10" t="n"/>
-      <c r="L43" s="17" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="M43" s="18" t="inlineStr">
-        <is>
-          <t>웹 샘플은 entry=manual · programId 빈 값</t>
-        </is>
-      </c>
+      <c r="L43" s="4" t="n"/>
+      <c r="M43" s="10" t="n"/>
       <c r="N43" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
@@ -4426,7 +4418,7 @@
     <row r="44" ht="48" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>M-02</t>
+          <t>M-01</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
@@ -4456,33 +4448,33 @@
       </c>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>개발에 이벤트 로그 확인 요청</t>
         </is>
       </c>
       <c r="H44" s="10" t="inlineStr">
         <is>
-          <t>한 섹션에 30초 머문 뒤 이동</t>
+          <t>카드 / 자동 팝업 / 진행 내역으로 각각 진입</t>
         </is>
       </c>
       <c r="I44" s="10" t="inlineStr">
         <is>
-          <t>해당 섹션 dwell ≈ 30초</t>
+          <t>entry 값이 경로별로 다르게 남음 · programId 채워짐</t>
         </is>
       </c>
       <c r="J44" s="10" t="inlineStr">
         <is>
-          <t>IA-Q-06</t>
+          <t>IA-Q-06 · 개발 D-4</t>
         </is>
       </c>
       <c r="K44" s="10" t="n"/>
       <c r="L44" s="17" t="inlineStr">
         <is>
-          <t>통과</t>
+          <t>보류</t>
         </is>
       </c>
       <c r="M44" s="18" t="inlineStr">
         <is>
-          <t>웹에서 section_view/leave + dwellMs 발생 확인</t>
+          <t>웹 샘플은 entry=manual · programId 빈 값</t>
         </is>
       </c>
       <c r="N44" s="15" t="inlineStr">
@@ -4500,22 +4492,22 @@
     <row r="45" ht="48" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>PH-01</t>
+          <t>M-02</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>6 전화번호</t>
+          <t>6 측정</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t>전 화면</t>
+          <t>이벤트</t>
         </is>
       </c>
       <c r="E45" s="10" t="inlineStr">
@@ -4525,42 +4517,38 @@
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
-          <t>앱 · 웹 · 문자</t>
+          <t>앱</t>
         </is>
       </c>
       <c r="G45" s="10" t="inlineStr">
         <is>
-          <t>개발 수정 반영 후</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H45" s="10" t="inlineStr">
         <is>
-          <t>리포트 완료 · 실패 화면 · 신청폼 결과 화면 · 문자 본문의 번호</t>
+          <t>한 섹션에 30초 머문 뒤 이동</t>
         </is>
       </c>
       <c r="I45" s="10" t="inlineStr">
         <is>
-          <t>모두 032-453-6160 (6163 · 담당자 번호 없음)</t>
+          <t>해당 섹션 dwell ≈ 30초</t>
         </is>
       </c>
       <c r="J45" s="10" t="inlineStr">
         <is>
-          <t>K-14 · 보건소 요청 10/12</t>
-        </is>
-      </c>
-      <c r="K45" s="14" t="inlineStr">
-        <is>
-          <t>cmp_08.png</t>
-        </is>
-      </c>
+          <t>IA-Q-06</t>
+        </is>
+      </c>
+      <c r="K45" s="10" t="n"/>
       <c r="L45" s="17" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>통과</t>
         </is>
       </c>
       <c r="M45" s="18" t="inlineStr">
         <is>
-          <t>완료 화면 032-453-6163 → WEB-1</t>
+          <t>웹에서 section_view/leave + dwellMs 발생 확인</t>
         </is>
       </c>
       <c r="N45" s="15" t="inlineStr">
@@ -4578,67 +4566,67 @@
     <row r="46" ht="48" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>PH-01</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>6 신청폼 4기</t>
+          <t>6 전화번호</t>
         </is>
       </c>
       <c r="D46" s="10" t="inlineStr">
         <is>
-          <t>첫 화면</t>
+          <t>전 화면</t>
         </is>
       </c>
       <c r="E46" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>①</t>
         </is>
       </c>
       <c r="F46" s="10" t="inlineStr">
         <is>
-          <t>휴대폰 브라우저</t>
+          <t>앱</t>
         </is>
       </c>
       <c r="G46" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>개발 수정 반영 후</t>
         </is>
       </c>
       <c r="H46" s="10" t="inlineStr">
         <is>
-          <t>/invitations/namdong4</t>
+          <t>리포트 완료(08) · 실패(08-a) 화면의 문의 번호</t>
         </is>
       </c>
       <c r="I46" s="10" t="inlineStr">
         <is>
-          <t>명칭 · 기관명은 결정 Q-1 · Q-2대로 · "2027년 2월~11월"</t>
+          <t>모두 032-453-6160 (6163 · 담당자 번호 없음)</t>
         </is>
       </c>
       <c r="J46" s="10" t="inlineStr">
         <is>
-          <t>개발 B-8</t>
+          <t>K-14 · 보건소 요청 10/12</t>
         </is>
       </c>
       <c r="K46" s="14" t="inlineStr">
         <is>
-          <t>dev_form4_landing.png</t>
+          <t>cmp_08.png</t>
         </is>
       </c>
       <c r="L46" s="17" t="inlineStr">
         <is>
-          <t>보류</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="M46" s="18" t="inlineStr">
         <is>
-          <t>"인천 남동구 보건소 x 맬리 · 치매예방교실 4기" → Q-1 · Q-2</t>
+          <t>완료 화면 032-453-6163 → WEB-1</t>
         </is>
       </c>
       <c r="N46" s="15" t="inlineStr">
@@ -4656,69 +4644,57 @@
     <row r="47" ht="48" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>6 신청폼 4기</t>
+          <t>7 글꼴</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>입력 · 결과</t>
+          <t>전 화면</t>
         </is>
       </c>
       <c r="E47" s="10" t="inlineStr">
         <is>
-          <t>본인 번호</t>
+          <t>②</t>
         </is>
       </c>
       <c r="F47" s="10" t="inlineStr">
         <is>
-          <t>휴대폰 브라우저</t>
+          <t>앱</t>
         </is>
       </c>
       <c r="G47" s="10" t="inlineStr">
         <is>
-          <t>실제 문자 발송 — 본인 번호로 1회만</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
-          <t>입력 폼 제출</t>
+          <t>표지부터 완료 화면까지 글꼴을 본다 (증서 제목 · 이름 · 03 요일 차트 · 로딩 · 오류 · 비대상 · 0점/100점 · 저장 실패 토스트)</t>
         </is>
       </c>
       <c r="I47" s="10" t="inlineStr">
         <is>
-          <t>결과 화면 문구 · 문자 내용 · 케어센터 신청자 관리에 1건</t>
+          <t>모든 글자가 Pretendard (세리프 · Inter · 시스템 기본 글꼴 없음)</t>
         </is>
       </c>
       <c r="J47" s="10" t="inlineStr">
         <is>
-          <t>개발 B-8 · Q-3</t>
-        </is>
-      </c>
-      <c r="K47" s="14" t="inlineStr">
-        <is>
-          <t>dev_form4_form.png</t>
-        </is>
-      </c>
-      <c r="L47" s="17" t="inlineStr">
-        <is>
-          <t>미실행</t>
-        </is>
-      </c>
-      <c r="M47" s="18" t="inlineStr">
-        <is>
-          <t>제출 금지 조건으로 미실행 · 입력 폼 "신청하면 바로 참여가 확정" → Q-3</t>
-        </is>
-      </c>
+          <t>10/12 기획 결정 · 변경이력 42</t>
+        </is>
+      </c>
+      <c r="K47" s="10" t="n"/>
+      <c r="L47" s="4" t="n"/>
+      <c r="M47" s="10" t="n"/>
       <c r="N47" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
@@ -4731,285 +4707,9 @@
       <c r="S47" s="15" t="n"/>
       <c r="T47" s="15" t="n"/>
     </row>
-    <row r="48" ht="48" customHeight="1">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>F-03</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C48" s="10" t="inlineStr">
-        <is>
-          <t>6 신청폼 4기</t>
-        </is>
-      </c>
-      <c r="D48" s="10" t="inlineStr">
-        <is>
-          <t>중복</t>
-        </is>
-      </c>
-      <c r="E48" s="10" t="inlineStr">
-        <is>
-          <t>본인 번호</t>
-        </is>
-      </c>
-      <c r="F48" s="10" t="inlineStr">
-        <is>
-          <t>휴대폰 브라우저</t>
-        </is>
-      </c>
-      <c r="G48" s="10" t="inlineStr">
-        <is>
-          <t>F-02 이후</t>
-        </is>
-      </c>
-      <c r="H48" s="10" t="inlineStr">
-        <is>
-          <t>같은 번호로 다시 제출</t>
-        </is>
-      </c>
-      <c r="I48" s="10" t="inlineStr">
-        <is>
-          <t>중복 안내 (정의 없음 → Q-4)</t>
-        </is>
-      </c>
-      <c r="J48" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K48" s="10" t="n"/>
-      <c r="L48" s="4" t="n"/>
-      <c r="M48" s="10" t="n"/>
-      <c r="N48" s="15" t="inlineStr">
-        <is>
-          <t>미실행</t>
-        </is>
-      </c>
-      <c r="O48" s="15" t="n"/>
-      <c r="P48" s="16" t="n"/>
-      <c r="Q48" s="15" t="n"/>
-      <c r="R48" s="16" t="n"/>
-      <c r="S48" s="15" t="n"/>
-      <c r="T48" s="15" t="n"/>
-    </row>
-    <row r="49" ht="48" customHeight="1">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>F-04</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="C49" s="10" t="inlineStr">
-        <is>
-          <t>6 신청폼 4기</t>
-        </is>
-      </c>
-      <c r="D49" s="10" t="inlineStr">
-        <is>
-          <t>대리 등록</t>
-        </is>
-      </c>
-      <c r="E49" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F49" s="10" t="inlineStr">
-        <is>
-          <t>휴대폰 브라우저</t>
-        </is>
-      </c>
-      <c r="G49" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H49" s="10" t="inlineStr">
-        <is>
-          <t>"보건소 직원이신가요?"</t>
-        </is>
-      </c>
-      <c r="I49" s="10" t="inlineStr">
-        <is>
-          <t>대리 등록 경로가 열림 (제출하지 않음)</t>
-        </is>
-      </c>
-      <c r="J49" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K49" s="10" t="n"/>
-      <c r="L49" s="4" t="n"/>
-      <c r="M49" s="10" t="n"/>
-      <c r="N49" s="15" t="inlineStr">
-        <is>
-          <t>미실행</t>
-        </is>
-      </c>
-      <c r="O49" s="15" t="n"/>
-      <c r="P49" s="16" t="n"/>
-      <c r="Q49" s="15" t="n"/>
-      <c r="R49" s="16" t="n"/>
-      <c r="S49" s="15" t="n"/>
-      <c r="T49" s="15" t="n"/>
-    </row>
-    <row r="50" ht="48" customHeight="1">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>F-05</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C50" s="10" t="inlineStr">
-        <is>
-          <t>6 신청폼 3기</t>
-        </is>
-      </c>
-      <c r="D50" s="10" t="inlineStr">
-        <is>
-          <t>3기 링크</t>
-        </is>
-      </c>
-      <c r="E50" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F50" s="10" t="inlineStr">
-        <is>
-          <t>휴대폰 브라우저</t>
-        </is>
-      </c>
-      <c r="G50" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H50" s="10" t="inlineStr">
-        <is>
-          <t>/invitations/namdong3</t>
-        </is>
-      </c>
-      <c r="I50" s="10" t="inlineStr">
-        <is>
-          <t>결정 Q-6대로</t>
-        </is>
-      </c>
-      <c r="J50" s="10" t="inlineStr">
-        <is>
-          <t>개발 §A ⑤</t>
-        </is>
-      </c>
-      <c r="K50" s="14" t="inlineStr">
-        <is>
-          <t>dev_form3_landing.png</t>
-        </is>
-      </c>
-      <c r="L50" s="17" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="M50" s="18" t="inlineStr">
-        <is>
-          <t>지금은 3기 첫 화면 정상 노출</t>
-        </is>
-      </c>
-      <c r="N50" s="15" t="inlineStr">
-        <is>
-          <t>미실행</t>
-        </is>
-      </c>
-      <c r="O50" s="15" t="n"/>
-      <c r="P50" s="16" t="n"/>
-      <c r="Q50" s="15" t="n"/>
-      <c r="R50" s="16" t="n"/>
-      <c r="S50" s="15" t="n"/>
-      <c r="T50" s="15" t="n"/>
-    </row>
-    <row r="51" ht="48" customHeight="1">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>K-01</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C51" s="10" t="inlineStr">
-        <is>
-          <t>6 케어센터</t>
-        </is>
-      </c>
-      <c r="D51" s="10" t="inlineStr">
-        <is>
-          <t>4기</t>
-        </is>
-      </c>
-      <c r="E51" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F51" s="10" t="inlineStr">
-        <is>
-          <t>PC</t>
-        </is>
-      </c>
-      <c r="G51" s="10" t="inlineStr">
-        <is>
-          <t>로그인</t>
-        </is>
-      </c>
-      <c r="H51" s="10" t="inlineStr">
-        <is>
-          <t>목록 · 신청자 관리</t>
-        </is>
-      </c>
-      <c r="I51" s="10" t="inlineStr">
-        <is>
-          <t>4기 "진행 예정" · 신청자 관리 탭 열림</t>
-        </is>
-      </c>
-      <c r="J51" s="10" t="inlineStr">
-        <is>
-          <t>개발 B-9</t>
-        </is>
-      </c>
-      <c r="K51" s="10" t="n"/>
-      <c r="L51" s="4" t="n"/>
-      <c r="M51" s="10" t="n"/>
-      <c r="N51" s="15" t="inlineStr">
-        <is>
-          <t>미실행</t>
-        </is>
-      </c>
-      <c r="O51" s="15" t="n"/>
-      <c r="P51" s="16" t="n"/>
-      <c r="Q51" s="15" t="n"/>
-      <c r="R51" s="16" t="n"/>
-      <c r="S51" s="15" t="n"/>
-      <c r="T51" s="15" t="n"/>
-    </row>
   </sheetData>
   <autoFilter ref="A1:T1"/>
-  <conditionalFormatting sqref="L2:L51">
+  <conditionalFormatting sqref="L2:L47">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"실패"</formula>
     </cfRule>
@@ -5017,7 +4717,7 @@
       <formula>"통과"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N51">
+  <conditionalFormatting sqref="N2:N47">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="0">
       <formula>"실패"</formula>
     </cfRule>
@@ -5025,7 +4725,7 @@
       <formula>"통과"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O51">
+  <conditionalFormatting sqref="O2:O47">
     <cfRule type="cellIs" priority="5" operator="equal" dxfId="0">
       <formula>"실패"</formula>
     </cfRule>
@@ -5033,16 +4733,16 @@
       <formula>"통과"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B51">
+  <conditionalFormatting sqref="B2:B47">
     <cfRule type="cellIs" priority="7" operator="equal" dxfId="2">
       <formula>"P1"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="N2:O51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N2:O47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"미실행,통과,실패,보류,해당없음"</formula1>
     </dataValidation>
-    <dataValidation sqref="L2:L51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L2:L47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"통과,실패,보류,미실행"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5057,17 +4757,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5233,7 +4930,7 @@
       </c>
       <c r="M2" s="10" t="inlineStr">
         <is>
-          <t>PH-01 · A-03 · A-07</t>
+          <t>PH-01 · A-03 · A-05</t>
         </is>
       </c>
       <c r="N2" s="16" t="n"/>
@@ -6826,7 +6523,7 @@
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>A-09</t>
+          <t>A-07</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -6880,7 +6577,7 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>A-03 · A-06</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -6934,7 +6631,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>A-07 · S-06 · S-07</t>
+          <t>A-05 · S-06 · S-07</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">

--- a/qa/3기리포트_QA_TC.xlsx
+++ b/qa/3기리포트_QA_TC.xlsx
@@ -1684,12 +1684,12 @@
       </c>
       <c r="I5" s="10" t="inlineStr">
         <is>
-          <t>리포트가 표지부터 열린다</t>
+          <t>성과 탭이 아니라 리포트가 표지부터 열린다</t>
         </is>
       </c>
       <c r="J5" s="10" t="inlineStr">
         <is>
-          <t>F4 · IA-R-07</t>
+          <t>F4 · IA-R-07 · 변경이력 43</t>
         </is>
       </c>
       <c r="K5" s="10" t="n"/>
@@ -3468,17 +3468,17 @@
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>닉네임 · 이름 없는 계정 (개발에 요청)</t>
+          <t>닉네임 · 이름이 모두 빈 3기 리포트 대상 계정 (개발 요청 · A 수료)</t>
         </is>
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>표지와 증서를 본다</t>
+          <t>표지 · 랭킹 · 증서를 보고 수료증을 저장한다</t>
         </is>
       </c>
       <c r="I30" s="10" t="inlineStr">
         <is>
-          <t>표지 "회원님," · 증서 이름 자리 "회원님" (빈칸 · null 없음)</t>
+          <t>표지 "회원님," · 랭킹 내 행 · 증서 이름 자리 "회원님" ("회원님 님" · 빈칸 · null 없음) · 파일명에 빈 이름 없음</t>
         </is>
       </c>
       <c r="J30" s="10" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="I43" s="10" t="inlineStr">
         <is>
-          <t>리포트 카드 사라짐 · 진행 내역으로는 열림</t>
+          <t>홈 자동 전환 · 리포트 카드 사라짐 · 내 정보 &gt; 진행 내역 &gt; 3기 항목으로는 리포트 열림</t>
         </is>
       </c>
       <c r="J43" s="10" t="inlineStr">
@@ -6377,7 +6377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6641,6 +6641,33 @@
       </c>
       <c r="F9" s="15" t="n"/>
       <c r="G9" s="16" t="n"/>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>닉네임 · 이름이 모두 빈 3기 리포트 대상 테스트 계정 1개 (A 수료 · 랭킹 데이터 있음)</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>"회원님" 표기 확인 (P12)</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>C-09</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="n"/>
+      <c r="G10" s="16" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:G1"/>

--- a/qa/3기리포트_QA_TC.xlsx
+++ b/qa/3기리포트_QA_TC.xlsx
@@ -1042,23 +1042,23 @@
         </is>
       </c>
       <c r="C5" s="4">
-        <f>COUNTIF(TC!$B$2:$B$47,A5)</f>
+        <f>COUNTIF(TC!$B$2:$B$48,A5)</f>
         <v/>
       </c>
       <c r="D5" s="4">
-        <f>COUNTIFS(TC!$B$2:$B$47,A5,TC!$N$2:$N$47,"통과")</f>
+        <f>COUNTIFS(TC!$B$2:$B$48,A5,TC!$N$2:$N$48,"통과")</f>
         <v/>
       </c>
       <c r="E5" s="4">
-        <f>COUNTIFS(TC!$B$2:$B$47,A5,TC!$N$2:$N$47,"실패")</f>
+        <f>COUNTIFS(TC!$B$2:$B$48,A5,TC!$N$2:$N$48,"실패")</f>
         <v/>
       </c>
       <c r="F5" s="4">
-        <f>COUNTIFS(TC!$B$2:$B$47,A5,TC!$N$2:$N$47,"보류")</f>
+        <f>COUNTIFS(TC!$B$2:$B$48,A5,TC!$N$2:$N$48,"보류")</f>
         <v/>
       </c>
       <c r="G5" s="4">
-        <f>C5-D5-E5-F5-COUNTIFS(TC!$B$2:$B$47,A5,TC!$N$2:$N$47,"해당없음")</f>
+        <f>C5-D5-E5-F5-COUNTIFS(TC!$B$2:$B$48,A5,TC!$N$2:$N$48,"해당없음")</f>
         <v/>
       </c>
       <c r="H5" s="5">
@@ -1078,23 +1078,23 @@
         </is>
       </c>
       <c r="C6" s="4">
-        <f>COUNTIF(TC!$B$2:$B$47,A6)</f>
+        <f>COUNTIF(TC!$B$2:$B$48,A6)</f>
         <v/>
       </c>
       <c r="D6" s="4">
-        <f>COUNTIFS(TC!$B$2:$B$47,A6,TC!$N$2:$N$47,"통과")</f>
+        <f>COUNTIFS(TC!$B$2:$B$48,A6,TC!$N$2:$N$48,"통과")</f>
         <v/>
       </c>
       <c r="E6" s="4">
-        <f>COUNTIFS(TC!$B$2:$B$47,A6,TC!$N$2:$N$47,"실패")</f>
+        <f>COUNTIFS(TC!$B$2:$B$48,A6,TC!$N$2:$N$48,"실패")</f>
         <v/>
       </c>
       <c r="F6" s="4">
-        <f>COUNTIFS(TC!$B$2:$B$47,A6,TC!$N$2:$N$47,"보류")</f>
+        <f>COUNTIFS(TC!$B$2:$B$48,A6,TC!$N$2:$N$48,"보류")</f>
         <v/>
       </c>
       <c r="G6" s="4">
-        <f>C6-D6-E6-F6-COUNTIFS(TC!$B$2:$B$47,A6,TC!$N$2:$N$47,"해당없음")</f>
+        <f>C6-D6-E6-F6-COUNTIFS(TC!$B$2:$B$48,A6,TC!$N$2:$N$48,"해당없음")</f>
         <v/>
       </c>
       <c r="H6" s="5">
@@ -1114,23 +1114,23 @@
         </is>
       </c>
       <c r="C7" s="4">
-        <f>COUNTIF(TC!$B$2:$B$47,A7)</f>
+        <f>COUNTIF(TC!$B$2:$B$48,A7)</f>
         <v/>
       </c>
       <c r="D7" s="4">
-        <f>COUNTIFS(TC!$B$2:$B$47,A7,TC!$N$2:$N$47,"통과")</f>
+        <f>COUNTIFS(TC!$B$2:$B$48,A7,TC!$N$2:$N$48,"통과")</f>
         <v/>
       </c>
       <c r="E7" s="4">
-        <f>COUNTIFS(TC!$B$2:$B$47,A7,TC!$N$2:$N$47,"실패")</f>
+        <f>COUNTIFS(TC!$B$2:$B$48,A7,TC!$N$2:$N$48,"실패")</f>
         <v/>
       </c>
       <c r="F7" s="4">
-        <f>COUNTIFS(TC!$B$2:$B$47,A7,TC!$N$2:$N$47,"보류")</f>
+        <f>COUNTIFS(TC!$B$2:$B$48,A7,TC!$N$2:$N$48,"보류")</f>
         <v/>
       </c>
       <c r="G7" s="4">
-        <f>C7-D7-E7-F7-COUNTIFS(TC!$B$2:$B$47,A7,TC!$N$2:$N$47,"해당없음")</f>
+        <f>C7-D7-E7-F7-COUNTIFS(TC!$B$2:$B$48,A7,TC!$N$2:$N$48,"해당없음")</f>
         <v/>
       </c>
       <c r="H7" s="5">
@@ -1312,7 +1312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T47"/>
+  <dimension ref="A1:T48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4084,7 +4084,7 @@
     <row r="39" ht="48" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>X-01</t>
+          <t>A-09</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
@@ -4094,12 +4094,12 @@
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>5 닫기 · 뒤로가기</t>
+          <t>4 4기 신청</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>08 완료 · 서버 저장</t>
         </is>
       </c>
       <c r="E39" s="10" t="inlineStr">
@@ -4109,27 +4109,27 @@
       </c>
       <c r="F39" s="10" t="inlineStr">
         <is>
-          <t>앱</t>
+          <t>앱 · 서버(dev DB)</t>
         </is>
       </c>
       <c r="G39" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>① A-03 신청 완료 (신청 시각 메모)</t>
         </is>
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
-          <t>아무 섹션에서 ✕</t>
+          <t>신청 후 개발에 저장 행 조회 요청 · 리포트 다시 열어 07-l 확인 · 08-a 실패 때 행 없음 확인</t>
         </is>
       </c>
       <c r="I39" s="10" t="inlineStr">
         <is>
-          <t>홈으로 복귀</t>
+          <t>신청 1번 = 행 1건 (중복 없음) · 사용자 ID · 4기 프로그램 · 신청 시각(KST) 저장 · season4_applied = true → 07-l · 실패 시 저장 없음</t>
         </is>
       </c>
       <c r="J39" s="10" t="inlineStr">
         <is>
-          <t>IA-R-05</t>
+          <t>S7-11 · IA-R-12 · apply.season4_applied · 데이터 요청 6</t>
         </is>
       </c>
       <c r="K39" s="10" t="n"/>
@@ -4150,7 +4150,7 @@
     <row r="40" ht="48" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>X-02</t>
+          <t>X-01</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
@@ -4175,7 +4175,7 @@
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>앱</t>
         </is>
       </c>
       <c r="G40" s="10" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="H40" s="10" t="inlineStr">
         <is>
-          <t>리포트 / 시트 열림 / 완료 화면에서 뒤로가기</t>
+          <t>아무 섹션에서 ✕</t>
         </is>
       </c>
       <c r="I40" s="10" t="inlineStr">
         <is>
-          <t>시트가 열려 있으면 시트만 닫힘 · 그 외 홈</t>
+          <t>홈으로 복귀</t>
         </is>
       </c>
       <c r="J40" s="10" t="inlineStr">
@@ -4216,12 +4216,12 @@
     <row r="41" ht="48" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>X-03</t>
+          <t>X-02</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
-          <t>iOS</t>
+          <t>Android</t>
         </is>
       </c>
       <c r="G41" s="10" t="inlineStr">
@@ -4251,17 +4251,17 @@
       </c>
       <c r="H41" s="10" t="inlineStr">
         <is>
-          <t>밀어서 닫기</t>
+          <t>리포트 / 시트 열림 / 완료 화면에서 뒤로가기</t>
         </is>
       </c>
       <c r="I41" s="10" t="inlineStr">
         <is>
-          <t>홈 복귀 · 화면 깨짐 없음</t>
+          <t>시트가 열려 있으면 시트만 닫힘 · 그 외 홈</t>
         </is>
       </c>
       <c r="J41" s="10" t="inlineStr">
         <is>
-          <t>개발 B-7</t>
+          <t>IA-R-05</t>
         </is>
       </c>
       <c r="K41" s="10" t="n"/>
@@ -4282,7 +4282,7 @@
     <row r="42" ht="48" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>X-04</t>
+          <t>X-03</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
@@ -4297,7 +4297,7 @@
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>08 완료</t>
+          <t>공통</t>
         </is>
       </c>
       <c r="E42" s="10" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
-          <t>앱</t>
+          <t>iOS</t>
         </is>
       </c>
       <c r="G42" s="10" t="inlineStr">
@@ -4317,26 +4317,22 @@
       </c>
       <c r="H42" s="10" t="inlineStr">
         <is>
-          <t>[홈으로 돌아가기]</t>
+          <t>밀어서 닫기</t>
         </is>
       </c>
       <c r="I42" s="10" t="inlineStr">
         <is>
-          <t>홈 복귀</t>
+          <t>홈 복귀 · 화면 깨짐 없음</t>
         </is>
       </c>
       <c r="J42" s="10" t="inlineStr">
         <is>
-          <t>S8-07</t>
+          <t>개발 B-7</t>
         </is>
       </c>
       <c r="K42" s="10" t="n"/>
       <c r="L42" s="4" t="n"/>
-      <c r="M42" s="10" t="inlineStr">
-        <is>
-          <t>웹에서는 동작 안 하는 게 정상</t>
-        </is>
-      </c>
+      <c r="M42" s="10" t="n"/>
       <c r="N42" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
@@ -4352,7 +4348,7 @@
     <row r="43" ht="48" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>T-01</t>
+          <t>X-04</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
@@ -4362,17 +4358,17 @@
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>6 4기 전환</t>
+          <t>5 닫기 · 뒤로가기</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>체험 홈</t>
+          <t>08 완료</t>
         </is>
       </c>
       <c r="E43" s="10" t="inlineStr">
         <is>
-          <t>4기 승인 계정</t>
+          <t>①</t>
         </is>
       </c>
       <c r="F43" s="10" t="inlineStr">
@@ -4382,27 +4378,31 @@
       </c>
       <c r="G43" s="10" t="inlineStr">
         <is>
-          <t>개발에 4기 시작일 당겨 달라고 요청</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H43" s="10" t="inlineStr">
         <is>
-          <t>4기 홈 전환 후 확인</t>
+          <t>[홈으로 돌아가기]</t>
         </is>
       </c>
       <c r="I43" s="10" t="inlineStr">
         <is>
-          <t>홈 자동 전환 · 리포트 카드 사라짐 · 내 정보 &gt; 진행 내역 &gt; 3기 항목으로는 리포트 열림</t>
+          <t>홈 복귀</t>
         </is>
       </c>
       <c r="J43" s="10" t="inlineStr">
         <is>
-          <t>IA-R-08 · F4</t>
+          <t>S8-07</t>
         </is>
       </c>
       <c r="K43" s="10" t="n"/>
       <c r="L43" s="4" t="n"/>
-      <c r="M43" s="10" t="n"/>
+      <c r="M43" s="10" t="inlineStr">
+        <is>
+          <t>웹에서는 동작 안 하는 게 정상</t>
+        </is>
+      </c>
       <c r="N43" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
@@ -4418,7 +4418,7 @@
     <row r="44" ht="48" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>M-01</t>
+          <t>T-01</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
@@ -4428,17 +4428,17 @@
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>6 측정</t>
+          <t>6 4기 전환</t>
         </is>
       </c>
       <c r="D44" s="10" t="inlineStr">
         <is>
-          <t>이벤트</t>
+          <t>체험 홈</t>
         </is>
       </c>
       <c r="E44" s="10" t="inlineStr">
         <is>
-          <t>①</t>
+          <t>4기 승인 계정</t>
         </is>
       </c>
       <c r="F44" s="10" t="inlineStr">
@@ -4448,35 +4448,27 @@
       </c>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t>개발에 이벤트 로그 확인 요청</t>
+          <t>개발에 4기 시작일 당겨 달라고 요청</t>
         </is>
       </c>
       <c r="H44" s="10" t="inlineStr">
         <is>
-          <t>카드 / 자동 팝업 / 진행 내역으로 각각 진입</t>
+          <t>4기 홈 전환 후 확인</t>
         </is>
       </c>
       <c r="I44" s="10" t="inlineStr">
         <is>
-          <t>entry 값이 경로별로 다르게 남음 · programId 채워짐</t>
+          <t>홈 자동 전환 · 리포트 카드 사라짐 · 내 정보 &gt; 진행 내역 &gt; 3기 항목으로는 리포트 열림</t>
         </is>
       </c>
       <c r="J44" s="10" t="inlineStr">
         <is>
-          <t>IA-Q-06 · 개발 D-4</t>
+          <t>IA-R-08 · F4</t>
         </is>
       </c>
       <c r="K44" s="10" t="n"/>
-      <c r="L44" s="17" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="M44" s="18" t="inlineStr">
-        <is>
-          <t>웹 샘플은 entry=manual · programId 빈 값</t>
-        </is>
-      </c>
+      <c r="L44" s="4" t="n"/>
+      <c r="M44" s="10" t="n"/>
       <c r="N44" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
@@ -4492,7 +4484,7 @@
     <row r="45" ht="48" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>M-02</t>
+          <t>M-01</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
@@ -4522,33 +4514,33 @@
       </c>
       <c r="G45" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>개발에 이벤트 로그 확인 요청</t>
         </is>
       </c>
       <c r="H45" s="10" t="inlineStr">
         <is>
-          <t>한 섹션에 30초 머문 뒤 이동</t>
+          <t>카드 / 자동 팝업 / 진행 내역으로 각각 진입</t>
         </is>
       </c>
       <c r="I45" s="10" t="inlineStr">
         <is>
-          <t>해당 섹션 dwell ≈ 30초</t>
+          <t>entry 값이 경로별로 다르게 남음 · programId 채워짐</t>
         </is>
       </c>
       <c r="J45" s="10" t="inlineStr">
         <is>
-          <t>IA-Q-06</t>
+          <t>IA-Q-06 · 개발 D-4</t>
         </is>
       </c>
       <c r="K45" s="10" t="n"/>
       <c r="L45" s="17" t="inlineStr">
         <is>
-          <t>통과</t>
+          <t>보류</t>
         </is>
       </c>
       <c r="M45" s="18" t="inlineStr">
         <is>
-          <t>웹에서 section_view/leave + dwellMs 발생 확인</t>
+          <t>웹 샘플은 entry=manual · programId 빈 값</t>
         </is>
       </c>
       <c r="N45" s="15" t="inlineStr">
@@ -4566,22 +4558,22 @@
     <row r="46" ht="48" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>PH-01</t>
+          <t>M-02</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>6 전화번호</t>
+          <t>6 측정</t>
         </is>
       </c>
       <c r="D46" s="10" t="inlineStr">
         <is>
-          <t>전 화면</t>
+          <t>이벤트</t>
         </is>
       </c>
       <c r="E46" s="10" t="inlineStr">
@@ -4596,37 +4588,33 @@
       </c>
       <c r="G46" s="10" t="inlineStr">
         <is>
-          <t>개발 수정 반영 후</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H46" s="10" t="inlineStr">
         <is>
-          <t>리포트 완료(08) · 실패(08-a) 화면의 문의 번호</t>
+          <t>한 섹션에 30초 머문 뒤 이동</t>
         </is>
       </c>
       <c r="I46" s="10" t="inlineStr">
         <is>
-          <t>모두 032-453-6160 (6163 · 담당자 번호 없음)</t>
+          <t>해당 섹션 dwell ≈ 30초</t>
         </is>
       </c>
       <c r="J46" s="10" t="inlineStr">
         <is>
-          <t>K-14 · 보건소 요청 10/12</t>
-        </is>
-      </c>
-      <c r="K46" s="14" t="inlineStr">
-        <is>
-          <t>cmp_08.png</t>
-        </is>
-      </c>
+          <t>IA-Q-06</t>
+        </is>
+      </c>
+      <c r="K46" s="10" t="n"/>
       <c r="L46" s="17" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>통과</t>
         </is>
       </c>
       <c r="M46" s="18" t="inlineStr">
         <is>
-          <t>완료 화면 032-453-6163 → WEB-1</t>
+          <t>웹에서 section_view/leave + dwellMs 발생 확인</t>
         </is>
       </c>
       <c r="N46" s="15" t="inlineStr">
@@ -4644,17 +4632,17 @@
     <row r="47" ht="48" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>PH-01</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>7 글꼴</t>
+          <t>6 전화번호</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr">
@@ -4664,7 +4652,7 @@
       </c>
       <c r="E47" s="10" t="inlineStr">
         <is>
-          <t>②</t>
+          <t>①</t>
         </is>
       </c>
       <c r="F47" s="10" t="inlineStr">
@@ -4674,27 +4662,39 @@
       </c>
       <c r="G47" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>개발 수정 반영 후</t>
         </is>
       </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
-          <t>표지부터 완료 화면까지 글꼴을 본다 (증서 제목 · 이름 · 03 요일 차트 · 로딩 · 오류 · 비대상 · 0점/100점 · 저장 실패 토스트)</t>
+          <t>리포트 완료(08) · 실패(08-a) 화면의 문의 번호</t>
         </is>
       </c>
       <c r="I47" s="10" t="inlineStr">
         <is>
-          <t>모든 글자가 Pretendard (세리프 · Inter · 시스템 기본 글꼴 없음)</t>
+          <t>모두 032-453-6160 (6163 · 담당자 번호 없음)</t>
         </is>
       </c>
       <c r="J47" s="10" t="inlineStr">
         <is>
-          <t>10/12 기획 결정 · 변경이력 42</t>
-        </is>
-      </c>
-      <c r="K47" s="10" t="n"/>
-      <c r="L47" s="4" t="n"/>
-      <c r="M47" s="10" t="n"/>
+          <t>K-14 · 보건소 요청 10/12</t>
+        </is>
+      </c>
+      <c r="K47" s="14" t="inlineStr">
+        <is>
+          <t>cmp_08.png</t>
+        </is>
+      </c>
+      <c r="L47" s="17" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="M47" s="18" t="inlineStr">
+        <is>
+          <t>완료 화면 032-453-6163 → WEB-1</t>
+        </is>
+      </c>
       <c r="N47" s="15" t="inlineStr">
         <is>
           <t>미실행</t>
@@ -4707,9 +4707,75 @@
       <c r="S47" s="15" t="n"/>
       <c r="T47" s="15" t="n"/>
     </row>
+    <row r="48" ht="48" customHeight="1">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>G-01</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C48" s="10" t="inlineStr">
+        <is>
+          <t>7 글꼴</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>전 화면</t>
+        </is>
+      </c>
+      <c r="E48" s="10" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="F48" s="10" t="inlineStr">
+        <is>
+          <t>앱</t>
+        </is>
+      </c>
+      <c r="G48" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H48" s="10" t="inlineStr">
+        <is>
+          <t>표지부터 완료 화면까지 글꼴을 본다 (증서 제목 · 이름 · 03 요일 차트 · 로딩 · 오류 · 비대상 · 0점/100점 · 저장 실패 토스트)</t>
+        </is>
+      </c>
+      <c r="I48" s="10" t="inlineStr">
+        <is>
+          <t>모든 글자가 Pretendard (세리프 · Inter · 시스템 기본 글꼴 없음)</t>
+        </is>
+      </c>
+      <c r="J48" s="10" t="inlineStr">
+        <is>
+          <t>10/12 기획 결정 · 변경이력 42</t>
+        </is>
+      </c>
+      <c r="K48" s="10" t="n"/>
+      <c r="L48" s="4" t="n"/>
+      <c r="M48" s="10" t="n"/>
+      <c r="N48" s="15" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+      <c r="O48" s="15" t="n"/>
+      <c r="P48" s="16" t="n"/>
+      <c r="Q48" s="15" t="n"/>
+      <c r="R48" s="16" t="n"/>
+      <c r="S48" s="15" t="n"/>
+      <c r="T48" s="15" t="n"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:T1"/>
-  <conditionalFormatting sqref="L2:L47">
+  <conditionalFormatting sqref="L2:L48">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"실패"</formula>
     </cfRule>
@@ -4717,7 +4783,7 @@
       <formula>"통과"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N47">
+  <conditionalFormatting sqref="N2:N48">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="0">
       <formula>"실패"</formula>
     </cfRule>
@@ -4725,7 +4791,7 @@
       <formula>"통과"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O47">
+  <conditionalFormatting sqref="O2:O48">
     <cfRule type="cellIs" priority="5" operator="equal" dxfId="0">
       <formula>"실패"</formula>
     </cfRule>
@@ -4733,16 +4799,16 @@
       <formula>"통과"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B47">
+  <conditionalFormatting sqref="B2:B48">
     <cfRule type="cellIs" priority="7" operator="equal" dxfId="2">
       <formula>"P1"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="N2:O47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N2:O48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"미실행,통과,실패,보류,해당없음"</formula1>
     </dataValidation>
-    <dataValidation sqref="L2:L47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L2:L48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"통과,실패,보류,미실행"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4764,7 +4830,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6572,12 +6638,12 @@
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>명단 이관 (§A ④)</t>
+          <t>명단 이관 (§A ④) · 신청 결과 저장 확인</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>A-03 · A-09</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
